--- a/OPNT Docs/ToDoList.xlsx
+++ b/OPNT Docs/ToDoList.xlsx
@@ -8,15 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\AST\GitHub\opnt\OPNT Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5BD6BDB6-EB2D-4262-934E-2AAC350F8804}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD4FE680-2222-4200-9645-AEF6837D4F40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="30960" windowHeight="16800" activeTab="3" xr2:uid="{C4C29C9D-7A78-44C9-A11D-2D7769206FE1}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="5" xr2:uid="{C4C29C9D-7A78-44C9-A11D-2D7769206FE1}"/>
   </bookViews>
   <sheets>
     <sheet name="TO DO" sheetId="2" r:id="rId1"/>
     <sheet name="AST USERS" sheetId="6" r:id="rId2"/>
-    <sheet name="PROC COMPARE" sheetId="4" r:id="rId3"/>
-    <sheet name="OBJECT COMPARE" sheetId="5" r:id="rId4"/>
+    <sheet name="TRIGGERS" sheetId="8" r:id="rId3"/>
+    <sheet name="Sheet7" sheetId="9" r:id="rId4"/>
+    <sheet name="BOT_COUNT" sheetId="7" r:id="rId5"/>
+    <sheet name="PROC COMPARE" sheetId="4" r:id="rId6"/>
+    <sheet name="OBJECT COMPARE" sheetId="5" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="429" uniqueCount="206">
   <si>
     <t>OPINITO TO DO LIST</t>
   </si>
@@ -605,6 +608,63 @@
   </si>
   <si>
     <t>WSR_UNTAGGED_ARCH</t>
+  </si>
+  <si>
+    <t>STP_MONITOR_REVAMP</t>
+  </si>
+  <si>
+    <t>createBOTDiscussion</t>
+  </si>
+  <si>
+    <t>proctest</t>
+  </si>
+  <si>
+    <t>userActionCommon</t>
+  </si>
+  <si>
+    <t>DEV</t>
+  </si>
+  <si>
+    <t>getDiscussionsNW</t>
+  </si>
+  <si>
+    <t>COMMENT_CONC_NOTIF_TRIGGER</t>
+  </si>
+  <si>
+    <t>NEW_COMMENT_CLEAN_FLAG</t>
+  </si>
+  <si>
+    <t>NEW_POST_CLEAN_FLAG</t>
+  </si>
+  <si>
+    <t>POST_ACTION_DELETE</t>
+  </si>
+  <si>
+    <t>POST_COMMENT_DELETE</t>
+  </si>
+  <si>
+    <t>POST_DELETE</t>
+  </si>
+  <si>
+    <t>POST_NW_NOTIF_TRIGGER</t>
+  </si>
+  <si>
+    <t>POST_TO_KW_INSERT</t>
+  </si>
+  <si>
+    <t>POST_UPDATE</t>
+  </si>
+  <si>
+    <t>USER_NETWORK_TRIGGER</t>
+  </si>
+  <si>
+    <t>convertPostToKW</t>
+  </si>
+  <si>
+    <t>getDiscussionsTrendingNW</t>
+  </si>
+  <si>
+    <t>getInstreamTrendingNW</t>
   </si>
 </sst>
 </file>
@@ -685,15 +745,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="22" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -705,6 +756,13 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1904,393 +1962,393 @@
   </cols>
   <sheetData>
     <row r="3" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C3" s="15">
+      <c r="C3" s="12">
         <v>1022601</v>
       </c>
-      <c r="D3" s="15" t="s">
+      <c r="D3" s="12" t="s">
         <v>101</v>
       </c>
-      <c r="E3" s="15" t="s">
+      <c r="E3" s="12" t="s">
         <v>100</v>
       </c>
-      <c r="F3" s="16">
+      <c r="F3" s="13">
         <v>43895.912951388891</v>
       </c>
-      <c r="G3" s="15" t="s">
+      <c r="G3" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="H3" s="15" t="s">
+      <c r="H3" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="I3" s="15" t="s">
+      <c r="I3" s="12" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="4" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C4" s="15">
+      <c r="C4" s="12">
         <v>1022658</v>
       </c>
-      <c r="D4" s="15" t="s">
+      <c r="D4" s="12" t="s">
         <v>99</v>
       </c>
-      <c r="E4" s="15" t="s">
+      <c r="E4" s="12" t="s">
         <v>98</v>
       </c>
-      <c r="F4" s="16">
+      <c r="F4" s="13">
         <v>43923.942187499997</v>
       </c>
-      <c r="G4" s="15" t="s">
+      <c r="G4" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="H4" s="15" t="s">
+      <c r="H4" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="I4" s="15" t="s">
+      <c r="I4" s="12" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="5" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C5" s="15">
+      <c r="C5" s="12">
         <v>1022662</v>
       </c>
-      <c r="D5" s="15" t="s">
+      <c r="D5" s="12" t="s">
         <v>97</v>
       </c>
-      <c r="E5" s="15" t="s">
+      <c r="E5" s="12" t="s">
         <v>96</v>
       </c>
-      <c r="F5" s="16">
+      <c r="F5" s="13">
         <v>43927.866064814814</v>
       </c>
-      <c r="G5" s="15" t="s">
+      <c r="G5" s="12" t="s">
         <v>80</v>
       </c>
-      <c r="H5" s="15" t="s">
+      <c r="H5" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="I5" s="15" t="s">
+      <c r="I5" s="12" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="6" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C6" s="15">
+      <c r="C6" s="12">
         <v>1022726</v>
       </c>
-      <c r="D6" s="15" t="s">
+      <c r="D6" s="12" t="s">
         <v>95</v>
       </c>
-      <c r="E6" s="15" t="s">
+      <c r="E6" s="12" t="s">
         <v>94</v>
       </c>
-      <c r="F6" s="16">
+      <c r="F6" s="13">
         <v>43982.709652777776</v>
       </c>
-      <c r="G6" s="15" t="s">
+      <c r="G6" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="H6" s="15" t="s">
+      <c r="H6" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="I6" s="15" t="s">
+      <c r="I6" s="12" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="7" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C7" s="15">
+      <c r="C7" s="12">
         <v>1022727</v>
       </c>
-      <c r="D7" s="15" t="s">
+      <c r="D7" s="12" t="s">
         <v>93</v>
       </c>
-      <c r="E7" s="15" t="s">
+      <c r="E7" s="12" t="s">
         <v>92</v>
       </c>
-      <c r="F7" s="16">
+      <c r="F7" s="13">
         <v>43982.814953703702</v>
       </c>
-      <c r="G7" s="15" t="s">
+      <c r="G7" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="H7" s="15" t="s">
+      <c r="H7" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="I7" s="15" t="s">
+      <c r="I7" s="12" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="8" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C8" s="15">
+      <c r="C8" s="12">
         <v>1022766</v>
       </c>
-      <c r="D8" s="15" t="s">
+      <c r="D8" s="12" t="s">
         <v>91</v>
       </c>
-      <c r="E8" s="15" t="s">
+      <c r="E8" s="12" t="s">
         <v>90</v>
       </c>
-      <c r="F8" s="16">
+      <c r="F8" s="13">
         <v>43989.993263888886</v>
       </c>
-      <c r="G8" s="15" t="s">
+      <c r="G8" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="H8" s="15" t="s">
+      <c r="H8" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="I8" s="15" t="s">
+      <c r="I8" s="12" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="9" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C9" s="15">
+      <c r="C9" s="12">
         <v>1023416</v>
       </c>
-      <c r="D9" s="15" t="s">
+      <c r="D9" s="12" t="s">
         <v>89</v>
       </c>
-      <c r="E9" s="15" t="s">
+      <c r="E9" s="12" t="s">
         <v>88</v>
       </c>
-      <c r="F9" s="16">
+      <c r="F9" s="13">
         <v>44176.769629629627</v>
       </c>
-      <c r="G9" s="15" t="s">
+      <c r="G9" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="H9" s="15" t="s">
+      <c r="H9" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="I9" s="15" t="s">
+      <c r="I9" s="12" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="10" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C10" s="15">
+      <c r="C10" s="12">
         <v>1023432</v>
       </c>
-      <c r="D10" s="15" t="s">
+      <c r="D10" s="12" t="s">
         <v>87</v>
       </c>
-      <c r="E10" s="15" t="s">
+      <c r="E10" s="12" t="s">
         <v>86</v>
       </c>
-      <c r="F10" s="16">
+      <c r="F10" s="13">
         <v>44203.767384259256</v>
       </c>
-      <c r="G10" s="15" t="s">
+      <c r="G10" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="H10" s="15" t="s">
+      <c r="H10" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="I10" s="15" t="s">
+      <c r="I10" s="12" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="11" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C11" s="15">
+      <c r="C11" s="12">
         <v>1023438</v>
       </c>
-      <c r="D11" s="15" t="s">
+      <c r="D11" s="12" t="s">
         <v>85</v>
       </c>
-      <c r="E11" s="15" t="s">
+      <c r="E11" s="12" t="s">
         <v>84</v>
       </c>
-      <c r="F11" s="16">
+      <c r="F11" s="13">
         <v>44205.722870370373</v>
       </c>
-      <c r="G11" s="15" t="s">
+      <c r="G11" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="H11" s="15" t="s">
+      <c r="H11" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="I11" s="15" t="s">
+      <c r="I11" s="12" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="12" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C12" s="15">
+      <c r="C12" s="12">
         <v>1023879</v>
       </c>
-      <c r="D12" s="15" t="s">
+      <c r="D12" s="12" t="s">
         <v>82</v>
       </c>
-      <c r="E12" s="15" t="s">
+      <c r="E12" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="F12" s="16">
+      <c r="F12" s="13">
         <v>44299.974594907406</v>
       </c>
-      <c r="G12" s="15" t="s">
+      <c r="G12" s="12" t="s">
         <v>80</v>
       </c>
-      <c r="H12" s="15" t="s">
+      <c r="H12" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="I12" s="15" t="s">
+      <c r="I12" s="12" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="13" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C13" s="15">
+      <c r="C13" s="12">
         <v>1023880</v>
       </c>
-      <c r="D13" s="15" t="s">
+      <c r="D13" s="12" t="s">
         <v>79</v>
       </c>
-      <c r="E13" s="15" t="s">
+      <c r="E13" s="12" t="s">
         <v>78</v>
       </c>
-      <c r="F13" s="16">
+      <c r="F13" s="13">
         <v>44299.988819444443</v>
       </c>
-      <c r="G13" s="15" t="s">
+      <c r="G13" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="H13" s="15" t="s">
+      <c r="H13" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="I13" s="15" t="s">
+      <c r="I13" s="12" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="14" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C14" s="15">
+      <c r="C14" s="12">
         <v>1023948</v>
       </c>
-      <c r="D14" s="15" t="s">
+      <c r="D14" s="12" t="s">
         <v>77</v>
       </c>
-      <c r="E14" s="15" t="s">
+      <c r="E14" s="12" t="s">
         <v>76</v>
       </c>
-      <c r="F14" s="16">
+      <c r="F14" s="13">
         <v>44328.066874999997</v>
       </c>
-      <c r="G14" s="15" t="s">
+      <c r="G14" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="H14" s="15" t="s">
+      <c r="H14" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="I14" s="15" t="s">
+      <c r="I14" s="12" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="15" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C15" s="15">
+      <c r="C15" s="12">
         <v>1026625</v>
       </c>
-      <c r="D15" s="15" t="s">
+      <c r="D15" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="E15" s="15" t="s">
+      <c r="E15" s="12" t="s">
         <v>74</v>
       </c>
-      <c r="F15" s="16">
+      <c r="F15" s="13">
         <v>44847.155381944445</v>
       </c>
-      <c r="G15" s="15" t="s">
+      <c r="G15" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="H15" s="15" t="s">
+      <c r="H15" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="I15" s="15" t="s">
+      <c r="I15" s="12" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="16" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C16" s="15">
+      <c r="C16" s="12">
         <v>1032123</v>
       </c>
-      <c r="D16" s="15" t="s">
+      <c r="D16" s="12" t="s">
         <v>73</v>
       </c>
-      <c r="E16" s="15" t="s">
+      <c r="E16" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="F16" s="16">
+      <c r="F16" s="13">
         <v>45033.01394675926</v>
       </c>
-      <c r="G16" s="15" t="s">
+      <c r="G16" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="H16" s="15" t="s">
+      <c r="H16" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="I16" s="15" t="s">
+      <c r="I16" s="12" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="17" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C17" s="15">
+      <c r="C17" s="12">
         <v>1032742</v>
       </c>
-      <c r="D17" s="15" t="s">
+      <c r="D17" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="E17" s="15" t="s">
+      <c r="E17" s="12" t="s">
         <v>69</v>
       </c>
-      <c r="F17" s="16">
+      <c r="F17" s="13">
         <v>45048.675509259258</v>
       </c>
-      <c r="G17" s="15" t="s">
+      <c r="G17" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="H17" s="15" t="s">
+      <c r="H17" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="I17" s="15" t="s">
+      <c r="I17" s="12" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="18" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C18" s="15">
+      <c r="C18" s="12">
         <v>1032875</v>
       </c>
-      <c r="D18" s="15" t="s">
+      <c r="D18" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="E18" s="15" t="s">
+      <c r="E18" s="12" t="s">
         <v>67</v>
       </c>
-      <c r="F18" s="16">
+      <c r="F18" s="13">
         <v>45051.104050925926</v>
       </c>
-      <c r="G18" s="15" t="s">
+      <c r="G18" s="12" t="s">
         <v>66</v>
       </c>
-      <c r="H18" s="15" t="s">
+      <c r="H18" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="I18" s="15" t="s">
+      <c r="I18" s="12" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="19" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C19" s="15">
+      <c r="C19" s="12">
         <v>1039072</v>
       </c>
-      <c r="D19" s="15" t="s">
+      <c r="D19" s="12" t="s">
         <v>64</v>
       </c>
-      <c r="E19" s="15" t="s">
+      <c r="E19" s="12" t="s">
         <v>63</v>
       </c>
-      <c r="F19" s="16">
+      <c r="F19" s="13">
         <v>45326.032002314816</v>
       </c>
-      <c r="G19" s="15" t="s">
+      <c r="G19" s="12" t="s">
         <v>62</v>
       </c>
-      <c r="H19" s="15" t="s">
+      <c r="H19" s="12" t="s">
         <v>61</v>
       </c>
-      <c r="I19" s="15" t="s">
+      <c r="I19" s="12" t="s">
         <v>60</v>
       </c>
     </row>
@@ -2300,11 +2358,1721 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61765B45-3C92-4BC2-B87F-7B61C3132362}">
-  <dimension ref="C2:K27"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{831397A3-B5B5-4502-B050-EC180F79243F}">
+  <dimension ref="C2:H12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="19.140625" customWidth="1"/>
+    <col min="3" max="3" width="31.85546875" customWidth="1"/>
+    <col min="7" max="7" width="35.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C2" t="s">
+        <v>44</v>
+      </c>
+      <c r="G2" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="3" spans="3:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="C3" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="D3" s="6">
+        <v>1904</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="H3" s="6">
+        <v>1904</v>
+      </c>
+    </row>
+    <row r="4" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C4" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="D4" s="6">
+        <v>6291</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="H4" s="6">
+        <v>6291</v>
+      </c>
+    </row>
+    <row r="5" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C5" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="D5" s="6">
+        <v>3032</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="H5" s="6">
+        <v>3032</v>
+      </c>
+    </row>
+    <row r="6" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C6" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="D6" s="6">
+        <v>829</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="H6" s="6">
+        <v>829</v>
+      </c>
+    </row>
+    <row r="7" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C7" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="D7" s="6">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="8" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C8" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="D8" s="6">
+        <v>918</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="H8" s="6">
+        <v>1009</v>
+      </c>
+    </row>
+    <row r="9" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C9" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="D9" s="6">
+        <v>3693</v>
+      </c>
+      <c r="G9" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="H9" s="6">
+        <v>3693</v>
+      </c>
+    </row>
+    <row r="10" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C10" s="6" t="s">
+        <v>200</v>
+      </c>
+      <c r="D10" s="6">
+        <v>1561</v>
+      </c>
+      <c r="G10" s="6" t="s">
+        <v>200</v>
+      </c>
+      <c r="H10" s="6">
+        <v>1561</v>
+      </c>
+    </row>
+    <row r="11" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C11" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="D11" s="6">
+        <v>890</v>
+      </c>
+      <c r="G11" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="H11" s="6">
+        <v>890</v>
+      </c>
+    </row>
+    <row r="12" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C12" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="D12" s="6">
+        <v>303</v>
+      </c>
+      <c r="G12" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="H12" s="6">
+        <v>303</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{58AD8689-83A3-4231-B877-3E047206A588}">
+  <dimension ref="C3:E94"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="3" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C3">
+        <v>2016</v>
+      </c>
+      <c r="D3">
+        <v>6</v>
+      </c>
+      <c r="E3">
+        <v>82514</v>
+      </c>
+    </row>
+    <row r="4" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C4">
+        <v>2016</v>
+      </c>
+      <c r="D4">
+        <v>8</v>
+      </c>
+      <c r="E4">
+        <v>40401</v>
+      </c>
+    </row>
+    <row r="5" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C5">
+        <v>2016</v>
+      </c>
+      <c r="D5">
+        <v>9</v>
+      </c>
+      <c r="E5">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="6" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C6">
+        <v>2016</v>
+      </c>
+      <c r="D6">
+        <v>10</v>
+      </c>
+      <c r="E6">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="7" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C7">
+        <v>2016</v>
+      </c>
+      <c r="D7">
+        <v>11</v>
+      </c>
+      <c r="E7">
+        <v>12353</v>
+      </c>
+    </row>
+    <row r="8" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C8">
+        <v>2016</v>
+      </c>
+      <c r="D8">
+        <v>12</v>
+      </c>
+      <c r="E8">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="9" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C9">
+        <v>2017</v>
+      </c>
+      <c r="D9">
+        <v>1</v>
+      </c>
+      <c r="E9">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="10" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C10">
+        <v>2017</v>
+      </c>
+      <c r="D10">
+        <v>2</v>
+      </c>
+      <c r="E10">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="11" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C11">
+        <v>2017</v>
+      </c>
+      <c r="D11">
+        <v>3</v>
+      </c>
+      <c r="E11">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="12" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C12">
+        <v>2017</v>
+      </c>
+      <c r="D12">
+        <v>4</v>
+      </c>
+      <c r="E12">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="13" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C13">
+        <v>2017</v>
+      </c>
+      <c r="D13">
+        <v>5</v>
+      </c>
+      <c r="E13">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="14" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C14">
+        <v>2017</v>
+      </c>
+      <c r="D14">
+        <v>6</v>
+      </c>
+      <c r="E14">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="15" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C15">
+        <v>2017</v>
+      </c>
+      <c r="D15">
+        <v>7</v>
+      </c>
+      <c r="E15">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="16" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C16">
+        <v>2017</v>
+      </c>
+      <c r="D16">
+        <v>8</v>
+      </c>
+      <c r="E16">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="17" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C17">
+        <v>2017</v>
+      </c>
+      <c r="D17">
+        <v>9</v>
+      </c>
+      <c r="E17">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="18" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C18">
+        <v>2017</v>
+      </c>
+      <c r="D18">
+        <v>10</v>
+      </c>
+      <c r="E18">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="19" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C19">
+        <v>2017</v>
+      </c>
+      <c r="D19">
+        <v>11</v>
+      </c>
+      <c r="E19">
+        <v>6100</v>
+      </c>
+    </row>
+    <row r="20" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C20">
+        <v>2017</v>
+      </c>
+      <c r="D20">
+        <v>12</v>
+      </c>
+      <c r="E20">
+        <v>8371</v>
+      </c>
+    </row>
+    <row r="21" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C21">
+        <v>2018</v>
+      </c>
+      <c r="D21">
+        <v>1</v>
+      </c>
+      <c r="E21">
+        <v>1816</v>
+      </c>
+    </row>
+    <row r="22" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C22">
+        <v>2018</v>
+      </c>
+      <c r="D22">
+        <v>2</v>
+      </c>
+      <c r="E22">
+        <v>2275</v>
+      </c>
+    </row>
+    <row r="23" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C23">
+        <v>2018</v>
+      </c>
+      <c r="D23">
+        <v>3</v>
+      </c>
+      <c r="E23">
+        <v>1673</v>
+      </c>
+    </row>
+    <row r="24" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C24">
+        <v>2018</v>
+      </c>
+      <c r="D24">
+        <v>4</v>
+      </c>
+      <c r="E24">
+        <v>1445</v>
+      </c>
+    </row>
+    <row r="25" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C25">
+        <v>2018</v>
+      </c>
+      <c r="D25">
+        <v>5</v>
+      </c>
+      <c r="E25">
+        <v>997</v>
+      </c>
+    </row>
+    <row r="26" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C26">
+        <v>2018</v>
+      </c>
+      <c r="D26">
+        <v>6</v>
+      </c>
+      <c r="E26">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="27" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C27">
+        <v>2018</v>
+      </c>
+      <c r="D27">
+        <v>7</v>
+      </c>
+      <c r="E27">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="28" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C28">
+        <v>2018</v>
+      </c>
+      <c r="D28">
+        <v>8</v>
+      </c>
+      <c r="E28">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="29" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C29">
+        <v>2018</v>
+      </c>
+      <c r="D29">
+        <v>9</v>
+      </c>
+      <c r="E29">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="30" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C30">
+        <v>2018</v>
+      </c>
+      <c r="D30">
+        <v>10</v>
+      </c>
+      <c r="E30">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="31" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C31">
+        <v>2018</v>
+      </c>
+      <c r="D31">
+        <v>11</v>
+      </c>
+      <c r="E31">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="32" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C32">
+        <v>2018</v>
+      </c>
+      <c r="D32">
+        <v>12</v>
+      </c>
+      <c r="E32">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="33" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C33">
+        <v>2019</v>
+      </c>
+      <c r="D33">
+        <v>1</v>
+      </c>
+      <c r="E33">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="34" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C34">
+        <v>2019</v>
+      </c>
+      <c r="D34">
+        <v>2</v>
+      </c>
+      <c r="E34">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="35" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C35">
+        <v>2019</v>
+      </c>
+      <c r="D35">
+        <v>3</v>
+      </c>
+      <c r="E35">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="36" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C36">
+        <v>2019</v>
+      </c>
+      <c r="D36">
+        <v>4</v>
+      </c>
+      <c r="E36">
+        <v>996</v>
+      </c>
+    </row>
+    <row r="37" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C37">
+        <v>2019</v>
+      </c>
+      <c r="D37">
+        <v>5</v>
+      </c>
+      <c r="E37">
+        <v>6364</v>
+      </c>
+    </row>
+    <row r="38" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C38">
+        <v>2019</v>
+      </c>
+      <c r="D38">
+        <v>6</v>
+      </c>
+      <c r="E38">
+        <v>4635</v>
+      </c>
+    </row>
+    <row r="39" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C39">
+        <v>2019</v>
+      </c>
+      <c r="D39">
+        <v>7</v>
+      </c>
+      <c r="E39">
+        <v>2975</v>
+      </c>
+    </row>
+    <row r="40" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C40">
+        <v>2019</v>
+      </c>
+      <c r="D40">
+        <v>8</v>
+      </c>
+      <c r="E40">
+        <v>1312</v>
+      </c>
+    </row>
+    <row r="41" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C41">
+        <v>2019</v>
+      </c>
+      <c r="D41">
+        <v>9</v>
+      </c>
+      <c r="E41">
+        <v>3329</v>
+      </c>
+    </row>
+    <row r="42" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C42">
+        <v>2019</v>
+      </c>
+      <c r="D42">
+        <v>10</v>
+      </c>
+      <c r="E42">
+        <v>872</v>
+      </c>
+    </row>
+    <row r="43" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C43">
+        <v>2019</v>
+      </c>
+      <c r="D43">
+        <v>11</v>
+      </c>
+      <c r="E43">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="44" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C44">
+        <v>2019</v>
+      </c>
+      <c r="D44">
+        <v>12</v>
+      </c>
+      <c r="E44">
+        <v>738</v>
+      </c>
+    </row>
+    <row r="45" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C45">
+        <v>2020</v>
+      </c>
+      <c r="D45">
+        <v>1</v>
+      </c>
+      <c r="E45">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="46" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C46">
+        <v>2020</v>
+      </c>
+      <c r="D46">
+        <v>2</v>
+      </c>
+      <c r="E46">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="47" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C47">
+        <v>2020</v>
+      </c>
+      <c r="D47">
+        <v>3</v>
+      </c>
+      <c r="E47">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="48" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C48">
+        <v>2020</v>
+      </c>
+      <c r="D48">
+        <v>4</v>
+      </c>
+      <c r="E48">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="49" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C49">
+        <v>2020</v>
+      </c>
+      <c r="D49">
+        <v>5</v>
+      </c>
+      <c r="E49">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="50" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C50">
+        <v>2020</v>
+      </c>
+      <c r="D50">
+        <v>6</v>
+      </c>
+      <c r="E50">
+        <v>1112</v>
+      </c>
+    </row>
+    <row r="51" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C51">
+        <v>2020</v>
+      </c>
+      <c r="D51">
+        <v>7</v>
+      </c>
+      <c r="E51">
+        <v>10295</v>
+      </c>
+    </row>
+    <row r="52" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C52">
+        <v>2020</v>
+      </c>
+      <c r="D52">
+        <v>8</v>
+      </c>
+      <c r="E52">
+        <v>9110</v>
+      </c>
+    </row>
+    <row r="53" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C53">
+        <v>2020</v>
+      </c>
+      <c r="D53">
+        <v>9</v>
+      </c>
+      <c r="E53">
+        <v>4608</v>
+      </c>
+    </row>
+    <row r="54" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C54">
+        <v>2020</v>
+      </c>
+      <c r="D54">
+        <v>10</v>
+      </c>
+      <c r="E54">
+        <v>3623</v>
+      </c>
+    </row>
+    <row r="55" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C55">
+        <v>2020</v>
+      </c>
+      <c r="D55">
+        <v>11</v>
+      </c>
+      <c r="E55">
+        <v>2103</v>
+      </c>
+    </row>
+    <row r="56" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C56">
+        <v>2020</v>
+      </c>
+      <c r="D56">
+        <v>12</v>
+      </c>
+      <c r="E56">
+        <v>2821</v>
+      </c>
+    </row>
+    <row r="57" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C57">
+        <v>2021</v>
+      </c>
+      <c r="D57">
+        <v>1</v>
+      </c>
+      <c r="E57">
+        <v>2375</v>
+      </c>
+    </row>
+    <row r="58" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C58">
+        <v>2021</v>
+      </c>
+      <c r="D58">
+        <v>2</v>
+      </c>
+      <c r="E58">
+        <v>11926</v>
+      </c>
+    </row>
+    <row r="59" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C59">
+        <v>2021</v>
+      </c>
+      <c r="D59">
+        <v>3</v>
+      </c>
+      <c r="E59">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="60" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C60">
+        <v>2021</v>
+      </c>
+      <c r="D60">
+        <v>4</v>
+      </c>
+      <c r="E60">
+        <v>4456</v>
+      </c>
+    </row>
+    <row r="61" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C61">
+        <v>2021</v>
+      </c>
+      <c r="D61">
+        <v>5</v>
+      </c>
+      <c r="E61">
+        <v>7918</v>
+      </c>
+    </row>
+    <row r="62" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C62">
+        <v>2021</v>
+      </c>
+      <c r="D62">
+        <v>6</v>
+      </c>
+      <c r="E62">
+        <v>2067</v>
+      </c>
+    </row>
+    <row r="63" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C63">
+        <v>2021</v>
+      </c>
+      <c r="D63">
+        <v>7</v>
+      </c>
+      <c r="E63">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="64" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C64">
+        <v>2021</v>
+      </c>
+      <c r="D64">
+        <v>8</v>
+      </c>
+      <c r="E64">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="65" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C65">
+        <v>2021</v>
+      </c>
+      <c r="D65">
+        <v>9</v>
+      </c>
+      <c r="E65">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="66" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C66">
+        <v>2021</v>
+      </c>
+      <c r="D66">
+        <v>10</v>
+      </c>
+      <c r="E66">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="67" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C67">
+        <v>2021</v>
+      </c>
+      <c r="D67">
+        <v>12</v>
+      </c>
+      <c r="E67">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="68" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C68">
+        <v>2022</v>
+      </c>
+      <c r="D68">
+        <v>3</v>
+      </c>
+      <c r="E68">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="69" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C69">
+        <v>2022</v>
+      </c>
+      <c r="D69">
+        <v>4</v>
+      </c>
+      <c r="E69">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="70" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C70">
+        <v>2022</v>
+      </c>
+      <c r="D70">
+        <v>5</v>
+      </c>
+      <c r="E70">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="71" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C71">
+        <v>2022</v>
+      </c>
+      <c r="D71">
+        <v>6</v>
+      </c>
+      <c r="E71">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="72" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C72">
+        <v>2022</v>
+      </c>
+      <c r="D72">
+        <v>9</v>
+      </c>
+      <c r="E72">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="73" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C73">
+        <v>2022</v>
+      </c>
+      <c r="D73">
+        <v>11</v>
+      </c>
+      <c r="E73">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="74" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C74">
+        <v>2022</v>
+      </c>
+      <c r="D74">
+        <v>12</v>
+      </c>
+      <c r="E74">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="75" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C75">
+        <v>2023</v>
+      </c>
+      <c r="D75">
+        <v>3</v>
+      </c>
+      <c r="E75">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="76" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C76">
+        <v>2023</v>
+      </c>
+      <c r="D76">
+        <v>5</v>
+      </c>
+      <c r="E76">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="77" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C77">
+        <v>2023</v>
+      </c>
+      <c r="D77">
+        <v>7</v>
+      </c>
+      <c r="E77">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="78" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C78">
+        <v>2023</v>
+      </c>
+      <c r="D78">
+        <v>8</v>
+      </c>
+      <c r="E78">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="79" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C79">
+        <v>2023</v>
+      </c>
+      <c r="D79">
+        <v>9</v>
+      </c>
+      <c r="E79">
+        <v>952</v>
+      </c>
+    </row>
+    <row r="80" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C80">
+        <v>2023</v>
+      </c>
+      <c r="D80">
+        <v>10</v>
+      </c>
+      <c r="E80">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="81" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C81">
+        <v>2023</v>
+      </c>
+      <c r="D81">
+        <v>11</v>
+      </c>
+      <c r="E81">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="82" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C82">
+        <v>2023</v>
+      </c>
+      <c r="D82">
+        <v>12</v>
+      </c>
+      <c r="E82">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="83" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C83">
+        <v>2024</v>
+      </c>
+      <c r="D83">
+        <v>1</v>
+      </c>
+      <c r="E83">
+        <v>2512</v>
+      </c>
+    </row>
+    <row r="84" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C84">
+        <v>2024</v>
+      </c>
+      <c r="D84">
+        <v>2</v>
+      </c>
+      <c r="E84">
+        <v>2348</v>
+      </c>
+    </row>
+    <row r="85" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C85">
+        <v>2024</v>
+      </c>
+      <c r="D85">
+        <v>3</v>
+      </c>
+      <c r="E85">
+        <v>2190</v>
+      </c>
+    </row>
+    <row r="86" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C86">
+        <v>2024</v>
+      </c>
+      <c r="D86">
+        <v>4</v>
+      </c>
+      <c r="E86">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="87" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C87">
+        <v>2024</v>
+      </c>
+      <c r="D87">
+        <v>5</v>
+      </c>
+      <c r="E87">
+        <v>965</v>
+      </c>
+    </row>
+    <row r="88" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C88">
+        <v>2024</v>
+      </c>
+      <c r="D88">
+        <v>6</v>
+      </c>
+      <c r="E88">
+        <v>1284</v>
+      </c>
+    </row>
+    <row r="89" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C89">
+        <v>2024</v>
+      </c>
+      <c r="D89">
+        <v>7</v>
+      </c>
+      <c r="E89">
+        <v>3295</v>
+      </c>
+    </row>
+    <row r="90" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C90">
+        <v>2024</v>
+      </c>
+      <c r="D90">
+        <v>8</v>
+      </c>
+      <c r="E90">
+        <v>12315</v>
+      </c>
+    </row>
+    <row r="91" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C91">
+        <v>2024</v>
+      </c>
+      <c r="D91">
+        <v>9</v>
+      </c>
+      <c r="E91">
+        <v>6846</v>
+      </c>
+    </row>
+    <row r="92" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C92">
+        <v>2024</v>
+      </c>
+      <c r="D92">
+        <v>10</v>
+      </c>
+      <c r="E92">
+        <v>31667</v>
+      </c>
+    </row>
+    <row r="93" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C93">
+        <v>2024</v>
+      </c>
+      <c r="D93">
+        <v>11</v>
+      </c>
+      <c r="E93">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="94" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="E94">
+        <f>SUM(E3:E93)</f>
+        <v>316461</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C1D50FC-F6C6-4A8B-8B80-3E57F2ED5AA6}">
+  <dimension ref="B2:J23"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="2" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="C2" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="3" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3">
+        <v>105087</v>
+      </c>
+      <c r="D3" t="s">
+        <v>80</v>
+      </c>
+      <c r="E3">
+        <v>228</v>
+      </c>
+      <c r="G3">
+        <v>1</v>
+      </c>
+      <c r="H3">
+        <v>105087</v>
+      </c>
+      <c r="I3" t="s">
+        <v>80</v>
+      </c>
+      <c r="J3">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="4" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4">
+        <v>105087</v>
+      </c>
+      <c r="D4" t="s">
+        <v>66</v>
+      </c>
+      <c r="E4">
+        <v>854</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>105087</v>
+      </c>
+      <c r="I4" t="s">
+        <v>66</v>
+      </c>
+      <c r="J4">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="5" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5">
+        <v>105087</v>
+      </c>
+      <c r="D5" t="s">
+        <v>62</v>
+      </c>
+      <c r="E5">
+        <v>2228</v>
+      </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="H5">
+        <v>105087</v>
+      </c>
+      <c r="I5" t="s">
+        <v>62</v>
+      </c>
+      <c r="J5">
+        <v>1108</v>
+      </c>
+    </row>
+    <row r="6" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B6">
+        <v>2</v>
+      </c>
+      <c r="C6">
+        <v>105654</v>
+      </c>
+      <c r="D6" t="s">
+        <v>80</v>
+      </c>
+      <c r="E6">
+        <v>122</v>
+      </c>
+      <c r="G6">
+        <v>2</v>
+      </c>
+      <c r="H6">
+        <v>105654</v>
+      </c>
+      <c r="I6" t="s">
+        <v>80</v>
+      </c>
+      <c r="J6">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="7" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B7">
+        <v>2</v>
+      </c>
+      <c r="C7">
+        <v>105654</v>
+      </c>
+      <c r="D7" t="s">
+        <v>66</v>
+      </c>
+      <c r="E7">
+        <v>338</v>
+      </c>
+      <c r="G7">
+        <v>2</v>
+      </c>
+      <c r="H7">
+        <v>105654</v>
+      </c>
+      <c r="I7" t="s">
+        <v>66</v>
+      </c>
+      <c r="J7">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="8" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B8">
+        <v>2</v>
+      </c>
+      <c r="C8">
+        <v>105654</v>
+      </c>
+      <c r="D8" t="s">
+        <v>62</v>
+      </c>
+      <c r="E8">
+        <v>668</v>
+      </c>
+      <c r="G8">
+        <v>2</v>
+      </c>
+      <c r="H8">
+        <v>105654</v>
+      </c>
+      <c r="I8" t="s">
+        <v>62</v>
+      </c>
+      <c r="J8">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="9" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B9">
+        <v>3</v>
+      </c>
+      <c r="C9">
+        <v>105108</v>
+      </c>
+      <c r="D9" t="s">
+        <v>80</v>
+      </c>
+      <c r="E9">
+        <v>250</v>
+      </c>
+      <c r="G9">
+        <v>3</v>
+      </c>
+      <c r="H9">
+        <v>105108</v>
+      </c>
+      <c r="I9" t="s">
+        <v>80</v>
+      </c>
+      <c r="J9">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="10" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="G10">
+        <v>3</v>
+      </c>
+      <c r="H10">
+        <v>105108</v>
+      </c>
+      <c r="I10" t="s">
+        <v>66</v>
+      </c>
+      <c r="J10">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="11" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="G11">
+        <v>3</v>
+      </c>
+      <c r="H11">
+        <v>105108</v>
+      </c>
+      <c r="I11" t="s">
+        <v>62</v>
+      </c>
+      <c r="J11">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="12" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B12">
+        <v>4</v>
+      </c>
+      <c r="C12">
+        <v>105653</v>
+      </c>
+      <c r="D12" t="s">
+        <v>80</v>
+      </c>
+      <c r="E12">
+        <v>218</v>
+      </c>
+      <c r="G12">
+        <v>4</v>
+      </c>
+      <c r="H12">
+        <v>105653</v>
+      </c>
+      <c r="I12" t="s">
+        <v>80</v>
+      </c>
+      <c r="J12">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="13" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B13">
+        <v>4</v>
+      </c>
+      <c r="C13">
+        <v>105653</v>
+      </c>
+      <c r="D13" t="s">
+        <v>66</v>
+      </c>
+      <c r="E13">
+        <v>438</v>
+      </c>
+      <c r="G13">
+        <v>4</v>
+      </c>
+      <c r="H13">
+        <v>105653</v>
+      </c>
+      <c r="I13" t="s">
+        <v>66</v>
+      </c>
+      <c r="J13">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="14" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B14">
+        <v>4</v>
+      </c>
+      <c r="C14">
+        <v>105653</v>
+      </c>
+      <c r="D14" t="s">
+        <v>62</v>
+      </c>
+      <c r="E14">
+        <v>768</v>
+      </c>
+      <c r="G14">
+        <v>4</v>
+      </c>
+      <c r="H14">
+        <v>105653</v>
+      </c>
+      <c r="I14" t="s">
+        <v>62</v>
+      </c>
+      <c r="J14">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="15" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B15">
+        <v>5</v>
+      </c>
+      <c r="C15">
+        <v>105655</v>
+      </c>
+      <c r="D15" t="s">
+        <v>80</v>
+      </c>
+      <c r="E15">
+        <v>215</v>
+      </c>
+      <c r="G15">
+        <v>5</v>
+      </c>
+      <c r="H15">
+        <v>105655</v>
+      </c>
+      <c r="I15" t="s">
+        <v>80</v>
+      </c>
+      <c r="J15">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="16" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B16">
+        <v>5</v>
+      </c>
+      <c r="C16">
+        <v>105655</v>
+      </c>
+      <c r="D16" t="s">
+        <v>66</v>
+      </c>
+      <c r="E16">
+        <v>435</v>
+      </c>
+      <c r="G16">
+        <v>5</v>
+      </c>
+      <c r="H16">
+        <v>105655</v>
+      </c>
+      <c r="I16" t="s">
+        <v>66</v>
+      </c>
+      <c r="J16">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="17" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B17">
+        <v>5</v>
+      </c>
+      <c r="C17">
+        <v>105655</v>
+      </c>
+      <c r="D17" t="s">
+        <v>62</v>
+      </c>
+      <c r="E17">
+        <v>765</v>
+      </c>
+      <c r="G17">
+        <v>5</v>
+      </c>
+      <c r="H17">
+        <v>105655</v>
+      </c>
+      <c r="I17" t="s">
+        <v>62</v>
+      </c>
+      <c r="J17">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="18" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B18">
+        <v>10</v>
+      </c>
+      <c r="C18">
+        <v>105088</v>
+      </c>
+      <c r="D18" t="s">
+        <v>80</v>
+      </c>
+      <c r="E18">
+        <v>110</v>
+      </c>
+      <c r="G18">
+        <v>10</v>
+      </c>
+      <c r="H18">
+        <v>105088</v>
+      </c>
+      <c r="I18" t="s">
+        <v>80</v>
+      </c>
+      <c r="J18">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="19" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B19">
+        <v>10</v>
+      </c>
+      <c r="C19">
+        <v>105088</v>
+      </c>
+      <c r="D19" t="s">
+        <v>66</v>
+      </c>
+      <c r="E19">
+        <v>438</v>
+      </c>
+      <c r="G19">
+        <v>10</v>
+      </c>
+      <c r="H19">
+        <v>105088</v>
+      </c>
+      <c r="I19" t="s">
+        <v>66</v>
+      </c>
+      <c r="J19">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="20" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B20">
+        <v>10</v>
+      </c>
+      <c r="C20">
+        <v>105088</v>
+      </c>
+      <c r="D20" t="s">
+        <v>62</v>
+      </c>
+      <c r="E20">
+        <v>220</v>
+      </c>
+      <c r="G20">
+        <v>10</v>
+      </c>
+      <c r="H20">
+        <v>105088</v>
+      </c>
+      <c r="I20" t="s">
+        <v>62</v>
+      </c>
+      <c r="J20">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="21" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B21">
+        <v>10</v>
+      </c>
+      <c r="C21">
+        <v>105089</v>
+      </c>
+      <c r="D21" t="s">
+        <v>80</v>
+      </c>
+      <c r="E21">
+        <v>441</v>
+      </c>
+      <c r="G21">
+        <v>10</v>
+      </c>
+      <c r="H21">
+        <v>105089</v>
+      </c>
+      <c r="I21" t="s">
+        <v>80</v>
+      </c>
+      <c r="J21">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="22" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B22">
+        <v>10</v>
+      </c>
+      <c r="C22">
+        <v>105089</v>
+      </c>
+      <c r="D22" t="s">
+        <v>66</v>
+      </c>
+      <c r="E22">
+        <v>741</v>
+      </c>
+      <c r="G22">
+        <v>10</v>
+      </c>
+      <c r="H22">
+        <v>105089</v>
+      </c>
+      <c r="I22" t="s">
+        <v>66</v>
+      </c>
+      <c r="J22">
+        <v>741</v>
+      </c>
+    </row>
+    <row r="23" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B23">
+        <v>10</v>
+      </c>
+      <c r="C23">
+        <v>105089</v>
+      </c>
+      <c r="D23" t="s">
+        <v>62</v>
+      </c>
+      <c r="E23">
+        <v>2227</v>
+      </c>
+      <c r="G23">
+        <v>10</v>
+      </c>
+      <c r="H23">
+        <v>105089</v>
+      </c>
+      <c r="I23" t="s">
+        <v>62</v>
+      </c>
+      <c r="J23">
+        <v>1227</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61765B45-3C92-4BC2-B87F-7B61C3132362}">
+  <dimension ref="C2:O35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="3" width="28.7109375" customWidth="1"/>
     <col min="4" max="4" width="30.5703125" customWidth="1"/>
     <col min="5" max="5" width="18.5703125" customWidth="1"/>
     <col min="6" max="6" width="15.7109375" customWidth="1"/>
@@ -2312,22 +4080,25 @@
     <col min="9" max="9" width="27" customWidth="1"/>
     <col min="10" max="10" width="23.7109375" customWidth="1"/>
     <col min="11" max="11" width="19.42578125" customWidth="1"/>
+    <col min="12" max="12" width="12.5703125" customWidth="1"/>
+    <col min="13" max="13" width="23.140625" customWidth="1"/>
+    <col min="14" max="14" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="3:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C2" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="4" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C4" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="D4" s="8" t="s">
+    <row r="4" spans="3:15" x14ac:dyDescent="0.25">
+      <c r="C4" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="E4" s="9">
+      <c r="D4" s="7">
         <v>45487.799317129633</v>
+      </c>
+      <c r="E4" s="6">
+        <v>3474</v>
       </c>
       <c r="F4" s="8">
         <v>3474</v>
@@ -2344,426 +4115,726 @@
       <c r="K4" s="6">
         <v>3474</v>
       </c>
-    </row>
-    <row r="5" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="M4" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="N4" s="7">
+        <v>45487.799317129633</v>
+      </c>
+      <c r="O4" s="6">
+        <v>3474</v>
+      </c>
+    </row>
+    <row r="5" spans="3:15" ht="30" x14ac:dyDescent="0.25">
+      <c r="C5" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="D5" s="7">
+        <v>45603.933032407411</v>
+      </c>
+      <c r="E5" s="6">
+        <v>7271</v>
+      </c>
       <c r="H5" s="6" t="s">
         <v>34</v>
       </c>
       <c r="I5" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="J5" s="7">
+        <v>45603.932650462964</v>
+      </c>
+      <c r="K5" s="6">
+        <v>7271</v>
+      </c>
+      <c r="M5" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="N5" s="7">
+        <v>45488.204421296294</v>
+      </c>
+      <c r="O5" s="6">
+        <v>2104</v>
+      </c>
+    </row>
+    <row r="6" spans="3:15" ht="30" x14ac:dyDescent="0.25">
+      <c r="C6" s="10" t="s">
+        <v>188</v>
+      </c>
+      <c r="D6" s="11">
+        <v>45592.980578703704</v>
+      </c>
+      <c r="E6" s="10">
+        <v>11282</v>
+      </c>
+      <c r="F6" s="9"/>
+      <c r="G6" s="9"/>
+      <c r="H6" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="I6" s="10" t="s">
+        <v>188</v>
+      </c>
+      <c r="J6" s="11">
+        <v>45603.922986111109</v>
+      </c>
+      <c r="K6" s="10">
+        <v>11380</v>
+      </c>
+      <c r="M6" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="N6" s="7">
+        <v>45580.246689814812</v>
+      </c>
+      <c r="O6" s="6">
+        <v>9550</v>
+      </c>
+    </row>
+    <row r="7" spans="3:15" x14ac:dyDescent="0.25">
+      <c r="C7" s="9"/>
+      <c r="D7" s="9"/>
+      <c r="E7" s="9"/>
+      <c r="F7" s="9"/>
+      <c r="G7" s="9"/>
+      <c r="H7" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="I7" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="J5" s="7">
+      <c r="J7" s="11">
         <v>45572.001712962963</v>
       </c>
-      <c r="K5" s="6">
+      <c r="K7" s="10">
         <v>3963</v>
       </c>
-    </row>
-    <row r="6" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="H6" s="6" t="s">
+      <c r="M7" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="N7" s="7">
+        <v>45559.065092592595</v>
+      </c>
+      <c r="O7" s="6">
+        <v>11083</v>
+      </c>
+    </row>
+    <row r="8" spans="3:15" x14ac:dyDescent="0.25">
+      <c r="C8" s="9"/>
+      <c r="D8" s="9"/>
+      <c r="E8" s="9"/>
+      <c r="F8" s="9"/>
+      <c r="G8" s="9"/>
+      <c r="H8" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="I6" s="6" t="s">
+      <c r="I8" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="J6" s="7">
+      <c r="J8" s="11">
         <v>45555.870868055557</v>
       </c>
-      <c r="K6" s="6">
+      <c r="K8" s="10">
         <v>430</v>
       </c>
-    </row>
-    <row r="7" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="H7" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="I7" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="J7" s="7">
-        <v>45568.769444444442</v>
-      </c>
-      <c r="K7" s="6">
-        <v>1370</v>
-      </c>
-    </row>
-    <row r="8" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="H8" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="I8" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="J8" s="7">
-        <v>45562.205208333333</v>
-      </c>
-      <c r="K8" s="6">
-        <v>938</v>
-      </c>
-    </row>
-    <row r="9" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="M8" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="N8" s="7">
+        <v>45585.078321759262</v>
+      </c>
+      <c r="O8" s="6">
+        <v>7216</v>
+      </c>
+    </row>
+    <row r="9" spans="3:15" x14ac:dyDescent="0.25">
       <c r="H9" s="6" t="s">
         <v>34</v>
       </c>
       <c r="I9" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="J9" s="7">
+        <v>45568.769444444442</v>
+      </c>
+      <c r="K9" s="6">
+        <v>1370</v>
+      </c>
+      <c r="M9" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="N9" s="7">
+        <v>45585.078958333332</v>
+      </c>
+      <c r="O9" s="6">
+        <v>6691</v>
+      </c>
+    </row>
+    <row r="10" spans="3:15" x14ac:dyDescent="0.25">
+      <c r="C10" s="10" t="s">
+        <v>192</v>
+      </c>
+      <c r="D10" s="11">
+        <v>45607.054201388892</v>
+      </c>
+      <c r="E10" s="10">
+        <v>6918</v>
+      </c>
+      <c r="F10" s="9"/>
+      <c r="G10" s="9"/>
+      <c r="H10" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="I10" s="10" t="s">
+        <v>192</v>
+      </c>
+      <c r="J10" s="11">
+        <v>45608.240393518521</v>
+      </c>
+      <c r="K10" s="10">
+        <v>7098</v>
+      </c>
+      <c r="M10" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="N10" s="7">
+        <v>45559.059641203705</v>
+      </c>
+      <c r="O10" s="6">
+        <v>3838</v>
+      </c>
+    </row>
+    <row r="11" spans="3:15" x14ac:dyDescent="0.25">
+      <c r="I11" s="10" t="s">
+        <v>204</v>
+      </c>
+      <c r="J11" s="11">
+        <v>45608.240486111114</v>
+      </c>
+      <c r="K11" s="10">
+        <v>4570</v>
+      </c>
+      <c r="M11" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="N11" s="7">
+        <v>45564.562025462961</v>
+      </c>
+      <c r="O11" s="6">
+        <v>2780</v>
+      </c>
+    </row>
+    <row r="12" spans="3:15" x14ac:dyDescent="0.25">
+      <c r="F12" s="14">
+        <v>2104</v>
+      </c>
+      <c r="G12" s="15"/>
+      <c r="H12" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="I12" s="10" t="s">
+        <v>205</v>
+      </c>
+      <c r="J12" s="11">
+        <v>45602.928657407407</v>
+      </c>
+      <c r="K12" s="10">
+        <v>5451</v>
+      </c>
+      <c r="M12" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="N12" s="7">
+        <v>45583.870821759258</v>
+      </c>
+      <c r="O12" s="6">
+        <v>2146</v>
+      </c>
+    </row>
+    <row r="13" spans="3:15" x14ac:dyDescent="0.25">
+      <c r="F13" s="15"/>
+      <c r="G13" s="15"/>
+      <c r="H13" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="I13" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="J13" s="11">
+        <v>45562.205208333333</v>
+      </c>
+      <c r="K13" s="10">
+        <v>938</v>
+      </c>
+      <c r="M13" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="N13" s="7">
+        <v>45564.561944444446</v>
+      </c>
+      <c r="O13" s="6">
+        <v>2756</v>
+      </c>
+    </row>
+    <row r="14" spans="3:15" x14ac:dyDescent="0.25">
+      <c r="F14" s="15"/>
+      <c r="G14" s="15"/>
+      <c r="H14" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="I14" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="J9" s="7">
+      <c r="J14" s="11">
         <v>45553.747881944444</v>
       </c>
-      <c r="K9" s="6">
+      <c r="K14" s="10">
         <v>1211</v>
       </c>
     </row>
-    <row r="10" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="H10" s="6" t="s">
+    <row r="15" spans="3:15" x14ac:dyDescent="0.25">
+      <c r="F15" s="15"/>
+      <c r="G15" s="15"/>
+      <c r="H15" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="I10" s="6" t="s">
+      <c r="I15" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="J10" s="7">
+      <c r="J15" s="7">
         <v>45488.006921296299</v>
       </c>
-      <c r="K10" s="6">
+      <c r="K15" s="6">
         <v>2192</v>
       </c>
     </row>
-    <row r="11" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C11" s="10" t="s">
+    <row r="16" spans="3:15" ht="30" x14ac:dyDescent="0.25">
+      <c r="C16" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="D16" s="7">
+        <v>45488.204421296294</v>
+      </c>
+      <c r="E16" s="6">
+        <v>2104</v>
+      </c>
+      <c r="F16" s="14">
+        <v>9550</v>
+      </c>
+      <c r="G16" s="15"/>
+      <c r="H16" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="D11" s="10" t="s">
+      <c r="I16" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="E11" s="11">
-        <v>45488.204421296294</v>
-      </c>
-      <c r="F11" s="10">
-        <v>2104</v>
-      </c>
-      <c r="G11" s="12"/>
-      <c r="H11" s="13" t="s">
+      <c r="J16" s="7">
+        <v>45488.089548611111</v>
+      </c>
+      <c r="K16" s="6">
+        <v>2254</v>
+      </c>
+    </row>
+    <row r="17" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="F17" s="15"/>
+      <c r="G17" s="15"/>
+      <c r="H17" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="I11" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="J11" s="14">
-        <v>45488.089548611111</v>
-      </c>
-      <c r="K11" s="13">
-        <v>2254</v>
-      </c>
-    </row>
-    <row r="12" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="H12" s="6" t="s">
+      <c r="I17" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="J17" s="7">
+        <v>45587.166886574072</v>
+      </c>
+      <c r="K17" s="6">
+        <v>1801</v>
+      </c>
+    </row>
+    <row r="18" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C18" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="D18" s="7">
+        <v>45598.704918981479</v>
+      </c>
+      <c r="E18" s="6">
+        <v>1654</v>
+      </c>
+      <c r="F18" s="15"/>
+      <c r="G18" s="15"/>
+      <c r="H18" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="I12" s="6" t="s">
+      <c r="I18" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="J12" s="7">
+      <c r="J18" s="7">
         <v>45570.907997685186</v>
       </c>
-      <c r="K12" s="6">
+      <c r="K18" s="6">
         <v>1654</v>
       </c>
     </row>
-    <row r="13" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="H13" s="6" t="s">
+    <row r="19" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C19" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="D19" s="7">
+        <v>45598.705104166664</v>
+      </c>
+      <c r="E19" s="6">
+        <v>1855</v>
+      </c>
+      <c r="F19" s="15"/>
+      <c r="G19" s="15"/>
+      <c r="H19" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="I13" s="6" t="s">
+      <c r="I19" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="J13" s="7">
+      <c r="J19" s="7">
         <v>45570.908067129632</v>
       </c>
-      <c r="K13" s="6">
+      <c r="K19" s="6">
         <v>1855</v>
       </c>
     </row>
-    <row r="14" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="H14" s="6" t="s">
+    <row r="20" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="F20" s="15"/>
+      <c r="G20" s="15"/>
+      <c r="H20" s="15"/>
+      <c r="I20" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="J20" s="11">
+        <v>45561.140324074076</v>
+      </c>
+      <c r="K20" s="10">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="21" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C21" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="D21" s="7">
+        <v>45580.246689814812</v>
+      </c>
+      <c r="E21" s="6">
+        <v>9550</v>
+      </c>
+      <c r="F21" s="15"/>
+      <c r="G21" s="15"/>
+      <c r="H21" s="15"/>
+      <c r="I21" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="J21" s="7">
+        <v>45580.654513888891</v>
+      </c>
+      <c r="K21" s="6">
+        <v>9550</v>
+      </c>
+    </row>
+    <row r="22" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C22" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="D22" s="7">
+        <v>45601.294317129628</v>
+      </c>
+      <c r="E22" s="6">
+        <v>6075</v>
+      </c>
+      <c r="F22" s="14"/>
+      <c r="G22" s="15"/>
+      <c r="H22" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="I14" s="6" t="s">
-        <v>53</v>
-      </c>
-      <c r="J14" s="7">
-        <v>45561.140324074076</v>
-      </c>
-      <c r="K14" s="6">
-        <v>686</v>
-      </c>
-    </row>
-    <row r="15" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C15" s="8" t="s">
+      <c r="I22" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="J22" s="7">
+        <v>45601.281597222223</v>
+      </c>
+      <c r="K22" s="6">
+        <v>6075</v>
+      </c>
+    </row>
+    <row r="23" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="F23" s="15"/>
+      <c r="G23" s="15"/>
+      <c r="H23" s="15"/>
+      <c r="I23" s="10" t="s">
+        <v>55</v>
+      </c>
+      <c r="J23" s="11">
+        <v>45562.222928240742</v>
+      </c>
+      <c r="K23" s="10">
+        <v>1633</v>
+      </c>
+    </row>
+    <row r="24" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C24" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="D24" s="7">
+        <v>45592.980821759258</v>
+      </c>
+      <c r="E24" s="6">
+        <v>8304</v>
+      </c>
+      <c r="F24" s="16"/>
+      <c r="G24" s="15"/>
+      <c r="H24" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="D15" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="E15" s="9">
-        <v>45580.246689814812</v>
-      </c>
-      <c r="F15" s="8">
-        <v>9550</v>
-      </c>
-      <c r="H15" s="6" t="s">
+      <c r="I24" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="J24" s="7">
+        <v>45583.714583333334</v>
+      </c>
+      <c r="K24" s="6">
+        <v>8304</v>
+      </c>
+    </row>
+    <row r="25" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C25" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="D25" s="7">
+        <v>45602.853263888886</v>
+      </c>
+      <c r="E25" s="6">
+        <v>9421</v>
+      </c>
+      <c r="F25" s="15"/>
+      <c r="G25" s="15"/>
+      <c r="H25" s="15"/>
+      <c r="I25" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="J25" s="7">
+        <v>45602.853148148148</v>
+      </c>
+      <c r="K25" s="6">
+        <v>9422</v>
+      </c>
+    </row>
+    <row r="26" spans="3:11" ht="30" x14ac:dyDescent="0.25">
+      <c r="C26" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="D26" s="7">
+        <v>45585.078321759262</v>
+      </c>
+      <c r="E26" s="6">
+        <v>7216</v>
+      </c>
+      <c r="F26" s="15"/>
+      <c r="G26" s="15"/>
+      <c r="H26" s="15"/>
+      <c r="I26" s="6" t="s">
+        <v>187</v>
+      </c>
+      <c r="J26" s="7">
+        <v>45587.921111111114</v>
+      </c>
+      <c r="K26" s="6">
+        <v>9421</v>
+      </c>
+    </row>
+    <row r="27" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C27" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="D27" s="7">
+        <v>45592.98133101852</v>
+      </c>
+      <c r="E27" s="6">
+        <v>6691</v>
+      </c>
+      <c r="F27" s="14"/>
+      <c r="G27" s="15"/>
+      <c r="H27" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="I15" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="J15" s="7">
-        <v>45580.654513888891</v>
-      </c>
-      <c r="K15" s="6">
-        <v>9550</v>
-      </c>
-    </row>
-    <row r="16" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="H16" s="6" t="s">
+      <c r="I27" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="J27" s="7">
+        <v>45582.831134259257</v>
+      </c>
+      <c r="K27" s="6">
+        <v>6691</v>
+      </c>
+    </row>
+    <row r="28" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="F28" s="14"/>
+      <c r="G28" s="15"/>
+      <c r="H28" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="I16" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="J16" s="7">
-        <v>45568.200532407405</v>
-      </c>
-      <c r="K16" s="6">
-        <v>5973</v>
-      </c>
-    </row>
-    <row r="17" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="H17" s="6" t="s">
+      <c r="I28" s="10" t="s">
+        <v>57</v>
+      </c>
+      <c r="J28" s="11">
+        <v>45571.087962962964</v>
+      </c>
+      <c r="K28" s="10">
+        <v>4306</v>
+      </c>
+    </row>
+    <row r="29" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C29" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="D29" s="7">
+        <v>45592.981458333335</v>
+      </c>
+      <c r="E29" s="6">
+        <v>5118</v>
+      </c>
+      <c r="F29" s="14"/>
+      <c r="G29" s="15"/>
+      <c r="H29" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="I17" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="J17" s="7">
-        <v>45562.222928240742</v>
-      </c>
-      <c r="K17" s="6">
-        <v>1633</v>
-      </c>
-    </row>
-    <row r="18" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="H18" s="6" t="s">
+      <c r="I29" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="J29" s="7">
+        <v>45587.194444444445</v>
+      </c>
+      <c r="K29" s="6">
+        <v>5118</v>
+      </c>
+    </row>
+    <row r="30" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C30" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="D30" s="7">
+        <v>45559.059641203705</v>
+      </c>
+      <c r="E30" s="6">
+        <v>3838</v>
+      </c>
+      <c r="F30" s="15"/>
+      <c r="G30" s="15"/>
+      <c r="H30" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="I18" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="J18" s="7">
-        <v>45572.131018518521</v>
-      </c>
-      <c r="K18" s="6">
-        <v>7890</v>
-      </c>
-    </row>
-    <row r="19" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C19" s="10" t="s">
+      <c r="I30" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="J30" s="7">
+        <v>45554.139884259261</v>
+      </c>
+      <c r="K30" s="6">
+        <v>3838</v>
+      </c>
+    </row>
+    <row r="31" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C31" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="D31" s="7">
+        <v>45564.562025462961</v>
+      </c>
+      <c r="E31" s="6">
+        <v>2780</v>
+      </c>
+      <c r="F31" s="14"/>
+      <c r="G31" s="15"/>
+      <c r="H31" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="D19" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="E19" s="11">
-        <v>45559.065092592595</v>
-      </c>
-      <c r="F19" s="10">
-        <v>11083</v>
-      </c>
-      <c r="G19" s="12"/>
-      <c r="H19" s="13" t="s">
+      <c r="I31" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="J31" s="7">
+        <v>45564.561550925922</v>
+      </c>
+      <c r="K31" s="6">
+        <v>2780</v>
+      </c>
+    </row>
+    <row r="32" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C32" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="D32" s="7">
+        <v>45592.926134259258</v>
+      </c>
+      <c r="E32" s="6">
+        <v>2667</v>
+      </c>
+      <c r="F32" s="15"/>
+      <c r="G32" s="15"/>
+      <c r="H32" s="16" t="s">
         <v>34</v>
       </c>
-      <c r="I19" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="J19" s="14">
-        <v>45558.301736111112</v>
-      </c>
-      <c r="K19" s="13">
-        <v>11057</v>
-      </c>
-    </row>
-    <row r="20" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C20" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="D20" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="E20" s="11">
-        <v>45495.157013888886</v>
-      </c>
-      <c r="F20" s="10">
-        <v>5465</v>
-      </c>
-      <c r="G20" s="12"/>
-      <c r="H20" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="I20" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="J20" s="14">
-        <v>45571.087465277778</v>
-      </c>
-      <c r="K20" s="13">
-        <v>6538</v>
-      </c>
-    </row>
-    <row r="21" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="H21" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="I21" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="J21" s="7">
-        <v>45571.087962962964</v>
-      </c>
-      <c r="K21" s="6">
-        <v>4306</v>
-      </c>
-    </row>
-    <row r="22" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C22" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="D22" s="8" t="s">
-        <v>40</v>
-      </c>
-      <c r="E22" s="9">
-        <v>45559.059641203705</v>
-      </c>
-      <c r="F22" s="8">
-        <v>3838</v>
-      </c>
-      <c r="H22" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="I22" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="J22" s="7">
-        <v>45554.139884259261</v>
-      </c>
-      <c r="K22" s="6">
-        <v>3838</v>
-      </c>
-    </row>
-    <row r="23" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C23" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="D23" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="E23" s="9">
-        <v>45564.562025462961</v>
-      </c>
-      <c r="F23" s="8">
-        <v>2780</v>
-      </c>
-      <c r="H23" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="I23" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="J23" s="7">
-        <v>45564.561550925922</v>
-      </c>
-      <c r="K23" s="6">
-        <v>2780</v>
-      </c>
-    </row>
-    <row r="24" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C24" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="D24" s="10" t="s">
+      <c r="I32" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="E24" s="11">
-        <v>45558.27107638889</v>
-      </c>
-      <c r="F24" s="10">
-        <v>2038</v>
-      </c>
-      <c r="G24" s="12"/>
-      <c r="H24" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="I24" s="13" t="s">
-        <v>42</v>
-      </c>
-      <c r="J24" s="14">
-        <v>45558.301238425927</v>
-      </c>
-      <c r="K24" s="13">
-        <v>2146</v>
-      </c>
-    </row>
-    <row r="25" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="H25" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="I25" s="6" t="s">
+      <c r="J32" s="7">
+        <v>45587.760914351849</v>
+      </c>
+      <c r="K32" s="6">
+        <v>2667</v>
+      </c>
+    </row>
+    <row r="33" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="F33" s="15"/>
+      <c r="G33" s="15"/>
+      <c r="I33" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="J25" s="7">
+      <c r="J33" s="7">
         <v>45494.86377314815</v>
       </c>
-      <c r="K25" s="6">
+      <c r="K33" s="6">
         <v>3716</v>
       </c>
     </row>
-    <row r="26" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C26" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="D26" s="8" t="s">
+    <row r="34" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C34" s="15"/>
+      <c r="D34" s="15"/>
+      <c r="E34" s="15"/>
+      <c r="F34" s="15"/>
+      <c r="G34" s="15"/>
+      <c r="I34" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="E26" s="9">
+      <c r="J34" s="7">
+        <v>45564.554328703707</v>
+      </c>
+      <c r="K34" s="6">
+        <v>2756</v>
+      </c>
+    </row>
+    <row r="35" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C35" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="D35" s="7">
         <v>45564.561944444446</v>
       </c>
-      <c r="F26" s="8">
+      <c r="E35" s="6">
         <v>2756</v>
       </c>
-      <c r="H26" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="I26" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="J26" s="7">
-        <v>45564.554328703707</v>
-      </c>
-      <c r="K26" s="6">
-        <v>2756</v>
-      </c>
-    </row>
-    <row r="27" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="H27" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="I27" s="6" t="s">
+      <c r="I35" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="J27" s="7">
+      <c r="J35" s="7">
         <v>45494.09170138889</v>
       </c>
-      <c r="K27" s="6">
+      <c r="K35" s="6">
         <v>3726</v>
       </c>
     </row>
@@ -2772,16 +4843,16 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5729499-E483-4C36-94CD-F33C4A49C2B8}">
-  <dimension ref="C3:G87"/>
+  <dimension ref="C3:H87"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="31.42578125" customWidth="1"/>
     <col min="6" max="6" width="35.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="3:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C3" s="6" t="s">
         <v>102</v>
       </c>
@@ -2794,8 +4865,12 @@
       <c r="G3" s="6">
         <v>9</v>
       </c>
-    </row>
-    <row r="4" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="H3">
+        <f>D3-G3</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C4" s="6" t="s">
         <v>103</v>
       </c>
@@ -2808,8 +4883,12 @@
       <c r="G4" s="6">
         <v>11</v>
       </c>
-    </row>
-    <row r="5" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="H4">
+        <f t="shared" ref="H4:H67" si="0">D4-G4</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C5" s="6" t="s">
         <v>104</v>
       </c>
@@ -2822,8 +4901,12 @@
       <c r="G5" s="6">
         <v>2</v>
       </c>
-    </row>
-    <row r="6" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="H5">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C6" s="6" t="s">
         <v>105</v>
       </c>
@@ -2836,8 +4919,12 @@
       <c r="G6" s="6">
         <v>5</v>
       </c>
-    </row>
-    <row r="7" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="H6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C7" s="6" t="s">
         <v>106</v>
       </c>
@@ -2850,8 +4937,12 @@
       <c r="G7" s="6">
         <v>6</v>
       </c>
-    </row>
-    <row r="8" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="H7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C8" s="6" t="s">
         <v>107</v>
       </c>
@@ -2864,8 +4955,12 @@
       <c r="G8" s="6">
         <v>5</v>
       </c>
-    </row>
-    <row r="9" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="H8">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C9" s="6" t="s">
         <v>108</v>
       </c>
@@ -2878,8 +4973,12 @@
       <c r="G9" s="6">
         <v>8</v>
       </c>
-    </row>
-    <row r="10" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="H9">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C10" s="6"/>
       <c r="D10" s="6"/>
       <c r="F10" s="6" t="s">
@@ -2888,8 +4987,12 @@
       <c r="G10" s="6">
         <v>3</v>
       </c>
-    </row>
-    <row r="11" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="H10">
+        <f t="shared" si="0"/>
+        <v>-3</v>
+      </c>
+    </row>
+    <row r="11" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C11" s="6" t="s">
         <v>110</v>
       </c>
@@ -2902,8 +5005,12 @@
       <c r="G11" s="6">
         <v>5</v>
       </c>
-    </row>
-    <row r="12" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="H11">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C12" s="6" t="s">
         <v>111</v>
       </c>
@@ -2916,8 +5023,12 @@
       <c r="G12" s="6">
         <v>13</v>
       </c>
-    </row>
-    <row r="13" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="H12">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C13" s="6" t="s">
         <v>112</v>
       </c>
@@ -2930,32 +5041,42 @@
       <c r="G13" s="6">
         <v>4</v>
       </c>
-    </row>
-    <row r="14" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C14" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="D14" s="6">
-        <v>2</v>
-      </c>
+      <c r="H13">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="3:8" x14ac:dyDescent="0.25">
       <c r="F14" s="6" t="s">
         <v>113</v>
       </c>
       <c r="G14" s="6">
         <v>4</v>
       </c>
-    </row>
-    <row r="15" spans="3:7" x14ac:dyDescent="0.25">
-      <c r="C15" s="6"/>
-      <c r="D15" s="6"/>
+      <c r="H14">
+        <f>D15-G14</f>
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="15" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C15" s="6" t="s">
+        <v>114</v>
+      </c>
+      <c r="D15" s="6">
+        <v>2</v>
+      </c>
       <c r="F15" s="6" t="s">
         <v>114</v>
       </c>
       <c r="G15" s="6">
         <v>2</v>
       </c>
-    </row>
-    <row r="16" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="H15">
+        <f>D15-G15</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C16" s="6" t="s">
         <v>115</v>
       </c>
@@ -2968,8 +5089,12 @@
       <c r="G16" s="6">
         <v>38</v>
       </c>
-    </row>
-    <row r="17" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="H16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C17" s="6" t="s">
         <v>116</v>
       </c>
@@ -2982,8 +5107,12 @@
       <c r="G17" s="6">
         <v>13</v>
       </c>
-    </row>
-    <row r="18" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="H17">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C18" s="6" t="s">
         <v>117</v>
       </c>
@@ -2996,8 +5125,12 @@
       <c r="G18" s="6">
         <v>12</v>
       </c>
-    </row>
-    <row r="19" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="H18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C19" s="6" t="s">
         <v>118</v>
       </c>
@@ -3010,8 +5143,12 @@
       <c r="G19" s="6">
         <v>17</v>
       </c>
-    </row>
-    <row r="20" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="H19">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C20" s="6" t="s">
         <v>119</v>
       </c>
@@ -3024,8 +5161,12 @@
       <c r="G20" s="6">
         <v>22</v>
       </c>
-    </row>
-    <row r="21" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="H20">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C21" s="6" t="s">
         <v>120</v>
       </c>
@@ -3038,8 +5179,12 @@
       <c r="G21" s="6">
         <v>26</v>
       </c>
-    </row>
-    <row r="22" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="H21">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C22" s="6" t="s">
         <v>121</v>
       </c>
@@ -3052,8 +5197,12 @@
       <c r="G22" s="6">
         <v>23</v>
       </c>
-    </row>
-    <row r="23" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="H22">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C23" s="6" t="s">
         <v>122</v>
       </c>
@@ -3066,8 +5215,12 @@
       <c r="G23" s="6">
         <v>8</v>
       </c>
-    </row>
-    <row r="24" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="H23">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C24" s="6" t="s">
         <v>123</v>
       </c>
@@ -3080,8 +5233,12 @@
       <c r="G24" s="6">
         <v>10</v>
       </c>
-    </row>
-    <row r="25" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="H24">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C25" s="6" t="s">
         <v>124</v>
       </c>
@@ -3094,8 +5251,12 @@
       <c r="G25" s="6">
         <v>10</v>
       </c>
-    </row>
-    <row r="26" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="H25">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C26" s="6" t="s">
         <v>125</v>
       </c>
@@ -3108,8 +5269,12 @@
       <c r="G26" s="6">
         <v>36</v>
       </c>
-    </row>
-    <row r="27" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="H26">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C27" s="6"/>
       <c r="D27" s="6"/>
       <c r="F27" s="6" t="s">
@@ -3118,8 +5283,12 @@
       <c r="G27" s="6">
         <v>32</v>
       </c>
-    </row>
-    <row r="28" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="H27">
+        <f t="shared" si="0"/>
+        <v>-32</v>
+      </c>
+    </row>
+    <row r="28" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C28" s="6" t="s">
         <v>127</v>
       </c>
@@ -3132,8 +5301,12 @@
       <c r="G28" s="6">
         <v>16</v>
       </c>
-    </row>
-    <row r="29" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="H28">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C29" s="6" t="s">
         <v>128</v>
       </c>
@@ -3146,8 +5319,12 @@
       <c r="G29" s="6">
         <v>32</v>
       </c>
-    </row>
-    <row r="30" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="H29">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C30" s="6" t="s">
         <v>129</v>
       </c>
@@ -3160,8 +5337,12 @@
       <c r="G30" s="6">
         <v>8</v>
       </c>
-    </row>
-    <row r="31" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="H30">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C31" s="6" t="s">
         <v>130</v>
       </c>
@@ -3174,8 +5355,12 @@
       <c r="G31" s="6">
         <v>28</v>
       </c>
-    </row>
-    <row r="32" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="H31">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C32" s="6" t="s">
         <v>131</v>
       </c>
@@ -3188,8 +5373,12 @@
       <c r="G32" s="6">
         <v>23</v>
       </c>
-    </row>
-    <row r="33" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="H32">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C33" s="6" t="s">
         <v>132</v>
       </c>
@@ -3202,8 +5391,12 @@
       <c r="G33" s="6">
         <v>5</v>
       </c>
-    </row>
-    <row r="34" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="H33">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C34" s="6" t="s">
         <v>133</v>
       </c>
@@ -3216,8 +5409,12 @@
       <c r="G34" s="6">
         <v>12</v>
       </c>
-    </row>
-    <row r="35" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="H34">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C35" s="6" t="s">
         <v>134</v>
       </c>
@@ -3230,8 +5427,12 @@
       <c r="G35" s="6">
         <v>5</v>
       </c>
-    </row>
-    <row r="36" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="H35">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C36" s="6" t="s">
         <v>135</v>
       </c>
@@ -3244,8 +5445,12 @@
       <c r="G36" s="6">
         <v>5</v>
       </c>
-    </row>
-    <row r="37" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="H36">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C37" s="6" t="s">
         <v>136</v>
       </c>
@@ -3258,8 +5463,12 @@
       <c r="G37" s="6">
         <v>10</v>
       </c>
-    </row>
-    <row r="38" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="H37">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C38" s="6" t="s">
         <v>137</v>
       </c>
@@ -3272,8 +5481,12 @@
       <c r="G38" s="6">
         <v>5</v>
       </c>
-    </row>
-    <row r="39" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="H38">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C39" s="6" t="s">
         <v>138</v>
       </c>
@@ -3286,8 +5499,12 @@
       <c r="G39" s="6">
         <v>12</v>
       </c>
-    </row>
-    <row r="40" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="H39">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C40" s="6" t="s">
         <v>139</v>
       </c>
@@ -3300,8 +5517,12 @@
       <c r="G40" s="6">
         <v>34</v>
       </c>
-    </row>
-    <row r="41" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="H40">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C41" s="6" t="s">
         <v>140</v>
       </c>
@@ -3314,8 +5535,12 @@
       <c r="G41" s="6">
         <v>30</v>
       </c>
-    </row>
-    <row r="42" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="H41">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C42" s="6" t="s">
         <v>141</v>
       </c>
@@ -3328,8 +5553,12 @@
       <c r="G42" s="6">
         <v>4</v>
       </c>
-    </row>
-    <row r="43" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="H42">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C43" s="6" t="s">
         <v>142</v>
       </c>
@@ -3342,8 +5571,12 @@
       <c r="G43" s="6">
         <v>15</v>
       </c>
-    </row>
-    <row r="44" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="H43">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C44" s="6" t="s">
         <v>143</v>
       </c>
@@ -3356,8 +5589,12 @@
       <c r="G44" s="6">
         <v>8</v>
       </c>
-    </row>
-    <row r="45" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="H44">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C45" s="6" t="s">
         <v>144</v>
       </c>
@@ -3370,8 +5607,12 @@
       <c r="G45" s="6">
         <v>17</v>
       </c>
-    </row>
-    <row r="46" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="H45">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C46" s="6" t="s">
         <v>145</v>
       </c>
@@ -3384,8 +5625,12 @@
       <c r="G46" s="6">
         <v>3</v>
       </c>
-    </row>
-    <row r="47" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="H46">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C47" s="6" t="s">
         <v>146</v>
       </c>
@@ -3398,8 +5643,12 @@
       <c r="G47" s="6">
         <v>10</v>
       </c>
-    </row>
-    <row r="48" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="H47">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C48" s="6" t="s">
         <v>147</v>
       </c>
@@ -3412,8 +5661,12 @@
       <c r="G48" s="6">
         <v>6</v>
       </c>
-    </row>
-    <row r="49" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="H48">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C49" s="6" t="s">
         <v>148</v>
       </c>
@@ -3426,8 +5679,12 @@
       <c r="G49" s="6">
         <v>5</v>
       </c>
-    </row>
-    <row r="50" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="H49">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C50" s="6" t="s">
         <v>149</v>
       </c>
@@ -3440,8 +5697,12 @@
       <c r="G50" s="6">
         <v>7</v>
       </c>
-    </row>
-    <row r="51" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="H50">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C51" s="6" t="s">
         <v>150</v>
       </c>
@@ -3454,8 +5715,12 @@
       <c r="G51" s="6">
         <v>12</v>
       </c>
-    </row>
-    <row r="52" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="H51">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C52" s="6" t="s">
         <v>151</v>
       </c>
@@ -3468,8 +5733,12 @@
       <c r="G52" s="6">
         <v>10</v>
       </c>
-    </row>
-    <row r="53" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="H52">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C53" s="6" t="s">
         <v>152</v>
       </c>
@@ -3482,8 +5751,12 @@
       <c r="G53" s="6">
         <v>1</v>
       </c>
-    </row>
-    <row r="54" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="H53">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C54" s="6" t="s">
         <v>153</v>
       </c>
@@ -3496,8 +5769,12 @@
       <c r="G54" s="6">
         <v>4</v>
       </c>
-    </row>
-    <row r="55" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="H54">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C55" s="6" t="s">
         <v>154</v>
       </c>
@@ -3510,8 +5787,12 @@
       <c r="G55" s="6">
         <v>3</v>
       </c>
-    </row>
-    <row r="56" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="H55">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C56" s="6" t="s">
         <v>155</v>
       </c>
@@ -3524,8 +5805,12 @@
       <c r="G56" s="6">
         <v>10</v>
       </c>
-    </row>
-    <row r="57" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="H56">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C57" s="6" t="s">
         <v>156</v>
       </c>
@@ -3538,8 +5823,12 @@
       <c r="G57" s="6">
         <v>10</v>
       </c>
-    </row>
-    <row r="58" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="H57">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C58" s="6" t="s">
         <v>157</v>
       </c>
@@ -3552,8 +5841,12 @@
       <c r="G58" s="6">
         <v>42</v>
       </c>
-    </row>
-    <row r="59" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="H58">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C59" s="6" t="s">
         <v>158</v>
       </c>
@@ -3566,8 +5859,12 @@
       <c r="G59" s="6">
         <v>7</v>
       </c>
-    </row>
-    <row r="60" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="H59">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C60" s="6" t="s">
         <v>159</v>
       </c>
@@ -3580,8 +5877,12 @@
       <c r="G60" s="6">
         <v>10</v>
       </c>
-    </row>
-    <row r="61" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="H60">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C61" s="6" t="s">
         <v>160</v>
       </c>
@@ -3594,8 +5895,12 @@
       <c r="G61" s="6">
         <v>9</v>
       </c>
-    </row>
-    <row r="62" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="H61">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C62" s="6" t="s">
         <v>161</v>
       </c>
@@ -3608,8 +5913,12 @@
       <c r="G62" s="6">
         <v>10</v>
       </c>
-    </row>
-    <row r="63" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="H62">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C63" s="6" t="s">
         <v>162</v>
       </c>
@@ -3622,8 +5931,12 @@
       <c r="G63" s="6">
         <v>9</v>
       </c>
-    </row>
-    <row r="64" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="H63">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C64" s="6" t="s">
         <v>163</v>
       </c>
@@ -3636,8 +5949,12 @@
       <c r="G64" s="6">
         <v>11</v>
       </c>
-    </row>
-    <row r="65" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="H64">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C65" s="6" t="s">
         <v>164</v>
       </c>
@@ -3650,8 +5967,12 @@
       <c r="G65" s="6">
         <v>13</v>
       </c>
-    </row>
-    <row r="66" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="H65">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C66" s="6" t="s">
         <v>165</v>
       </c>
@@ -3664,8 +5985,12 @@
       <c r="G66" s="6">
         <v>20</v>
       </c>
-    </row>
-    <row r="67" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="H66">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C67" s="6" t="s">
         <v>166</v>
       </c>
@@ -3678,8 +6003,12 @@
       <c r="G67" s="6">
         <v>10</v>
       </c>
-    </row>
-    <row r="68" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="H67">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C68" s="6" t="s">
         <v>167</v>
       </c>
@@ -3692,8 +6021,12 @@
       <c r="G68" s="6">
         <v>10</v>
       </c>
-    </row>
-    <row r="69" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="H68">
+        <f t="shared" ref="H68:H87" si="1">D68-G68</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C69" s="6" t="s">
         <v>168</v>
       </c>
@@ -3706,8 +6039,12 @@
       <c r="G69" s="6">
         <v>3</v>
       </c>
-    </row>
-    <row r="70" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="H69">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C70" s="6" t="s">
         <v>169</v>
       </c>
@@ -3720,8 +6057,12 @@
       <c r="G70" s="6">
         <v>7</v>
       </c>
-    </row>
-    <row r="71" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="H70">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C71" s="6" t="s">
         <v>170</v>
       </c>
@@ -3734,8 +6075,12 @@
       <c r="G71" s="6">
         <v>8</v>
       </c>
-    </row>
-    <row r="72" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="H71">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C72" s="6" t="s">
         <v>171</v>
       </c>
@@ -3748,8 +6093,12 @@
       <c r="G72" s="6">
         <v>3</v>
       </c>
-    </row>
-    <row r="73" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="H72">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C73" s="6" t="s">
         <v>172</v>
       </c>
@@ -3762,8 +6111,12 @@
       <c r="G73" s="6">
         <v>2</v>
       </c>
-    </row>
-    <row r="74" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="H73">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C74" s="6" t="s">
         <v>173</v>
       </c>
@@ -3776,8 +6129,12 @@
       <c r="G74" s="6">
         <v>7</v>
       </c>
-    </row>
-    <row r="75" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="H74">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C75" s="6" t="s">
         <v>174</v>
       </c>
@@ -3790,8 +6147,12 @@
       <c r="G75" s="6">
         <v>5</v>
       </c>
-    </row>
-    <row r="76" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="H75">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C76" s="6" t="s">
         <v>175</v>
       </c>
@@ -3804,8 +6165,12 @@
       <c r="G76" s="6">
         <v>5</v>
       </c>
-    </row>
-    <row r="77" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="H76">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C77" s="6" t="s">
         <v>176</v>
       </c>
@@ -3818,8 +6183,12 @@
       <c r="G77" s="6">
         <v>21</v>
       </c>
-    </row>
-    <row r="78" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="H77">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C78" s="6" t="s">
         <v>177</v>
       </c>
@@ -3832,8 +6201,12 @@
       <c r="G78" s="6">
         <v>19</v>
       </c>
-    </row>
-    <row r="79" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="H78">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C79" s="6" t="s">
         <v>178</v>
       </c>
@@ -3846,24 +6219,36 @@
       <c r="G79" s="6">
         <v>21</v>
       </c>
-    </row>
-    <row r="80" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="H79">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="3:8" x14ac:dyDescent="0.25">
       <c r="F80" s="6" t="s">
         <v>179</v>
       </c>
       <c r="G80" s="6">
         <v>21</v>
       </c>
-    </row>
-    <row r="81" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="H80">
+        <f t="shared" si="1"/>
+        <v>-21</v>
+      </c>
+    </row>
+    <row r="81" spans="3:8" x14ac:dyDescent="0.25">
       <c r="F81" s="6" t="s">
         <v>180</v>
       </c>
       <c r="G81" s="6">
         <v>19</v>
       </c>
-    </row>
-    <row r="82" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="H81">
+        <f t="shared" si="1"/>
+        <v>-19</v>
+      </c>
+    </row>
+    <row r="82" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C82" s="6" t="s">
         <v>181</v>
       </c>
@@ -3876,16 +6261,24 @@
       <c r="G82" s="6">
         <v>19</v>
       </c>
-    </row>
-    <row r="83" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="H82">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="3:8" x14ac:dyDescent="0.25">
       <c r="F83" s="6" t="s">
         <v>182</v>
       </c>
       <c r="G83" s="6">
         <v>19</v>
       </c>
-    </row>
-    <row r="84" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="H83">
+        <f t="shared" si="1"/>
+        <v>-19</v>
+      </c>
+    </row>
+    <row r="84" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C84" s="6" t="s">
         <v>183</v>
       </c>
@@ -3898,8 +6291,12 @@
       <c r="G84" s="6">
         <v>3</v>
       </c>
-    </row>
-    <row r="85" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="H84">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C85" s="6" t="s">
         <v>184</v>
       </c>
@@ -3912,8 +6309,12 @@
       <c r="G85" s="6">
         <v>6</v>
       </c>
-    </row>
-    <row r="86" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="H85">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C86" s="6" t="s">
         <v>185</v>
       </c>
@@ -3926,8 +6327,12 @@
       <c r="G86" s="6">
         <v>18</v>
       </c>
-    </row>
-    <row r="87" spans="3:7" x14ac:dyDescent="0.25">
+      <c r="H86">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C87" s="6" t="s">
         <v>186</v>
       </c>
@@ -3939,6 +6344,10 @@
       </c>
       <c r="G87" s="6">
         <v>18</v>
+      </c>
+      <c r="H87">
+        <f t="shared" si="1"/>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/OPNT Docs/ToDoList.xlsx
+++ b/OPNT Docs/ToDoList.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\AST\GitHub\opnt\OPNT Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B07D5319-2B9D-44C9-8D5F-EFF614FEF96D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEE9D5B3-13AD-4288-949E-5B8C4EBD2FA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{C4C29C9D-7A78-44C9-A11D-2D7769206FE1}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{C4C29C9D-7A78-44C9-A11D-2D7769206FE1}"/>
   </bookViews>
   <sheets>
     <sheet name="PROC COMPARE (2)" sheetId="10" r:id="rId1"/>
@@ -43,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="528" uniqueCount="207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="548" uniqueCount="216">
   <si>
     <t>OPINITO TO DO LIST</t>
   </si>
@@ -669,6 +669,33 @@
   </si>
   <si>
     <t>done</t>
+  </si>
+  <si>
+    <t>273588fd-27bc-11ef-91a5-02ffc6c8051d</t>
+  </si>
+  <si>
+    <t>CountryCode</t>
+  </si>
+  <si>
+    <t>opntnewuser@gmail.com</t>
+  </si>
+  <si>
+    <t>2dbc1a5d-9b39-11ef-a597-02ffc6c8051d</t>
+  </si>
+  <si>
+    <t>showDialog</t>
+  </si>
+  <si>
+    <t>b720e82f-9d8d-11ef-a597-02ffc6c8051d</t>
+  </si>
+  <si>
+    <t>CopyCart</t>
+  </si>
+  <si>
+    <t>5ac3f470-abd5-11ef-a597-02ffc6c8051d</t>
+  </si>
+  <si>
+    <t>ProfileNav</t>
   </si>
 </sst>
 </file>
@@ -731,7 +758,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -772,13 +799,6 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1220,17 +1240,16 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G6" s="16"/>
-      <c r="H6" s="17" t="s">
+      <c r="H6" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="I6" s="17" t="s">
+      <c r="I6" s="6" t="s">
         <v>188</v>
       </c>
-      <c r="J6" s="18">
+      <c r="J6" s="7">
         <v>45603.922986111109</v>
       </c>
-      <c r="K6" s="17">
+      <c r="K6" s="6">
         <v>11380</v>
       </c>
       <c r="M6" s="6" t="s">
@@ -1257,17 +1276,16 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G7" s="16"/>
-      <c r="H7" s="17" t="s">
+      <c r="H7" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="I7" s="17" t="s">
+      <c r="I7" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="J7" s="18">
+      <c r="J7" s="7">
         <v>45572.001712962963</v>
       </c>
-      <c r="K7" s="17">
+      <c r="K7" s="6">
         <v>3963</v>
       </c>
       <c r="M7" s="6" t="s">
@@ -1294,17 +1312,16 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G8" s="16"/>
-      <c r="H8" s="17" t="s">
+      <c r="H8" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="I8" s="17" t="s">
+      <c r="I8" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="J8" s="18">
+      <c r="J8" s="7">
         <v>45555.870868055557</v>
       </c>
-      <c r="K8" s="17">
+      <c r="K8" s="6">
         <v>430</v>
       </c>
       <c r="M8" s="6" t="s">
@@ -1322,17 +1339,16 @@
         <f t="shared" si="0"/>
         <v>-1370</v>
       </c>
-      <c r="G9" s="16"/>
-      <c r="H9" s="17" t="s">
+      <c r="H9" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="I9" s="17" t="s">
+      <c r="I9" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="J9" s="18">
+      <c r="J9" s="7">
         <v>45568.769444444442</v>
       </c>
-      <c r="K9" s="17">
+      <c r="K9" s="6">
         <v>1370</v>
       </c>
       <c r="M9" s="6" t="s">
@@ -1362,17 +1378,16 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G10" s="16"/>
-      <c r="H10" s="17" t="s">
+      <c r="H10" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="I10" s="17" t="s">
+      <c r="I10" s="6" t="s">
         <v>192</v>
       </c>
-      <c r="J10" s="18">
+      <c r="J10" s="7">
         <v>45608.240393518521</v>
       </c>
-      <c r="K10" s="17">
+      <c r="K10" s="6">
         <v>7098</v>
       </c>
       <c r="M10" s="6" t="s">
@@ -1386,7 +1401,7 @@
       </c>
     </row>
     <row r="11" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B11" s="16" t="s">
+      <c r="B11" t="s">
         <v>206</v>
       </c>
       <c r="C11" s="6" t="s">
@@ -1402,15 +1417,13 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G11" s="16"/>
-      <c r="H11" s="16"/>
-      <c r="I11" s="17" t="s">
+      <c r="I11" s="6" t="s">
         <v>204</v>
       </c>
-      <c r="J11" s="18">
+      <c r="J11" s="7">
         <v>45608.240486111114</v>
       </c>
-      <c r="K11" s="17">
+      <c r="K11" s="6">
         <v>4570</v>
       </c>
       <c r="M11" s="6" t="s">
@@ -1424,7 +1437,7 @@
       </c>
     </row>
     <row r="12" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B12" s="16" t="s">
+      <c r="B12" t="s">
         <v>206</v>
       </c>
       <c r="C12" s="6" t="s">
@@ -1440,17 +1453,16 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G12" s="16"/>
-      <c r="H12" s="17" t="s">
+      <c r="H12" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="I12" s="17" t="s">
+      <c r="I12" s="6" t="s">
         <v>205</v>
       </c>
-      <c r="J12" s="18">
+      <c r="J12" s="7">
         <v>45602.928657407407</v>
       </c>
-      <c r="K12" s="17">
+      <c r="K12" s="6">
         <v>5451</v>
       </c>
       <c r="M12" s="6" t="s">
@@ -1468,7 +1480,6 @@
         <f t="shared" si="0"/>
         <v>-938</v>
       </c>
-      <c r="G13" s="16"/>
       <c r="H13" s="9" t="s">
         <v>34</v>
       </c>
@@ -1492,26 +1503,25 @@
       </c>
     </row>
     <row r="14" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="C14" s="17" t="s">
+      <c r="C14" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="D14" s="18">
+      <c r="D14" s="7">
         <v>45553.747881944444</v>
       </c>
-      <c r="E14" s="17">
+      <c r="E14" s="6">
         <v>1211</v>
       </c>
-      <c r="G14" s="16"/>
-      <c r="H14" s="17" t="s">
+      <c r="H14" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="I14" s="17" t="s">
+      <c r="I14" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="J14" s="18">
+      <c r="J14" s="7">
         <v>45553.747881944444</v>
       </c>
-      <c r="K14" s="17">
+      <c r="K14" s="6">
         <v>1211</v>
       </c>
     </row>
@@ -1520,17 +1530,16 @@
         <f t="shared" si="0"/>
         <v>-2192</v>
       </c>
-      <c r="G15" s="16"/>
-      <c r="H15" s="17" t="s">
+      <c r="H15" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="I15" s="17" t="s">
+      <c r="I15" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="J15" s="18">
+      <c r="J15" s="7">
         <v>45488.006921296299</v>
       </c>
-      <c r="K15" s="17">
+      <c r="K15" s="6">
         <v>2192</v>
       </c>
     </row>
@@ -1548,17 +1557,16 @@
         <f t="shared" si="0"/>
         <v>-150</v>
       </c>
-      <c r="G16" s="16"/>
-      <c r="H16" s="17" t="s">
+      <c r="H16" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="I16" s="17" t="s">
+      <c r="I16" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="J16" s="18">
+      <c r="J16" s="7">
         <v>45488.089548611111</v>
       </c>
-      <c r="K16" s="17">
+      <c r="K16" s="6">
         <v>2254</v>
       </c>
     </row>
@@ -1567,17 +1575,16 @@
         <f t="shared" si="0"/>
         <v>-1801</v>
       </c>
-      <c r="G17" s="16"/>
-      <c r="H17" s="17" t="s">
+      <c r="H17" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="I17" s="17" t="s">
+      <c r="I17" s="6" t="s">
         <v>189</v>
       </c>
-      <c r="J17" s="18">
+      <c r="J17" s="7">
         <v>45587.166886574072</v>
       </c>
-      <c r="K17" s="17">
+      <c r="K17" s="6">
         <v>1801</v>
       </c>
     </row>
@@ -1595,17 +1602,16 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G18" s="16"/>
-      <c r="H18" s="17" t="s">
+      <c r="H18" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="I18" s="17" t="s">
+      <c r="I18" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="J18" s="18">
+      <c r="J18" s="7">
         <v>45570.907997685186</v>
       </c>
-      <c r="K18" s="17">
+      <c r="K18" s="6">
         <v>1654</v>
       </c>
     </row>
@@ -1623,17 +1629,16 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G19" s="16"/>
-      <c r="H19" s="17" t="s">
+      <c r="H19" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="I19" s="17" t="s">
+      <c r="I19" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="J19" s="18">
+      <c r="J19" s="7">
         <v>45570.908067129632</v>
       </c>
-      <c r="K19" s="17">
+      <c r="K19" s="6">
         <v>1855</v>
       </c>
     </row>
@@ -1642,7 +1647,6 @@
         <f t="shared" si="0"/>
         <v>-686</v>
       </c>
-      <c r="G20" s="16"/>
       <c r="H20" s="8"/>
       <c r="I20" s="9" t="s">
         <v>53</v>
@@ -1668,15 +1672,13 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G21" s="16"/>
-      <c r="H21" s="16"/>
-      <c r="I21" s="17" t="s">
+      <c r="I21" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="J21" s="18">
+      <c r="J21" s="7">
         <v>45580.654513888891</v>
       </c>
-      <c r="K21" s="17">
+      <c r="K21" s="6">
         <v>9550</v>
       </c>
     </row>
@@ -1694,17 +1696,16 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G22" s="16"/>
-      <c r="H22" s="17" t="s">
+      <c r="H22" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="I22" s="17" t="s">
+      <c r="I22" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="J22" s="18">
+      <c r="J22" s="7">
         <v>45601.281597222223</v>
       </c>
-      <c r="K22" s="17">
+      <c r="K22" s="6">
         <v>6075</v>
       </c>
     </row>
@@ -1725,15 +1726,13 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G23" s="16"/>
-      <c r="H23" s="16"/>
-      <c r="I23" s="17" t="s">
+      <c r="I23" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="J23" s="18">
+      <c r="J23" s="7">
         <v>45562.222928240742</v>
       </c>
-      <c r="K23" s="17">
+      <c r="K23" s="6">
         <v>1633</v>
       </c>
     </row>
@@ -1751,17 +1750,16 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G24" s="16"/>
-      <c r="H24" s="17" t="s">
+      <c r="H24" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="I24" s="17" t="s">
+      <c r="I24" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="J24" s="18">
+      <c r="J24" s="7">
         <v>45583.714583333334</v>
       </c>
-      <c r="K24" s="17">
+      <c r="K24" s="6">
         <v>8304</v>
       </c>
     </row>
@@ -1779,15 +1777,13 @@
         <f t="shared" si="0"/>
         <v>-1</v>
       </c>
-      <c r="G25" s="16"/>
-      <c r="H25" s="16"/>
-      <c r="I25" s="17" t="s">
+      <c r="I25" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="J25" s="18">
+      <c r="J25" s="7">
         <v>45602.853148148148</v>
       </c>
-      <c r="K25" s="17">
+      <c r="K25" s="6">
         <v>9422</v>
       </c>
     </row>
@@ -1805,15 +1801,13 @@
         <f t="shared" si="0"/>
         <v>-2205</v>
       </c>
-      <c r="G26" s="16"/>
-      <c r="H26" s="16"/>
-      <c r="I26" s="17" t="s">
+      <c r="I26" s="6" t="s">
         <v>187</v>
       </c>
-      <c r="J26" s="18">
+      <c r="J26" s="7">
         <v>45587.921111111114</v>
       </c>
-      <c r="K26" s="17">
+      <c r="K26" s="6">
         <v>9421</v>
       </c>
     </row>
@@ -1831,17 +1825,16 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G27" s="16"/>
-      <c r="H27" s="17" t="s">
+      <c r="H27" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="I27" s="17" t="s">
+      <c r="I27" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="J27" s="18">
+      <c r="J27" s="7">
         <v>45582.831134259257</v>
       </c>
-      <c r="K27" s="17">
+      <c r="K27" s="6">
         <v>6691</v>
       </c>
     </row>
@@ -1859,17 +1852,16 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="G28" s="16"/>
-      <c r="H28" s="17" t="s">
+      <c r="H28" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="I28" s="17" t="s">
+      <c r="I28" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="J28" s="18">
+      <c r="J28" s="7">
         <v>45571.087962962964</v>
       </c>
-      <c r="K28" s="17">
+      <c r="K28" s="6">
         <v>4306</v>
       </c>
     </row>
@@ -2892,7 +2884,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BAEFE0D4-32B6-4E46-897F-75BA1FBDC9D0}">
-  <dimension ref="C3:I19"/>
+  <dimension ref="C3:I23"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="16.42578125" customWidth="1"/>
@@ -3292,6 +3284,98 @@
       </c>
       <c r="I19" s="11" t="s">
         <v>60</v>
+      </c>
+    </row>
+    <row r="20" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C20" s="6">
+        <v>1042834</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="F20" s="7">
+        <v>45454.27144675926</v>
+      </c>
+      <c r="G20" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="H20" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="I20" s="6" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="21" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C21" s="6">
+        <v>1050846</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>211</v>
+      </c>
+      <c r="F21" s="7">
+        <v>45601.239988425928</v>
+      </c>
+      <c r="G21" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="H21" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="I21" s="6" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="22" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C22" s="6">
+        <v>1051098</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>212</v>
+      </c>
+      <c r="E22" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="F22" s="7">
+        <v>45604.205393518518</v>
+      </c>
+      <c r="G22" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="H22" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="I22" s="6" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="23" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C23" s="6">
+        <v>1052020</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="E23" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="F23" s="7">
+        <v>45622.37767361111</v>
+      </c>
+      <c r="G23" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="H23" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="I23" s="6" t="s">
+        <v>209</v>
       </c>
     </row>
   </sheetData>
@@ -5250,7 +5334,7 @@
       </c>
     </row>
     <row r="11" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B11" s="16" t="s">
+      <c r="B11" t="s">
         <v>206</v>
       </c>
       <c r="C11" s="15"/>
@@ -5279,7 +5363,7 @@
       </c>
     </row>
     <row r="12" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B12" s="16" t="s">
+      <c r="B12" t="s">
         <v>206</v>
       </c>
       <c r="C12" s="15"/>

--- a/OPNT Docs/ToDoList.xlsx
+++ b/OPNT Docs/ToDoList.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\AST\GitHub\opnt\OPNT Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEE9D5B3-13AD-4288-949E-5B8C4EBD2FA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{74F3BFCC-2220-4B28-84F5-EFE466627D52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{C4C29C9D-7A78-44C9-A11D-2D7769206FE1}"/>
   </bookViews>
@@ -16,13 +16,15 @@
     <sheet name="PROC COMPARE (2)" sheetId="10" r:id="rId1"/>
     <sheet name="TO DO" sheetId="2" r:id="rId2"/>
     <sheet name="AST USERS" sheetId="6" r:id="rId3"/>
-    <sheet name="TRIGGERS" sheetId="8" r:id="rId4"/>
-    <sheet name="Sheet7" sheetId="9" r:id="rId5"/>
-    <sheet name="BOT_COUNT" sheetId="7" r:id="rId6"/>
-    <sheet name="PROC COMPARE" sheetId="4" r:id="rId7"/>
-    <sheet name="OBJECT COMPARE" sheetId="5" r:id="rId8"/>
+    <sheet name="BUGLIST" sheetId="11" r:id="rId4"/>
+    <sheet name="TRIGGERS" sheetId="8" r:id="rId5"/>
+    <sheet name="Sheet7" sheetId="9" r:id="rId6"/>
+    <sheet name="BOT_COUNT" sheetId="7" r:id="rId7"/>
+    <sheet name="PROC COMPARE" sheetId="4" r:id="rId8"/>
+    <sheet name="OBJECT COMPARE" sheetId="5" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -43,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="548" uniqueCount="216">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="580" uniqueCount="240">
   <si>
     <t>OPINITO TO DO LIST</t>
   </si>
@@ -696,6 +698,79 @@
   </si>
   <si>
     <t>ProfileNav</t>
+  </si>
+  <si>
+    <t>82a22cf1-ba5d-11ef-8133-02ffc6c8051d</t>
+  </si>
+  <si>
+    <t>MyOpinions</t>
+  </si>
+  <si>
+    <t>astopnt@gmail.com</t>
+  </si>
+  <si>
+    <t>f39a9c49-d1e7-11ef-8133-02ffc6c8051d</t>
+  </si>
+  <si>
+    <t>ASTOpinions</t>
+  </si>
+  <si>
+    <t>8150579c-d2ad-11ef-8133-02ffc6c8051d</t>
+  </si>
+  <si>
+    <t>ASTPolemics</t>
+  </si>
+  <si>
+    <t>NUM</t>
+  </si>
+  <si>
+    <t>APP</t>
+  </si>
+  <si>
+    <t>AREA</t>
+  </si>
+  <si>
+    <t>BUG DESCRIPTION AND STEPS</t>
+  </si>
+  <si>
+    <t>COMMENT - EXPECTED BEHAVIOR</t>
+  </si>
+  <si>
+    <t>STATUS</t>
+  </si>
+  <si>
+    <t>VERIF</t>
+  </si>
+  <si>
+    <t>PRIO</t>
+  </si>
+  <si>
+    <t>IOS</t>
+  </si>
+  <si>
+    <t>INTEREST MULTISELECT</t>
+  </si>
+  <si>
+    <t>When a new user is created, the multi-select of the interests just doesn't work - it doesn't select multi - stops working after selecting just one interest</t>
+  </si>
+  <si>
+    <t>Other App Bhv</t>
+  </si>
+  <si>
+    <t>works in Android</t>
+  </si>
+  <si>
+    <t>ios</t>
+  </si>
+  <si>
+    <t>showFreshContent - next step</t>
+  </si>
+  <si>
+    <t>When the SFC popup is shown I can select one or more l/h. This allows me to click 'DISCUSS' on any of the entries. If I complete my comment (so far things work well) - there is no place to go except the back button. And this back button still keeps the previously shown SFC and my selections - at this stage the user can do any changes - which will mess up the data integrity and app will be unusable if i unselect the l/h on which I commented.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The expectation is that once I click the 'discuss' after clicking l/h on one or more sfc entries, the app should SAVE all the selections. The back button should really take the user back to "discussions' screen - NOT show the SFC popup again.
+Or - the completion of the comment and save, should allow the user to go to discussions automatically - the back button causes problem in the SFC popup - it works fine when the comment is made from the Discussions screen origin. </t>
   </si>
 </sst>
 </file>
@@ -2884,7 +2959,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BAEFE0D4-32B6-4E46-897F-75BA1FBDC9D0}">
-  <dimension ref="C3:I23"/>
+  <dimension ref="C3:I26"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="16.42578125" customWidth="1"/>
@@ -3378,12 +3453,469 @@
         <v>209</v>
       </c>
     </row>
+    <row r="24" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C24" s="6">
+        <v>1052875</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>216</v>
+      </c>
+      <c r="E24" s="6" t="s">
+        <v>217</v>
+      </c>
+      <c r="F24" s="7">
+        <v>45640.870659722219</v>
+      </c>
+      <c r="G24" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="H24" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="I24" s="6" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="25" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C25" s="6">
+        <v>1053689</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>219</v>
+      </c>
+      <c r="E25" s="6" t="s">
+        <v>220</v>
+      </c>
+      <c r="F25" s="7">
+        <v>45670.828263888892</v>
+      </c>
+      <c r="G25" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="H25" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="I25" s="6" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="26" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C26" s="6">
+        <v>1053712</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>221</v>
+      </c>
+      <c r="E26" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="F26" s="7">
+        <v>45671.810312499998</v>
+      </c>
+      <c r="G26" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="H26" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="I26" s="6" t="s">
+        <v>218</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F112A336-CC77-4941-95EC-193C8E6A3B94}">
+  <dimension ref="B2:J32"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="3" width="11.42578125" customWidth="1"/>
+    <col min="4" max="4" width="25.85546875" customWidth="1"/>
+    <col min="5" max="5" width="52.42578125" customWidth="1"/>
+    <col min="6" max="6" width="46.85546875" customWidth="1"/>
+    <col min="7" max="7" width="18.7109375" customWidth="1"/>
+    <col min="8" max="8" width="11.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B2" t="s">
+        <v>223</v>
+      </c>
+      <c r="C2" t="s">
+        <v>224</v>
+      </c>
+      <c r="D2" t="s">
+        <v>225</v>
+      </c>
+      <c r="E2" t="s">
+        <v>226</v>
+      </c>
+      <c r="F2" t="s">
+        <v>227</v>
+      </c>
+      <c r="G2" t="s">
+        <v>234</v>
+      </c>
+      <c r="H2" t="s">
+        <v>230</v>
+      </c>
+      <c r="I2" t="s">
+        <v>228</v>
+      </c>
+      <c r="J2" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="4" spans="2:10" ht="45" x14ac:dyDescent="0.25">
+      <c r="B4" s="1">
+        <v>1</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>231</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="H4" s="1">
+        <v>1</v>
+      </c>
+      <c r="I4" s="1"/>
+      <c r="J4" s="1"/>
+    </row>
+    <row r="5" spans="2:10" ht="165" x14ac:dyDescent="0.25">
+      <c r="B5" s="1">
+        <v>2</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>239</v>
+      </c>
+      <c r="G5" s="1"/>
+      <c r="H5" s="1"/>
+      <c r="I5" s="1"/>
+      <c r="J5" s="1"/>
+    </row>
+    <row r="6" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B6" s="1"/>
+      <c r="C6" s="1"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
+      <c r="I6" s="1"/>
+      <c r="J6" s="1"/>
+    </row>
+    <row r="7" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B7" s="1"/>
+      <c r="C7" s="1"/>
+      <c r="D7" s="1"/>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1"/>
+      <c r="G7" s="1"/>
+      <c r="H7" s="1"/>
+      <c r="I7" s="1"/>
+      <c r="J7" s="1"/>
+    </row>
+    <row r="8" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B8" s="1"/>
+      <c r="C8" s="1"/>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1"/>
+      <c r="I8" s="1"/>
+      <c r="J8" s="1"/>
+    </row>
+    <row r="9" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B9" s="1"/>
+      <c r="C9" s="1"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1"/>
+      <c r="G9" s="1"/>
+      <c r="H9" s="1"/>
+      <c r="I9" s="1"/>
+      <c r="J9" s="1"/>
+    </row>
+    <row r="10" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B10" s="1"/>
+      <c r="C10" s="1"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
+      <c r="G10" s="1"/>
+      <c r="H10" s="1"/>
+      <c r="I10" s="1"/>
+      <c r="J10" s="1"/>
+    </row>
+    <row r="11" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B11" s="1"/>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+      <c r="G11" s="1"/>
+      <c r="H11" s="1"/>
+      <c r="I11" s="1"/>
+      <c r="J11" s="1"/>
+    </row>
+    <row r="12" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B12" s="1"/>
+      <c r="C12" s="1"/>
+      <c r="D12" s="1"/>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1"/>
+      <c r="G12" s="1"/>
+      <c r="H12" s="1"/>
+      <c r="I12" s="1"/>
+      <c r="J12" s="1"/>
+    </row>
+    <row r="13" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B13" s="1"/>
+      <c r="C13" s="1"/>
+      <c r="D13" s="1"/>
+      <c r="E13" s="1"/>
+      <c r="F13" s="1"/>
+      <c r="G13" s="1"/>
+      <c r="H13" s="1"/>
+      <c r="I13" s="1"/>
+      <c r="J13" s="1"/>
+    </row>
+    <row r="14" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B14" s="1"/>
+      <c r="C14" s="1"/>
+      <c r="D14" s="1"/>
+      <c r="E14" s="1"/>
+      <c r="F14" s="1"/>
+      <c r="G14" s="1"/>
+      <c r="H14" s="1"/>
+      <c r="I14" s="1"/>
+      <c r="J14" s="1"/>
+    </row>
+    <row r="15" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B15" s="1"/>
+      <c r="C15" s="1"/>
+      <c r="D15" s="1"/>
+      <c r="E15" s="1"/>
+      <c r="F15" s="1"/>
+      <c r="G15" s="1"/>
+      <c r="H15" s="1"/>
+      <c r="I15" s="1"/>
+      <c r="J15" s="1"/>
+    </row>
+    <row r="16" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B16" s="1"/>
+      <c r="C16" s="1"/>
+      <c r="D16" s="1"/>
+      <c r="E16" s="1"/>
+      <c r="F16" s="1"/>
+      <c r="G16" s="1"/>
+      <c r="H16" s="1"/>
+      <c r="I16" s="1"/>
+      <c r="J16" s="1"/>
+    </row>
+    <row r="17" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B17" s="1"/>
+      <c r="C17" s="1"/>
+      <c r="D17" s="1"/>
+      <c r="E17" s="1"/>
+      <c r="F17" s="1"/>
+      <c r="G17" s="1"/>
+      <c r="H17" s="1"/>
+      <c r="I17" s="1"/>
+      <c r="J17" s="1"/>
+    </row>
+    <row r="18" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B18" s="1"/>
+      <c r="C18" s="1"/>
+      <c r="D18" s="1"/>
+      <c r="E18" s="1"/>
+      <c r="F18" s="1"/>
+      <c r="G18" s="1"/>
+      <c r="H18" s="1"/>
+      <c r="I18" s="1"/>
+      <c r="J18" s="1"/>
+    </row>
+    <row r="19" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B19" s="1"/>
+      <c r="C19" s="1"/>
+      <c r="D19" s="1"/>
+      <c r="E19" s="1"/>
+      <c r="F19" s="1"/>
+      <c r="G19" s="1"/>
+      <c r="H19" s="1"/>
+      <c r="I19" s="1"/>
+      <c r="J19" s="1"/>
+    </row>
+    <row r="20" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B20" s="1"/>
+      <c r="C20" s="1"/>
+      <c r="D20" s="1"/>
+      <c r="E20" s="1"/>
+      <c r="F20" s="1"/>
+      <c r="G20" s="1"/>
+      <c r="H20" s="1"/>
+      <c r="I20" s="1"/>
+      <c r="J20" s="1"/>
+    </row>
+    <row r="21" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B21" s="1"/>
+      <c r="C21" s="1"/>
+      <c r="D21" s="1"/>
+      <c r="E21" s="1"/>
+      <c r="F21" s="1"/>
+      <c r="G21" s="1"/>
+      <c r="H21" s="1"/>
+      <c r="I21" s="1"/>
+      <c r="J21" s="1"/>
+    </row>
+    <row r="22" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B22" s="1"/>
+      <c r="C22" s="1"/>
+      <c r="D22" s="1"/>
+      <c r="E22" s="1"/>
+      <c r="F22" s="1"/>
+      <c r="G22" s="1"/>
+      <c r="H22" s="1"/>
+      <c r="I22" s="1"/>
+      <c r="J22" s="1"/>
+    </row>
+    <row r="23" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B23" s="1"/>
+      <c r="C23" s="1"/>
+      <c r="D23" s="1"/>
+      <c r="E23" s="1"/>
+      <c r="F23" s="1"/>
+      <c r="G23" s="1"/>
+      <c r="H23" s="1"/>
+      <c r="I23" s="1"/>
+      <c r="J23" s="1"/>
+    </row>
+    <row r="24" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B24" s="1"/>
+      <c r="C24" s="1"/>
+      <c r="D24" s="1"/>
+      <c r="E24" s="1"/>
+      <c r="F24" s="1"/>
+      <c r="G24" s="1"/>
+      <c r="H24" s="1"/>
+      <c r="I24" s="1"/>
+      <c r="J24" s="1"/>
+    </row>
+    <row r="25" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B25" s="1"/>
+      <c r="C25" s="1"/>
+      <c r="D25" s="1"/>
+      <c r="E25" s="1"/>
+      <c r="F25" s="1"/>
+      <c r="G25" s="1"/>
+      <c r="H25" s="1"/>
+      <c r="I25" s="1"/>
+      <c r="J25" s="1"/>
+    </row>
+    <row r="26" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B26" s="1"/>
+      <c r="C26" s="1"/>
+      <c r="D26" s="1"/>
+      <c r="E26" s="1"/>
+      <c r="F26" s="1"/>
+      <c r="G26" s="1"/>
+      <c r="H26" s="1"/>
+      <c r="I26" s="1"/>
+      <c r="J26" s="1"/>
+    </row>
+    <row r="27" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B27" s="1"/>
+      <c r="C27" s="1"/>
+      <c r="D27" s="1"/>
+      <c r="E27" s="1"/>
+      <c r="F27" s="1"/>
+      <c r="G27" s="1"/>
+      <c r="H27" s="1"/>
+      <c r="I27" s="1"/>
+      <c r="J27" s="1"/>
+    </row>
+    <row r="28" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B28" s="1"/>
+      <c r="C28" s="1"/>
+      <c r="D28" s="1"/>
+      <c r="E28" s="1"/>
+      <c r="F28" s="1"/>
+      <c r="G28" s="1"/>
+      <c r="H28" s="1"/>
+      <c r="I28" s="1"/>
+      <c r="J28" s="1"/>
+    </row>
+    <row r="29" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B29" s="1"/>
+      <c r="C29" s="1"/>
+      <c r="D29" s="1"/>
+      <c r="E29" s="1"/>
+      <c r="F29" s="1"/>
+      <c r="G29" s="1"/>
+      <c r="H29" s="1"/>
+      <c r="I29" s="1"/>
+      <c r="J29" s="1"/>
+    </row>
+    <row r="30" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B30" s="1"/>
+      <c r="C30" s="1"/>
+      <c r="D30" s="1"/>
+      <c r="E30" s="1"/>
+      <c r="F30" s="1"/>
+      <c r="G30" s="1"/>
+      <c r="H30" s="1"/>
+      <c r="I30" s="1"/>
+      <c r="J30" s="1"/>
+    </row>
+    <row r="31" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B31" s="1"/>
+      <c r="C31" s="1"/>
+      <c r="D31" s="1"/>
+      <c r="E31" s="1"/>
+      <c r="F31" s="1"/>
+      <c r="G31" s="1"/>
+      <c r="H31" s="1"/>
+      <c r="I31" s="1"/>
+      <c r="J31" s="1"/>
+    </row>
+    <row r="32" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B32" s="1"/>
+      <c r="C32" s="1"/>
+      <c r="D32" s="1"/>
+      <c r="E32" s="1"/>
+      <c r="F32" s="1"/>
+      <c r="G32" s="1"/>
+      <c r="H32" s="1"/>
+      <c r="I32" s="1"/>
+      <c r="J32" s="1"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{831397A3-B5B5-4502-B050-EC180F79243F}">
   <dimension ref="C2:H12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -3539,7 +4071,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{58AD8689-83A3-4231-B877-3E047206A588}">
   <dimension ref="C3:E94"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -4556,7 +5088,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C1D50FC-F6C6-4A8B-8B80-3E57F2ED5AA6}">
   <dimension ref="B2:J23"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -5093,7 +5625,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61765B45-3C92-4BC2-B87F-7B61C3132362}">
   <dimension ref="B2:O35"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -5183,7 +5715,7 @@
         <v>2104</v>
       </c>
     </row>
-    <row r="6" spans="2:15" ht="30" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:15" x14ac:dyDescent="0.25">
       <c r="C6" s="13" t="s">
         <v>188</v>
       </c>
@@ -5446,7 +5978,7 @@
         <v>2192</v>
       </c>
     </row>
-    <row r="16" spans="2:15" ht="30" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:15" x14ac:dyDescent="0.25">
       <c r="C16" s="6" t="s">
         <v>36</v>
       </c>
@@ -5651,7 +6183,7 @@
         <v>9422</v>
       </c>
     </row>
-    <row r="26" spans="2:11" ht="30" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:11" x14ac:dyDescent="0.25">
       <c r="C26" s="6" t="s">
         <v>187</v>
       </c>
@@ -5855,7 +6387,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5729499-E483-4C36-94CD-F33C4A49C2B8}">
   <dimension ref="C3:H87"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>

--- a/OPNT Docs/ToDoList.xlsx
+++ b/OPNT Docs/ToDoList.xlsx
@@ -1,30 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\AST\GitHub\opnt\OPNT Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{74F3BFCC-2220-4B28-84F5-EFE466627D52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D32FB3CD-7885-4819-BE33-D220A9C68C9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{C4C29C9D-7A78-44C9-A11D-2D7769206FE1}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="4" xr2:uid="{C4C29C9D-7A78-44C9-A11D-2D7769206FE1}"/>
   </bookViews>
   <sheets>
     <sheet name="PROC COMPARE (2)" sheetId="10" r:id="rId1"/>
     <sheet name="TO DO" sheetId="2" r:id="rId2"/>
     <sheet name="AST USERS" sheetId="6" r:id="rId3"/>
     <sheet name="BUGLIST" sheetId="11" r:id="rId4"/>
-    <sheet name="TRIGGERS" sheetId="8" r:id="rId5"/>
-    <sheet name="Sheet7" sheetId="9" r:id="rId6"/>
-    <sheet name="BOT_COUNT" sheetId="7" r:id="rId7"/>
-    <sheet name="PROC COMPARE" sheetId="4" r:id="rId8"/>
-    <sheet name="OBJECT COMPARE" sheetId="5" r:id="rId9"/>
+    <sheet name="NEWS_ONLY" sheetId="12" r:id="rId5"/>
+    <sheet name="TRIGGERS" sheetId="8" r:id="rId6"/>
+    <sheet name="MAINBOTS" sheetId="7" r:id="rId7"/>
+    <sheet name="OBJECT COMPARE" sheetId="5" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -45,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="580" uniqueCount="240">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="524" uniqueCount="298">
   <si>
     <t>OPINITO TO DO LIST</t>
   </si>
@@ -154,9 +152,6 @@
     <t>how to find the users instream and disc counts</t>
   </si>
   <si>
-    <t>PROCEDURE</t>
-  </si>
-  <si>
     <t>ADD_NUSERS_4K1</t>
   </si>
   <si>
@@ -193,18 +188,12 @@
     <t>delUserInterests</t>
   </si>
   <si>
-    <t>DIVTEST</t>
-  </si>
-  <si>
     <t>getUserInterests</t>
   </si>
   <si>
     <t>insertUserInterests</t>
   </si>
   <si>
-    <t>OPN_1_CART_CLEANUP</t>
-  </si>
-  <si>
     <t>reflectCartInterests</t>
   </si>
   <si>
@@ -226,12 +215,6 @@
     <t>STP_REMAINDER_NONXYZ</t>
   </si>
   <si>
-    <t>WSR_DEDUPE</t>
-  </si>
-  <si>
-    <t>WSR_DEDUPE_WSRL</t>
-  </si>
-  <si>
     <t>ast.commerce@gmail.com</t>
   </si>
   <si>
@@ -619,9 +602,6 @@
     <t>createBOTDiscussion</t>
   </si>
   <si>
-    <t>proctest</t>
-  </si>
-  <si>
     <t>userActionCommon</t>
   </si>
   <si>
@@ -668,9 +648,6 @@
   </si>
   <si>
     <t>getInstreamTrendingNW</t>
-  </si>
-  <si>
-    <t>done</t>
   </si>
   <si>
     <t>273588fd-27bc-11ef-91a5-02ffc6c8051d</t>
@@ -771,13 +748,208 @@
   <si>
     <t xml:space="preserve">The expectation is that once I click the 'discuss' after clicking l/h on one or more sfc entries, the app should SAVE all the selections. The back button should really take the user back to "discussions' screen - NOT show the SFC popup again.
 Or - the completion of the comment and save, should allow the user to go to discussions automatically - the back button causes problem in the SFC popup - it works fine when the comment is made from the Discussions screen origin. </t>
+  </si>
+  <si>
+    <t>createGoogleUserTokenApp</t>
+  </si>
+  <si>
+    <t>createGuestUserApp</t>
+  </si>
+  <si>
+    <t>createTCCDiscussion</t>
+  </si>
+  <si>
+    <t>insertCartDelQ</t>
+  </si>
+  <si>
+    <t>insertCartInsertQ</t>
+  </si>
+  <si>
+    <t>insertSFC</t>
+  </si>
+  <si>
+    <t>loadScrapes</t>
+  </si>
+  <si>
+    <t>callSTDbyTCC</t>
+  </si>
+  <si>
+    <t>showTCCContent</t>
+  </si>
+  <si>
+    <t>GGST1020628</t>
+  </si>
+  <si>
+    <t>ELITES</t>
+  </si>
+  <si>
+    <t>GGST1020656</t>
+  </si>
+  <si>
+    <t>REFORM</t>
+  </si>
+  <si>
+    <t>GGST1020657</t>
+  </si>
+  <si>
+    <t>TLRGUEST.1164</t>
+  </si>
+  <si>
+    <t>TLRGUEST.1206</t>
+  </si>
+  <si>
+    <t>TLRGUEST.1296</t>
+  </si>
+  <si>
+    <t>TLRGUEST.1338</t>
+  </si>
+  <si>
+    <t>TLRGUEST.1347</t>
+  </si>
+  <si>
+    <t>TLRGUEST.1349</t>
+  </si>
+  <si>
+    <t>TLRGUEST.1402</t>
+  </si>
+  <si>
+    <t>TLRGUEST.1495</t>
+  </si>
+  <si>
+    <t>TLRGUEST.1595</t>
+  </si>
+  <si>
+    <t>TLRGUEST.1599</t>
+  </si>
+  <si>
+    <t>TLRGUEST.1660</t>
+  </si>
+  <si>
+    <t>TLRGUEST.1680</t>
+  </si>
+  <si>
+    <t>TLRGUEST.1691</t>
+  </si>
+  <si>
+    <t>TLRGUEST.1785</t>
+  </si>
+  <si>
+    <t>TLRGUEST.1802</t>
+  </si>
+  <si>
+    <t>TLRGUEST.1870</t>
+  </si>
+  <si>
+    <t>TLRGUEST.1923</t>
+  </si>
+  <si>
+    <t>Bollywood news</t>
+  </si>
+  <si>
+    <t>CELEB</t>
+  </si>
+  <si>
+    <t>bollywoodnews10</t>
+  </si>
+  <si>
+    <t>Business News</t>
+  </si>
+  <si>
+    <t>BUSINESS</t>
+  </si>
+  <si>
+    <t>businessnews4</t>
+  </si>
+  <si>
+    <t>Celeb News</t>
+  </si>
+  <si>
+    <t>CELEBNEWS</t>
+  </si>
+  <si>
+    <t>Entertainment News</t>
+  </si>
+  <si>
+    <t>ENT</t>
+  </si>
+  <si>
+    <t>entertainmentnews5</t>
+  </si>
+  <si>
+    <t>Politics News</t>
+  </si>
+  <si>
+    <t>POLITICS</t>
+  </si>
+  <si>
+    <t>politicsnews1</t>
+  </si>
+  <si>
+    <t>Politics News (Left)</t>
+  </si>
+  <si>
+    <t>politicsnews(left)1</t>
+  </si>
+  <si>
+    <t>Politics News (Right)</t>
+  </si>
+  <si>
+    <t>politicsnews(right)1</t>
+  </si>
+  <si>
+    <t>Science News</t>
+  </si>
+  <si>
+    <t>SCIENCE</t>
+  </si>
+  <si>
+    <t>sciencenews3</t>
+  </si>
+  <si>
+    <t>Sports News</t>
+  </si>
+  <si>
+    <t>SPORTS</t>
+  </si>
+  <si>
+    <t>sportsnews2</t>
+  </si>
+  <si>
+    <t>Trending News</t>
+  </si>
+  <si>
+    <t>TREND</t>
+  </si>
+  <si>
+    <t>trendingnews9</t>
+  </si>
+  <si>
+    <t>KEYID</t>
+  </si>
+  <si>
+    <t>TOPICID</t>
+  </si>
+  <si>
+    <t>KEYWORDS</t>
+  </si>
+  <si>
+    <t>SCRAPE_TAG1</t>
+  </si>
+  <si>
+    <t>SCRAPE_TAG2</t>
+  </si>
+  <si>
+    <t>OCCODE</t>
+  </si>
+  <si>
+    <t>CCODE</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -785,25 +957,19 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="4">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.39997558519241921"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -833,7 +999,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -854,26 +1020,19 @@
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="22" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="22" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1208,7 +1367,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26322B8C-3462-41FC-A723-2D3481BF841F}">
-  <dimension ref="B2:O35"/>
+  <dimension ref="C2:O39"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="28.7109375" customWidth="1"/>
@@ -1224,14 +1383,14 @@
     <col min="14" max="14" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:15" x14ac:dyDescent="0.25">
+    <row r="2" spans="3:15" x14ac:dyDescent="0.25">
       <c r="C2" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="4" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="C4" s="6" t="s">
-        <v>35</v>
+        <v>43</v>
+      </c>
+    </row>
+    <row r="4" spans="3:15" x14ac:dyDescent="0.25">
+      <c r="C4" s="10" t="s">
+        <v>34</v>
       </c>
       <c r="D4" s="7">
         <v>45487.799317129633</v>
@@ -1239,25 +1398,22 @@
       <c r="E4" s="6">
         <v>3474</v>
       </c>
-      <c r="F4" s="6">
+      <c r="F4" s="6"/>
+      <c r="G4">
         <f>E4-K4</f>
         <v>0</v>
       </c>
-      <c r="H4" s="6" t="s">
+      <c r="H4" s="11"/>
+      <c r="I4" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="I4" s="6" t="s">
-        <v>35</v>
-      </c>
       <c r="J4" s="7">
-        <v>45487.7969212963</v>
+        <v>45487.799317129633</v>
       </c>
       <c r="K4" s="6">
         <v>3474</v>
       </c>
-      <c r="M4" s="6" t="s">
-        <v>35</v>
-      </c>
+      <c r="M4" s="6"/>
       <c r="N4" s="7">
         <v>45487.799317129633</v>
       </c>
@@ -1265,35 +1421,23 @@
         <v>3474</v>
       </c>
     </row>
-    <row r="5" spans="2:15" ht="30" x14ac:dyDescent="0.25">
-      <c r="C5" s="6" t="s">
-        <v>203</v>
-      </c>
-      <c r="D5" s="7">
-        <v>45603.933032407411</v>
-      </c>
-      <c r="E5" s="6">
-        <v>7271</v>
-      </c>
-      <c r="F5" s="6">
-        <f t="shared" ref="F5:F34" si="0">E5-K5</f>
-        <v>0</v>
-      </c>
-      <c r="H5" s="6" t="s">
-        <v>34</v>
-      </c>
+    <row r="5" spans="3:15" x14ac:dyDescent="0.25">
+      <c r="F5" s="6"/>
+      <c r="G5">
+        <f t="shared" ref="G5:G39" si="0">E5-K5</f>
+        <v>-1267</v>
+      </c>
+      <c r="H5" s="11"/>
       <c r="I5" s="6" t="s">
-        <v>203</v>
+        <v>240</v>
       </c>
       <c r="J5" s="7">
-        <v>45603.932650462964</v>
+        <v>45720.899895833332</v>
       </c>
       <c r="K5" s="6">
-        <v>7271</v>
-      </c>
-      <c r="M5" s="6" t="s">
-        <v>36</v>
-      </c>
+        <v>1267</v>
+      </c>
+      <c r="M5" s="6"/>
       <c r="N5" s="7">
         <v>45488.204421296294</v>
       </c>
@@ -1301,35 +1445,32 @@
         <v>2104</v>
       </c>
     </row>
-    <row r="6" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="C6" s="6" t="s">
-        <v>188</v>
+    <row r="6" spans="3:15" x14ac:dyDescent="0.25">
+      <c r="C6" s="10" t="s">
+        <v>197</v>
       </c>
       <c r="D6" s="7">
-        <v>45611.902060185188</v>
+        <v>45603.933032407411</v>
       </c>
       <c r="E6" s="6">
-        <v>11380</v>
-      </c>
-      <c r="F6" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H6" s="6" t="s">
-        <v>34</v>
-      </c>
+        <v>7271</v>
+      </c>
+      <c r="F6" s="6"/>
+      <c r="G6">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H6" s="11"/>
       <c r="I6" s="6" t="s">
-        <v>188</v>
+        <v>197</v>
       </c>
       <c r="J6" s="7">
-        <v>45603.922986111109</v>
+        <v>45603.933032407411</v>
       </c>
       <c r="K6" s="6">
-        <v>11380</v>
-      </c>
-      <c r="M6" s="6" t="s">
-        <v>37</v>
-      </c>
+        <v>7271</v>
+      </c>
+      <c r="M6" s="6"/>
       <c r="N6" s="7">
         <v>45580.246689814812</v>
       </c>
@@ -1337,35 +1478,32 @@
         <v>9550</v>
       </c>
     </row>
-    <row r="7" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="C7" s="6" t="s">
-        <v>45</v>
+    <row r="7" spans="3:15" x14ac:dyDescent="0.25">
+      <c r="C7" s="10" t="s">
+        <v>183</v>
       </c>
       <c r="D7" s="7">
-        <v>45611.920717592591</v>
+        <v>45613.034363425926</v>
       </c>
       <c r="E7" s="6">
-        <v>3963</v>
-      </c>
-      <c r="F7" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H7" s="6" t="s">
-        <v>34</v>
-      </c>
+        <v>11381</v>
+      </c>
+      <c r="F7" s="6"/>
+      <c r="G7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H7" s="11"/>
       <c r="I7" s="6" t="s">
-        <v>45</v>
+        <v>183</v>
       </c>
       <c r="J7" s="7">
-        <v>45572.001712962963</v>
+        <v>45613.034363425926</v>
       </c>
       <c r="K7" s="6">
-        <v>3963</v>
-      </c>
-      <c r="M7" s="6" t="s">
-        <v>38</v>
-      </c>
+        <v>11381</v>
+      </c>
+      <c r="M7" s="6"/>
       <c r="N7" s="7">
         <v>45559.065092592595</v>
       </c>
@@ -1373,35 +1511,32 @@
         <v>11083</v>
       </c>
     </row>
-    <row r="8" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="C8" s="6" t="s">
-        <v>46</v>
+    <row r="8" spans="3:15" x14ac:dyDescent="0.25">
+      <c r="C8" s="10" t="s">
+        <v>233</v>
       </c>
       <c r="D8" s="7">
-        <v>45611.923206018517</v>
+        <v>45680.928414351853</v>
       </c>
       <c r="E8" s="6">
-        <v>430</v>
-      </c>
-      <c r="F8" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H8" s="6" t="s">
-        <v>34</v>
-      </c>
+        <v>3445</v>
+      </c>
+      <c r="F8" s="6"/>
+      <c r="G8">
+        <f t="shared" si="0"/>
+        <v>305</v>
+      </c>
+      <c r="H8" s="11"/>
       <c r="I8" s="6" t="s">
-        <v>46</v>
+        <v>233</v>
       </c>
       <c r="J8" s="7">
-        <v>45555.870868055557</v>
+        <v>45671.798101851855</v>
       </c>
       <c r="K8" s="6">
-        <v>430</v>
-      </c>
-      <c r="M8" s="6" t="s">
-        <v>187</v>
-      </c>
+        <v>3140</v>
+      </c>
+      <c r="M8" s="6"/>
       <c r="N8" s="7">
         <v>45585.078321759262</v>
       </c>
@@ -1409,26 +1544,32 @@
         <v>7216</v>
       </c>
     </row>
-    <row r="9" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="F9" s="6">
-        <f t="shared" si="0"/>
-        <v>-1370</v>
-      </c>
-      <c r="H9" s="6" t="s">
-        <v>34</v>
-      </c>
+    <row r="9" spans="3:15" x14ac:dyDescent="0.25">
+      <c r="C9" s="10" t="s">
+        <v>234</v>
+      </c>
+      <c r="D9" s="7">
+        <v>45680.932337962964</v>
+      </c>
+      <c r="E9" s="6">
+        <v>6546</v>
+      </c>
+      <c r="F9" s="6"/>
+      <c r="G9">
+        <f t="shared" si="0"/>
+        <v>126</v>
+      </c>
+      <c r="H9" s="11"/>
       <c r="I9" s="6" t="s">
-        <v>47</v>
+        <v>234</v>
       </c>
       <c r="J9" s="7">
-        <v>45568.769444444442</v>
+        <v>45671.798946759256</v>
       </c>
       <c r="K9" s="6">
-        <v>1370</v>
-      </c>
-      <c r="M9" s="6" t="s">
-        <v>39</v>
-      </c>
+        <v>6420</v>
+      </c>
+      <c r="M9" s="6"/>
       <c r="N9" s="7">
         <v>45585.078958333332</v>
       </c>
@@ -1436,38 +1577,32 @@
         <v>6691</v>
       </c>
     </row>
-    <row r="10" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B10" t="s">
-        <v>206</v>
-      </c>
-      <c r="C10" s="6" t="s">
-        <v>192</v>
+    <row r="10" spans="3:15" x14ac:dyDescent="0.25">
+      <c r="C10" s="10" t="s">
+        <v>44</v>
       </c>
       <c r="D10" s="7">
-        <v>45611.893055555556</v>
+        <v>45611.920717592591</v>
       </c>
       <c r="E10" s="6">
-        <v>7098</v>
-      </c>
-      <c r="F10" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H10" s="6" t="s">
-        <v>34</v>
-      </c>
+        <v>3963</v>
+      </c>
+      <c r="F10" s="6"/>
+      <c r="G10">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H10" s="11"/>
       <c r="I10" s="6" t="s">
-        <v>192</v>
+        <v>44</v>
       </c>
       <c r="J10" s="7">
-        <v>45608.240393518521</v>
+        <v>45611.920717592591</v>
       </c>
       <c r="K10" s="6">
-        <v>7098</v>
-      </c>
-      <c r="M10" s="6" t="s">
-        <v>40</v>
-      </c>
+        <v>3963</v>
+      </c>
+      <c r="M10" s="6"/>
       <c r="N10" s="7">
         <v>45559.059641203705</v>
       </c>
@@ -1475,35 +1610,32 @@
         <v>3838</v>
       </c>
     </row>
-    <row r="11" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B11" t="s">
-        <v>206</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>204</v>
+    <row r="11" spans="3:15" x14ac:dyDescent="0.25">
+      <c r="C11" s="10" t="s">
+        <v>235</v>
       </c>
       <c r="D11" s="7">
-        <v>45611.890706018516</v>
+        <v>45716.741701388892</v>
       </c>
       <c r="E11" s="6">
-        <v>4570</v>
-      </c>
-      <c r="F11" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
+        <v>6525</v>
+      </c>
+      <c r="F11" s="6"/>
+      <c r="G11">
+        <f t="shared" si="0"/>
+        <v>-202</v>
+      </c>
+      <c r="H11" s="12"/>
       <c r="I11" s="6" t="s">
-        <v>204</v>
+        <v>235</v>
       </c>
       <c r="J11" s="7">
-        <v>45608.240486111114</v>
+        <v>45720.87972222222</v>
       </c>
       <c r="K11" s="6">
-        <v>4570</v>
-      </c>
-      <c r="M11" s="6" t="s">
-        <v>41</v>
-      </c>
+        <v>6727</v>
+      </c>
+      <c r="M11" s="6"/>
       <c r="N11" s="7">
         <v>45564.562025462961</v>
       </c>
@@ -1511,38 +1643,32 @@
         <v>2780</v>
       </c>
     </row>
-    <row r="12" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B12" t="s">
-        <v>206</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>205</v>
+    <row r="12" spans="3:15" x14ac:dyDescent="0.25">
+      <c r="C12" s="10" t="s">
+        <v>45</v>
       </c>
       <c r="D12" s="7">
-        <v>45611.894548611112</v>
+        <v>45611.923206018517</v>
       </c>
       <c r="E12" s="6">
-        <v>5451</v>
-      </c>
-      <c r="F12" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H12" s="6" t="s">
-        <v>34</v>
-      </c>
+        <v>430</v>
+      </c>
+      <c r="F12" s="6"/>
+      <c r="G12">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H12" s="11"/>
       <c r="I12" s="6" t="s">
-        <v>205</v>
+        <v>45</v>
       </c>
       <c r="J12" s="7">
-        <v>45602.928657407407</v>
+        <v>45611.923206018517</v>
       </c>
       <c r="K12" s="6">
-        <v>5451</v>
-      </c>
-      <c r="M12" s="6" t="s">
-        <v>42</v>
-      </c>
+        <v>430</v>
+      </c>
+      <c r="M12" s="6"/>
       <c r="N12" s="7">
         <v>45583.870821759258</v>
       </c>
@@ -1550,26 +1676,32 @@
         <v>2146</v>
       </c>
     </row>
-    <row r="13" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="F13" s="6">
-        <f t="shared" si="0"/>
-        <v>-938</v>
-      </c>
-      <c r="H13" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="I13" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="J13" s="10">
-        <v>45562.205208333333</v>
-      </c>
-      <c r="K13" s="9">
-        <v>938</v>
-      </c>
-      <c r="M13" s="6" t="s">
-        <v>43</v>
-      </c>
+    <row r="13" spans="3:15" x14ac:dyDescent="0.25">
+      <c r="C13" s="10" t="s">
+        <v>186</v>
+      </c>
+      <c r="D13" s="7">
+        <v>45611.893055555556</v>
+      </c>
+      <c r="E13" s="6">
+        <v>7098</v>
+      </c>
+      <c r="F13" s="6"/>
+      <c r="G13">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H13" s="11"/>
+      <c r="I13" s="6" t="s">
+        <v>186</v>
+      </c>
+      <c r="J13" s="7">
+        <v>45611.893055555556</v>
+      </c>
+      <c r="K13" s="6">
+        <v>7098</v>
+      </c>
+      <c r="M13" s="6"/>
       <c r="N13" s="7">
         <v>45564.561944444446</v>
       </c>
@@ -1577,528 +1709,657 @@
         <v>2756</v>
       </c>
     </row>
-    <row r="14" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="C14" s="6" t="s">
+    <row r="14" spans="3:15" x14ac:dyDescent="0.25">
+      <c r="C14" s="10" t="s">
+        <v>198</v>
+      </c>
+      <c r="D14" s="7">
+        <v>45611.890706018516</v>
+      </c>
+      <c r="E14" s="6">
+        <v>4570</v>
+      </c>
+      <c r="G14">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H14" s="11"/>
+      <c r="I14" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="J14" s="7">
+        <v>45611.890706018516</v>
+      </c>
+      <c r="K14" s="6">
+        <v>4570</v>
+      </c>
+    </row>
+    <row r="15" spans="3:15" x14ac:dyDescent="0.25">
+      <c r="C15" s="10" t="s">
+        <v>199</v>
+      </c>
+      <c r="D15" s="7">
+        <v>45611.894548611112</v>
+      </c>
+      <c r="E15" s="6">
+        <v>5451</v>
+      </c>
+      <c r="F15" s="6"/>
+      <c r="G15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H15" s="11"/>
+      <c r="I15" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="J15" s="7">
+        <v>45611.894548611112</v>
+      </c>
+      <c r="K15" s="6">
+        <v>5451</v>
+      </c>
+    </row>
+    <row r="16" spans="3:15" x14ac:dyDescent="0.25">
+      <c r="C16" s="10" t="s">
+        <v>46</v>
+      </c>
+      <c r="D16" s="7">
+        <v>45617.285960648151</v>
+      </c>
+      <c r="E16" s="6">
+        <v>938</v>
+      </c>
+      <c r="F16" s="6"/>
+      <c r="G16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H16" s="11"/>
+      <c r="I16" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="J16" s="7">
+        <v>45617.285960648151</v>
+      </c>
+      <c r="K16" s="6">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="17" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C17" s="10" t="s">
+        <v>236</v>
+      </c>
+      <c r="D17" s="7">
+        <v>45653.232268518521</v>
+      </c>
+      <c r="E17" s="6">
+        <v>1459</v>
+      </c>
+      <c r="F17" s="6"/>
+      <c r="G17">
+        <f t="shared" si="0"/>
+        <v>-114</v>
+      </c>
+      <c r="H17" s="11"/>
+      <c r="I17" s="6" t="s">
+        <v>236</v>
+      </c>
+      <c r="J17" s="7">
+        <v>45687.014085648145</v>
+      </c>
+      <c r="K17" s="6">
+        <v>1573</v>
+      </c>
+    </row>
+    <row r="18" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C18" s="10" t="s">
+        <v>237</v>
+      </c>
+      <c r="D18" s="7">
+        <v>45654.888842592591</v>
+      </c>
+      <c r="E18" s="6">
+        <v>2334</v>
+      </c>
+      <c r="F18" s="6"/>
+      <c r="G18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H18" s="11"/>
+      <c r="I18" s="6" t="s">
+        <v>237</v>
+      </c>
+      <c r="J18" s="7">
+        <v>45654.888842592591</v>
+      </c>
+      <c r="K18" s="6">
+        <v>2334</v>
+      </c>
+    </row>
+    <row r="19" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C19" s="10" t="s">
+        <v>238</v>
+      </c>
+      <c r="D19" s="7">
+        <v>45687.001134259262</v>
+      </c>
+      <c r="E19" s="6">
+        <v>1973</v>
+      </c>
+      <c r="F19" s="6"/>
+      <c r="G19">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H19" s="11"/>
+      <c r="I19" s="6" t="s">
+        <v>238</v>
+      </c>
+      <c r="J19" s="7">
+        <v>45686.941863425927</v>
+      </c>
+      <c r="K19" s="6">
+        <v>1973</v>
+      </c>
+    </row>
+    <row r="20" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C20" s="10" t="s">
+        <v>47</v>
+      </c>
+      <c r="D20" s="7">
+        <v>45650.162094907406</v>
+      </c>
+      <c r="E20" s="6">
+        <v>1482</v>
+      </c>
+      <c r="F20" s="6"/>
+      <c r="G20">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H20" s="12"/>
+      <c r="I20" s="6" t="s">
+        <v>47</v>
+      </c>
+      <c r="J20" s="7">
+        <v>45650.162094907406</v>
+      </c>
+      <c r="K20" s="6">
+        <v>1482</v>
+      </c>
+    </row>
+    <row r="21" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C21" s="10" t="s">
+        <v>239</v>
+      </c>
+      <c r="D21" s="7">
+        <v>45669.216539351852</v>
+      </c>
+      <c r="E21" s="6">
+        <v>1663</v>
+      </c>
+      <c r="F21" s="6"/>
+      <c r="G21">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H21" s="12"/>
+      <c r="I21" s="6" t="s">
+        <v>239</v>
+      </c>
+      <c r="J21" s="7">
+        <v>45669.216539351852</v>
+      </c>
+      <c r="K21" s="6">
+        <v>1663</v>
+      </c>
+    </row>
+    <row r="22" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C22" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="D22" s="7">
+        <v>45488.204421296294</v>
+      </c>
+      <c r="E22" s="6">
+        <v>2104</v>
+      </c>
+      <c r="F22" s="6"/>
+      <c r="G22">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H22" s="11"/>
+      <c r="I22" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="J22" s="7">
+        <v>45488.204421296294</v>
+      </c>
+      <c r="K22" s="6">
+        <v>2104</v>
+      </c>
+    </row>
+    <row r="23" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C23" s="10" t="s">
+        <v>48</v>
+      </c>
+      <c r="D23" s="7">
+        <v>45680.90152777778</v>
+      </c>
+      <c r="E23" s="6">
+        <v>1924</v>
+      </c>
+      <c r="F23" s="6"/>
+      <c r="G23">
+        <f t="shared" si="0"/>
+        <v>270</v>
+      </c>
+      <c r="H23" s="12"/>
+      <c r="I23" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="J23" s="7">
+        <v>45598.704918981479</v>
+      </c>
+      <c r="K23" s="6">
+        <v>1654</v>
+      </c>
+    </row>
+    <row r="24" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C24" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="D14" s="7">
-        <v>45553.747881944444</v>
-      </c>
-      <c r="E14" s="6">
-        <v>1211</v>
-      </c>
-      <c r="H14" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="I14" s="6" t="s">
+      <c r="D24" s="7">
+        <v>45653.014664351853</v>
+      </c>
+      <c r="E24" s="6">
+        <v>2522</v>
+      </c>
+      <c r="F24" s="6"/>
+      <c r="G24">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H24" s="11"/>
+      <c r="I24" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="J14" s="7">
-        <v>45553.747881944444</v>
-      </c>
-      <c r="K14" s="6">
-        <v>1211</v>
-      </c>
-    </row>
-    <row r="15" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="F15" s="6">
-        <f t="shared" si="0"/>
-        <v>-2192</v>
-      </c>
-      <c r="H15" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="I15" s="6" t="s">
+      <c r="J24" s="7">
+        <v>45653.014664351853</v>
+      </c>
+      <c r="K24" s="6">
+        <v>2522</v>
+      </c>
+    </row>
+    <row r="25" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C25" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="J15" s="7">
-        <v>45488.006921296299</v>
-      </c>
-      <c r="K15" s="6">
-        <v>2192</v>
-      </c>
-    </row>
-    <row r="16" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="C16" s="6" t="s">
+      <c r="D25" s="7">
+        <v>45650.943425925929</v>
+      </c>
+      <c r="E25" s="6">
+        <v>1000</v>
+      </c>
+      <c r="F25" s="6"/>
+      <c r="G25">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H25" s="12"/>
+      <c r="I25" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="J25" s="7">
+        <v>45650.943425925929</v>
+      </c>
+      <c r="K25" s="6">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="26" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C26" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="D16" s="7">
-        <v>45488.204421296294</v>
-      </c>
-      <c r="E16" s="6">
-        <v>2104</v>
-      </c>
-      <c r="F16" s="6">
-        <f t="shared" si="0"/>
-        <v>-150</v>
-      </c>
-      <c r="H16" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="I16" s="6" t="s">
+      <c r="D26" s="7">
+        <v>45580.246689814812</v>
+      </c>
+      <c r="E26" s="6">
+        <v>9550</v>
+      </c>
+      <c r="F26" s="6"/>
+      <c r="G26">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I26" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="J16" s="7">
-        <v>45488.089548611111</v>
-      </c>
-      <c r="K16" s="6">
-        <v>2254</v>
-      </c>
-    </row>
-    <row r="17" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="F17" s="6">
-        <f t="shared" si="0"/>
-        <v>-1801</v>
-      </c>
-      <c r="H17" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="I17" s="6" t="s">
-        <v>189</v>
-      </c>
-      <c r="J17" s="7">
-        <v>45587.166886574072</v>
-      </c>
-      <c r="K17" s="6">
-        <v>1801</v>
-      </c>
-    </row>
-    <row r="18" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C18" s="6" t="s">
+      <c r="J26" s="7">
+        <v>45580.246689814812</v>
+      </c>
+      <c r="K26" s="6">
+        <v>9550</v>
+      </c>
+    </row>
+    <row r="27" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C27" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="D18" s="7">
-        <v>45598.704918981479</v>
-      </c>
-      <c r="E18" s="6">
-        <v>1654</v>
-      </c>
-      <c r="F18" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H18" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="I18" s="6" t="s">
+      <c r="D27" s="7">
+        <v>45601.294317129628</v>
+      </c>
+      <c r="E27" s="6">
+        <v>6075</v>
+      </c>
+      <c r="F27" s="6"/>
+      <c r="G27">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H27" s="6"/>
+      <c r="I27" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="J18" s="7">
-        <v>45570.907997685186</v>
-      </c>
-      <c r="K18" s="6">
-        <v>1654</v>
-      </c>
-    </row>
-    <row r="19" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C19" s="6" t="s">
+      <c r="J27" s="7">
+        <v>45601.294317129628</v>
+      </c>
+      <c r="K27" s="6">
+        <v>6075</v>
+      </c>
+    </row>
+    <row r="28" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C28" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="D19" s="7">
-        <v>45598.705104166664</v>
-      </c>
-      <c r="E19" s="6">
-        <v>1855</v>
-      </c>
-      <c r="F19" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H19" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="I19" s="6" t="s">
+      <c r="D28" s="7">
+        <v>45611.897511574076</v>
+      </c>
+      <c r="E28" s="6">
+        <v>1633</v>
+      </c>
+      <c r="F28" s="6"/>
+      <c r="G28">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H28" s="6"/>
+      <c r="I28" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="J19" s="7">
-        <v>45570.908067129632</v>
-      </c>
-      <c r="K19" s="6">
-        <v>1855</v>
-      </c>
-    </row>
-    <row r="20" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="F20" s="6">
-        <f t="shared" si="0"/>
-        <v>-686</v>
-      </c>
-      <c r="H20" s="8"/>
-      <c r="I20" s="9" t="s">
+      <c r="J28" s="7">
+        <v>45611.897511574076</v>
+      </c>
+      <c r="K28" s="6">
+        <v>1633</v>
+      </c>
+    </row>
+    <row r="29" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="F29" s="6"/>
+      <c r="G29">
+        <f t="shared" si="0"/>
+        <v>-5523</v>
+      </c>
+      <c r="H29" s="6"/>
+      <c r="I29" s="6" t="s">
+        <v>241</v>
+      </c>
+      <c r="J29" s="7">
+        <v>45721.988587962966</v>
+      </c>
+      <c r="K29" s="6">
+        <v>5523</v>
+      </c>
+    </row>
+    <row r="30" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C30" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="J20" s="10">
-        <v>45561.140324074076</v>
-      </c>
-      <c r="K20" s="9">
-        <v>686</v>
-      </c>
-    </row>
-    <row r="21" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C21" s="6" t="s">
+      <c r="D30" s="7">
+        <v>45592.980821759258</v>
+      </c>
+      <c r="E30" s="6">
+        <v>8304</v>
+      </c>
+      <c r="F30" s="6"/>
+      <c r="G30">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H30" s="6"/>
+      <c r="I30" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="J30" s="7">
+        <v>45592.980821759258</v>
+      </c>
+      <c r="K30" s="6">
+        <v>8304</v>
+      </c>
+    </row>
+    <row r="31" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C31" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="D21" s="7">
-        <v>45580.246689814812</v>
-      </c>
-      <c r="E21" s="6">
-        <v>9550</v>
-      </c>
-      <c r="F21" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I21" s="6" t="s">
+      <c r="D31" s="7">
+        <v>45602.853263888886</v>
+      </c>
+      <c r="E31" s="6">
+        <v>9421</v>
+      </c>
+      <c r="F31" s="6"/>
+      <c r="G31">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H31" s="6"/>
+      <c r="I31" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="J21" s="7">
-        <v>45580.654513888891</v>
-      </c>
-      <c r="K21" s="6">
-        <v>9550</v>
-      </c>
-    </row>
-    <row r="22" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C22" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="D22" s="7">
-        <v>45601.294317129628</v>
-      </c>
-      <c r="E22" s="6">
-        <v>6075</v>
-      </c>
-      <c r="F22" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H22" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="I22" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="J22" s="7">
-        <v>45601.281597222223</v>
-      </c>
-      <c r="K22" s="6">
-        <v>6075</v>
-      </c>
-    </row>
-    <row r="23" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B23" t="s">
-        <v>206</v>
-      </c>
-      <c r="C23" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="D23" s="7">
-        <v>45611.897511574076</v>
-      </c>
-      <c r="E23" s="6">
-        <v>1633</v>
-      </c>
-      <c r="F23" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I23" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="J23" s="7">
-        <v>45562.222928240742</v>
-      </c>
-      <c r="K23" s="6">
-        <v>1633</v>
-      </c>
-    </row>
-    <row r="24" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C24" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="D24" s="7">
-        <v>45592.980821759258</v>
-      </c>
-      <c r="E24" s="6">
-        <v>8304</v>
-      </c>
-      <c r="F24" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H24" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="I24" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="J24" s="7">
-        <v>45583.714583333334</v>
-      </c>
-      <c r="K24" s="6">
-        <v>8304</v>
-      </c>
-    </row>
-    <row r="25" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C25" s="6" t="s">
+      <c r="J31" s="7">
+        <v>45602.853263888886</v>
+      </c>
+      <c r="K31" s="6">
+        <v>9421</v>
+      </c>
+    </row>
+    <row r="32" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C32" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="D32" s="7">
+        <v>45585.078321759262</v>
+      </c>
+      <c r="E32" s="6">
+        <v>7216</v>
+      </c>
+      <c r="F32" s="6"/>
+      <c r="G32">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H32" s="6"/>
+      <c r="I32" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="J32" s="7">
+        <v>45585.078321759262</v>
+      </c>
+      <c r="K32" s="6">
+        <v>7216</v>
+      </c>
+    </row>
+    <row r="33" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C33" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="D25" s="7">
-        <v>45602.853263888886</v>
-      </c>
-      <c r="E25" s="6">
-        <v>9421</v>
-      </c>
-      <c r="F25" s="6">
-        <f t="shared" si="0"/>
-        <v>-1</v>
-      </c>
-      <c r="I25" s="6" t="s">
+      <c r="D33" s="7">
+        <v>45592.98133101852</v>
+      </c>
+      <c r="E33" s="6">
+        <v>6691</v>
+      </c>
+      <c r="F33" s="6"/>
+      <c r="G33">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I33" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="J25" s="7">
-        <v>45602.853148148148</v>
-      </c>
-      <c r="K25" s="6">
-        <v>9422</v>
-      </c>
-    </row>
-    <row r="26" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C26" s="6" t="s">
-        <v>187</v>
-      </c>
-      <c r="D26" s="7">
-        <v>45585.078321759262</v>
-      </c>
-      <c r="E26" s="6">
-        <v>7216</v>
-      </c>
-      <c r="F26" s="6">
-        <f t="shared" si="0"/>
-        <v>-2205</v>
-      </c>
-      <c r="I26" s="6" t="s">
-        <v>187</v>
-      </c>
-      <c r="J26" s="7">
-        <v>45587.921111111114</v>
-      </c>
-      <c r="K26" s="6">
-        <v>9421</v>
-      </c>
-    </row>
-    <row r="27" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C27" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="D27" s="7">
+      <c r="J33" s="7">
         <v>45592.98133101852</v>
       </c>
-      <c r="E27" s="6">
+      <c r="K33" s="6">
         <v>6691</v>
-      </c>
-      <c r="F27" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H27" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="I27" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="J27" s="7">
-        <v>45582.831134259257</v>
-      </c>
-      <c r="K27" s="6">
-        <v>6691</v>
-      </c>
-    </row>
-    <row r="28" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C28" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="D28" s="7">
-        <v>45611.898240740738</v>
-      </c>
-      <c r="E28" s="6">
-        <v>4306</v>
-      </c>
-      <c r="F28" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H28" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="I28" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="J28" s="7">
-        <v>45571.087962962964</v>
-      </c>
-      <c r="K28" s="6">
-        <v>4306</v>
-      </c>
-    </row>
-    <row r="29" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C29" s="6" t="s">
-        <v>190</v>
-      </c>
-      <c r="D29" s="7">
-        <v>45592.981458333335</v>
-      </c>
-      <c r="E29" s="6">
-        <v>5118</v>
-      </c>
-      <c r="F29" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H29" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="I29" s="6" t="s">
-        <v>190</v>
-      </c>
-      <c r="J29" s="7">
-        <v>45587.194444444445</v>
-      </c>
-      <c r="K29" s="6">
-        <v>5118</v>
-      </c>
-    </row>
-    <row r="30" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C30" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="D30" s="7">
-        <v>45559.059641203705</v>
-      </c>
-      <c r="E30" s="6">
-        <v>3838</v>
-      </c>
-      <c r="F30" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H30" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="I30" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="J30" s="7">
-        <v>45554.139884259261</v>
-      </c>
-      <c r="K30" s="6">
-        <v>3838</v>
-      </c>
-    </row>
-    <row r="31" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C31" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="D31" s="7">
-        <v>45564.562025462961</v>
-      </c>
-      <c r="E31" s="6">
-        <v>2780</v>
-      </c>
-      <c r="F31" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H31" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="I31" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="J31" s="7">
-        <v>45564.561550925922</v>
-      </c>
-      <c r="K31" s="6">
-        <v>2780</v>
-      </c>
-    </row>
-    <row r="32" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C32" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="D32" s="7">
-        <v>45592.926134259258</v>
-      </c>
-      <c r="E32" s="6">
-        <v>2667</v>
-      </c>
-      <c r="F32" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="H32" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="I32" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="J32" s="7">
-        <v>45587.760914351849</v>
-      </c>
-      <c r="K32" s="6">
-        <v>2667</v>
-      </c>
-    </row>
-    <row r="33" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="F33" s="6">
-        <f t="shared" si="0"/>
-        <v>-3716</v>
-      </c>
-      <c r="I33" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="J33" s="7">
-        <v>45494.86377314815</v>
-      </c>
-      <c r="K33" s="6">
-        <v>3716</v>
       </c>
     </row>
     <row r="34" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C34" s="6" t="s">
-        <v>43</v>
+        <v>54</v>
       </c>
       <c r="D34" s="7">
+        <v>45611.898240740738</v>
+      </c>
+      <c r="E34" s="6">
+        <v>4306</v>
+      </c>
+      <c r="F34" s="6"/>
+      <c r="G34">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I34" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="J34" s="7">
+        <v>45611.898240740738</v>
+      </c>
+      <c r="K34" s="6">
+        <v>4306</v>
+      </c>
+    </row>
+    <row r="35" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C35" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="D35" s="7">
+        <v>45592.981458333335</v>
+      </c>
+      <c r="E35" s="6">
+        <v>5118</v>
+      </c>
+      <c r="G35">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I35" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="J35" s="7">
+        <v>45592.981458333335</v>
+      </c>
+      <c r="K35" s="6">
+        <v>5118</v>
+      </c>
+    </row>
+    <row r="36" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C36" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="D36" s="7">
+        <v>45559.059641203705</v>
+      </c>
+      <c r="E36" s="6">
+        <v>3838</v>
+      </c>
+      <c r="G36">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I36" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="J36" s="7">
+        <v>45559.059641203705</v>
+      </c>
+      <c r="K36" s="6">
+        <v>3838</v>
+      </c>
+    </row>
+    <row r="37" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C37" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="D37" s="7">
+        <v>45564.562025462961</v>
+      </c>
+      <c r="E37" s="6">
+        <v>2780</v>
+      </c>
+      <c r="G37">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I37" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="J37" s="7">
+        <v>45564.562025462961</v>
+      </c>
+      <c r="K37" s="6">
+        <v>2780</v>
+      </c>
+    </row>
+    <row r="38" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C38" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="D38" s="7">
+        <v>45592.926134259258</v>
+      </c>
+      <c r="E38" s="6">
+        <v>2667</v>
+      </c>
+      <c r="G38">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I38" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="J38" s="7">
+        <v>45592.926134259258</v>
+      </c>
+      <c r="K38" s="6">
+        <v>2667</v>
+      </c>
+    </row>
+    <row r="39" spans="3:11" x14ac:dyDescent="0.25">
+      <c r="C39" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="D39" s="7">
         <v>45564.561944444446</v>
       </c>
-      <c r="E34" s="6">
+      <c r="E39" s="6">
         <v>2756</v>
       </c>
-      <c r="F34" s="6">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="I34" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="J34" s="7">
-        <v>45564.554328703707</v>
-      </c>
-      <c r="K34" s="6">
+      <c r="G39">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="I39" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="J39" s="7">
+        <v>45564.561944444446</v>
+      </c>
+      <c r="K39" s="6">
         <v>2756</v>
-      </c>
-    </row>
-    <row r="35" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C35" s="6"/>
-      <c r="D35" s="7"/>
-      <c r="E35" s="6"/>
-      <c r="I35" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="J35" s="7">
-        <v>45494.09170138889</v>
-      </c>
-      <c r="K35" s="6">
-        <v>3726</v>
       </c>
     </row>
   </sheetData>
@@ -2971,394 +3232,394 @@
   </cols>
   <sheetData>
     <row r="3" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C3" s="11">
+      <c r="C3" s="8">
         <v>1022601</v>
       </c>
-      <c r="D3" s="11" t="s">
-        <v>101</v>
-      </c>
-      <c r="E3" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="F3" s="12">
+      <c r="D3" s="8" t="s">
+        <v>96</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>95</v>
+      </c>
+      <c r="F3" s="9">
         <v>43895.912951388891</v>
       </c>
-      <c r="G3" s="11" t="s">
+      <c r="G3" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="H3" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="I3" s="8" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="4" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C4" s="8">
+        <v>1022658</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>94</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="F4" s="9">
+        <v>43923.942187499997</v>
+      </c>
+      <c r="G4" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="I4" s="8" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="5" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C5" s="8">
+        <v>1022662</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>92</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>91</v>
+      </c>
+      <c r="F5" s="9">
+        <v>43927.866064814814</v>
+      </c>
+      <c r="G5" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="H5" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="I5" s="8" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="6" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C6" s="8">
+        <v>1022726</v>
+      </c>
+      <c r="D6" s="8" t="s">
+        <v>90</v>
+      </c>
+      <c r="E6" s="8" t="s">
+        <v>89</v>
+      </c>
+      <c r="F6" s="9">
+        <v>43982.709652777776</v>
+      </c>
+      <c r="G6" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="H6" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="I6" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="H3" s="11" t="s">
+    </row>
+    <row r="7" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C7" s="8">
+        <v>1022727</v>
+      </c>
+      <c r="D7" s="8" t="s">
+        <v>88</v>
+      </c>
+      <c r="E7" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="F7" s="9">
+        <v>43982.814953703702</v>
+      </c>
+      <c r="G7" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="I7" s="8" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="8" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C8" s="8">
+        <v>1022766</v>
+      </c>
+      <c r="D8" s="8" t="s">
+        <v>86</v>
+      </c>
+      <c r="E8" s="8" t="s">
+        <v>85</v>
+      </c>
+      <c r="F8" s="9">
+        <v>43989.993263888886</v>
+      </c>
+      <c r="G8" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="I3" s="11" t="s">
+      <c r="H8" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="I8" s="8" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="9" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C9" s="8">
+        <v>1023416</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>84</v>
+      </c>
+      <c r="E9" s="8" t="s">
+        <v>83</v>
+      </c>
+      <c r="F9" s="9">
+        <v>44176.769629629627</v>
+      </c>
+      <c r="G9" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="H9" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="I9" s="8" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="10" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C10" s="8">
+        <v>1023432</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>82</v>
+      </c>
+      <c r="E10" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="F10" s="9">
+        <v>44203.767384259256</v>
+      </c>
+      <c r="G10" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="H10" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="I10" s="8" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="11" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C11" s="8">
+        <v>1023438</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="E11" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="F11" s="9">
+        <v>44205.722870370373</v>
+      </c>
+      <c r="G11" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="H11" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="I11" s="8" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="12" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C12" s="8">
+        <v>1023879</v>
+      </c>
+      <c r="D12" s="8" t="s">
+        <v>77</v>
+      </c>
+      <c r="E12" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="F12" s="9">
+        <v>44299.974594907406</v>
+      </c>
+      <c r="G12" s="8" t="s">
+        <v>75</v>
+      </c>
+      <c r="H12" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="I12" s="8" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="4" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C4" s="11">
-        <v>1022658</v>
-      </c>
-      <c r="D4" s="11" t="s">
-        <v>99</v>
-      </c>
-      <c r="E4" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="F4" s="12">
-        <v>43923.942187499997</v>
-      </c>
-      <c r="G4" s="11" t="s">
+    <row r="13" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C13" s="8">
+        <v>1023880</v>
+      </c>
+      <c r="D13" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="E13" s="8" t="s">
+        <v>73</v>
+      </c>
+      <c r="F13" s="9">
+        <v>44299.988819444443</v>
+      </c>
+      <c r="G13" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="H13" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="I13" s="8" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="14" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C14" s="8">
+        <v>1023948</v>
+      </c>
+      <c r="D14" s="8" t="s">
+        <v>72</v>
+      </c>
+      <c r="E14" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="F14" s="9">
+        <v>44328.066874999997</v>
+      </c>
+      <c r="G14" s="8" t="s">
+        <v>61</v>
+      </c>
+      <c r="H14" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="I14" s="8" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="15" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C15" s="8">
+        <v>1026625</v>
+      </c>
+      <c r="D15" s="8" t="s">
+        <v>70</v>
+      </c>
+      <c r="E15" s="8" t="s">
+        <v>69</v>
+      </c>
+      <c r="F15" s="9">
+        <v>44847.155381944445</v>
+      </c>
+      <c r="G15" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="H15" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="I15" s="8" t="s">
         <v>66</v>
       </c>
-      <c r="H4" s="11" t="s">
+    </row>
+    <row r="16" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C16" s="8">
+        <v>1032123</v>
+      </c>
+      <c r="D16" s="8" t="s">
+        <v>68</v>
+      </c>
+      <c r="E16" s="8" t="s">
+        <v>67</v>
+      </c>
+      <c r="F16" s="9">
+        <v>45033.01394675926</v>
+      </c>
+      <c r="G16" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="H16" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="I16" s="8" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="17" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C17" s="8">
+        <v>1032742</v>
+      </c>
+      <c r="D17" s="8" t="s">
+        <v>65</v>
+      </c>
+      <c r="E17" s="8" t="s">
+        <v>64</v>
+      </c>
+      <c r="F17" s="9">
+        <v>45048.675509259258</v>
+      </c>
+      <c r="G17" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="H17" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="I17" s="8" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="18" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C18" s="8">
+        <v>1032875</v>
+      </c>
+      <c r="D18" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="E18" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="F18" s="9">
+        <v>45051.104050925926</v>
+      </c>
+      <c r="G18" s="8" t="s">
         <v>61</v>
       </c>
-      <c r="I4" s="11" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="5" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C5" s="11">
-        <v>1022662</v>
-      </c>
-      <c r="D5" s="11" t="s">
-        <v>97</v>
-      </c>
-      <c r="E5" s="11" t="s">
-        <v>96</v>
-      </c>
-      <c r="F5" s="12">
-        <v>43927.866064814814</v>
-      </c>
-      <c r="G5" s="11" t="s">
-        <v>80</v>
-      </c>
-      <c r="H5" s="11" t="s">
-        <v>61</v>
-      </c>
-      <c r="I5" s="11" t="s">
+      <c r="H18" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="I18" s="8" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="6" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C6" s="11">
-        <v>1022726</v>
-      </c>
-      <c r="D6" s="11" t="s">
-        <v>95</v>
-      </c>
-      <c r="E6" s="11" t="s">
-        <v>94</v>
-      </c>
-      <c r="F6" s="12">
-        <v>43982.709652777776</v>
-      </c>
-      <c r="G6" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="H6" s="11" t="s">
-        <v>61</v>
-      </c>
-      <c r="I6" s="11" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="7" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C7" s="11">
-        <v>1022727</v>
-      </c>
-      <c r="D7" s="11" t="s">
-        <v>93</v>
-      </c>
-      <c r="E7" s="11" t="s">
-        <v>92</v>
-      </c>
-      <c r="F7" s="12">
-        <v>43982.814953703702</v>
-      </c>
-      <c r="G7" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="H7" s="11" t="s">
-        <v>61</v>
-      </c>
-      <c r="I7" s="11" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="8" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C8" s="11">
-        <v>1022766</v>
-      </c>
-      <c r="D8" s="11" t="s">
-        <v>91</v>
-      </c>
-      <c r="E8" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="F8" s="12">
-        <v>43989.993263888886</v>
-      </c>
-      <c r="G8" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="H8" s="11" t="s">
-        <v>61</v>
-      </c>
-      <c r="I8" s="11" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="9" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C9" s="11">
-        <v>1023416</v>
-      </c>
-      <c r="D9" s="11" t="s">
-        <v>89</v>
-      </c>
-      <c r="E9" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="F9" s="12">
-        <v>44176.769629629627</v>
-      </c>
-      <c r="G9" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="H9" s="11" t="s">
-        <v>61</v>
-      </c>
-      <c r="I9" s="11" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="10" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C10" s="11">
-        <v>1023432</v>
-      </c>
-      <c r="D10" s="11" t="s">
-        <v>87</v>
-      </c>
-      <c r="E10" s="11" t="s">
-        <v>86</v>
-      </c>
-      <c r="F10" s="12">
-        <v>44203.767384259256</v>
-      </c>
-      <c r="G10" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="H10" s="11" t="s">
-        <v>61</v>
-      </c>
-      <c r="I10" s="11" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="11" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C11" s="11">
-        <v>1023438</v>
-      </c>
-      <c r="D11" s="11" t="s">
-        <v>85</v>
-      </c>
-      <c r="E11" s="11" t="s">
-        <v>84</v>
-      </c>
-      <c r="F11" s="12">
-        <v>44205.722870370373</v>
-      </c>
-      <c r="G11" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="H11" s="11" t="s">
-        <v>61</v>
-      </c>
-      <c r="I11" s="11" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="12" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C12" s="11">
-        <v>1023879</v>
-      </c>
-      <c r="D12" s="11" t="s">
-        <v>82</v>
-      </c>
-      <c r="E12" s="11" t="s">
-        <v>81</v>
-      </c>
-      <c r="F12" s="12">
-        <v>44299.974594907406</v>
-      </c>
-      <c r="G12" s="11" t="s">
-        <v>80</v>
-      </c>
-      <c r="H12" s="11" t="s">
-        <v>61</v>
-      </c>
-      <c r="I12" s="11" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="13" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C13" s="11">
-        <v>1023880</v>
-      </c>
-      <c r="D13" s="11" t="s">
-        <v>79</v>
-      </c>
-      <c r="E13" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="F13" s="12">
-        <v>44299.988819444443</v>
-      </c>
-      <c r="G13" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="H13" s="11" t="s">
-        <v>61</v>
-      </c>
-      <c r="I13" s="11" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="14" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C14" s="11">
-        <v>1023948</v>
-      </c>
-      <c r="D14" s="11" t="s">
-        <v>77</v>
-      </c>
-      <c r="E14" s="11" t="s">
-        <v>76</v>
-      </c>
-      <c r="F14" s="12">
-        <v>44328.066874999997</v>
-      </c>
-      <c r="G14" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="H14" s="11" t="s">
-        <v>61</v>
-      </c>
-      <c r="I14" s="11" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="15" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C15" s="11">
-        <v>1026625</v>
-      </c>
-      <c r="D15" s="11" t="s">
-        <v>75</v>
-      </c>
-      <c r="E15" s="11" t="s">
-        <v>74</v>
-      </c>
-      <c r="F15" s="12">
-        <v>44847.155381944445</v>
-      </c>
-      <c r="G15" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="H15" s="11" t="s">
-        <v>61</v>
-      </c>
-      <c r="I15" s="11" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="16" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C16" s="11">
-        <v>1032123</v>
-      </c>
-      <c r="D16" s="11" t="s">
-        <v>73</v>
-      </c>
-      <c r="E16" s="11" t="s">
-        <v>72</v>
-      </c>
-      <c r="F16" s="12">
-        <v>45033.01394675926</v>
-      </c>
-      <c r="G16" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="H16" s="11" t="s">
-        <v>61</v>
-      </c>
-      <c r="I16" s="11" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="17" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C17" s="11">
-        <v>1032742</v>
-      </c>
-      <c r="D17" s="11" t="s">
-        <v>70</v>
-      </c>
-      <c r="E17" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="F17" s="12">
-        <v>45048.675509259258</v>
-      </c>
-      <c r="G17" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="H17" s="11" t="s">
-        <v>61</v>
-      </c>
-      <c r="I17" s="11" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="18" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C18" s="11">
-        <v>1032875</v>
-      </c>
-      <c r="D18" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="E18" s="11" t="s">
-        <v>67</v>
-      </c>
-      <c r="F18" s="12">
-        <v>45051.104050925926</v>
-      </c>
-      <c r="G18" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="H18" s="11" t="s">
-        <v>61</v>
-      </c>
-      <c r="I18" s="11" t="s">
-        <v>65</v>
-      </c>
-    </row>
     <row r="19" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C19" s="11">
+      <c r="C19" s="8">
         <v>1039072</v>
       </c>
-      <c r="D19" s="11" t="s">
-        <v>64</v>
-      </c>
-      <c r="E19" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="F19" s="12">
+      <c r="D19" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="E19" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="F19" s="9">
         <v>45326.032002314816</v>
       </c>
-      <c r="G19" s="11" t="s">
-        <v>62</v>
-      </c>
-      <c r="H19" s="11" t="s">
-        <v>61</v>
-      </c>
-      <c r="I19" s="11" t="s">
-        <v>60</v>
+      <c r="G19" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="H19" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="I19" s="8" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="20" spans="3:9" x14ac:dyDescent="0.25">
@@ -3366,22 +3627,22 @@
         <v>1042834</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>207</v>
+        <v>200</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="F20" s="7">
         <v>45454.27144675926</v>
       </c>
       <c r="G20" s="6" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="H20" s="6" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="I20" s="6" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
     </row>
     <row r="21" spans="3:9" x14ac:dyDescent="0.25">
@@ -3389,22 +3650,22 @@
         <v>1050846</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>210</v>
+        <v>203</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>211</v>
+        <v>204</v>
       </c>
       <c r="F21" s="7">
         <v>45601.239988425928</v>
       </c>
       <c r="G21" s="6" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="H21" s="6" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="I21" s="6" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
     </row>
     <row r="22" spans="3:9" x14ac:dyDescent="0.25">
@@ -3412,22 +3673,22 @@
         <v>1051098</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>212</v>
+        <v>205</v>
       </c>
       <c r="E22" s="6" t="s">
-        <v>213</v>
+        <v>206</v>
       </c>
       <c r="F22" s="7">
         <v>45604.205393518518</v>
       </c>
       <c r="G22" s="6" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="H22" s="6" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="I22" s="6" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
     </row>
     <row r="23" spans="3:9" x14ac:dyDescent="0.25">
@@ -3435,22 +3696,22 @@
         <v>1052020</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>214</v>
+        <v>207</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>215</v>
+        <v>208</v>
       </c>
       <c r="F23" s="7">
         <v>45622.37767361111</v>
       </c>
       <c r="G23" s="6" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="H23" s="6" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="I23" s="6" t="s">
-        <v>209</v>
+        <v>202</v>
       </c>
     </row>
     <row r="24" spans="3:9" x14ac:dyDescent="0.25">
@@ -3458,22 +3719,22 @@
         <v>1052875</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>216</v>
+        <v>209</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="F24" s="7">
         <v>45640.870659722219</v>
       </c>
       <c r="G24" s="6" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="H24" s="6" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="I24" s="6" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
     </row>
     <row r="25" spans="3:9" x14ac:dyDescent="0.25">
@@ -3481,22 +3742,22 @@
         <v>1053689</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="F25" s="7">
         <v>45670.828263888892</v>
       </c>
       <c r="G25" s="6" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="H25" s="6" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="I25" s="6" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
     </row>
     <row r="26" spans="3:9" x14ac:dyDescent="0.25">
@@ -3504,22 +3765,22 @@
         <v>1053712</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="E26" s="6" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
       <c r="F26" s="7">
         <v>45671.810312499998</v>
       </c>
       <c r="G26" s="6" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="H26" s="6" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="I26" s="6" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
     </row>
   </sheetData>
@@ -3542,31 +3803,31 @@
   <sheetData>
     <row r="2" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
+        <v>216</v>
+      </c>
+      <c r="C2" t="s">
+        <v>217</v>
+      </c>
+      <c r="D2" t="s">
+        <v>218</v>
+      </c>
+      <c r="E2" t="s">
+        <v>219</v>
+      </c>
+      <c r="F2" t="s">
+        <v>220</v>
+      </c>
+      <c r="G2" t="s">
+        <v>227</v>
+      </c>
+      <c r="H2" t="s">
         <v>223</v>
       </c>
-      <c r="C2" t="s">
-        <v>224</v>
-      </c>
-      <c r="D2" t="s">
-        <v>225</v>
-      </c>
-      <c r="E2" t="s">
-        <v>226</v>
-      </c>
-      <c r="F2" t="s">
-        <v>227</v>
-      </c>
-      <c r="G2" t="s">
-        <v>234</v>
-      </c>
-      <c r="H2" t="s">
-        <v>230</v>
-      </c>
       <c r="I2" t="s">
-        <v>228</v>
+        <v>221</v>
       </c>
       <c r="J2" t="s">
-        <v>229</v>
+        <v>222</v>
       </c>
     </row>
     <row r="4" spans="2:10" ht="45" x14ac:dyDescent="0.25">
@@ -3574,17 +3835,17 @@
         <v>1</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>231</v>
+        <v>224</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>232</v>
+        <v>225</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="F4" s="1"/>
       <c r="G4" s="1" t="s">
-        <v>235</v>
+        <v>228</v>
       </c>
       <c r="H4" s="1">
         <v>1</v>
@@ -3597,16 +3858,16 @@
         <v>2</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>238</v>
+        <v>231</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="G5" s="1"/>
       <c r="H5" s="1"/>
@@ -3916,6 +4177,275 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E62F5D6-175B-45B6-972E-43ED476FB806}">
+  <dimension ref="B3:H13"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="4" max="4" width="22.42578125" customWidth="1"/>
+    <col min="5" max="5" width="16" customWidth="1"/>
+    <col min="6" max="6" width="22.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B3" t="s">
+        <v>291</v>
+      </c>
+      <c r="C3" t="s">
+        <v>292</v>
+      </c>
+      <c r="D3" t="s">
+        <v>293</v>
+      </c>
+      <c r="E3" t="s">
+        <v>294</v>
+      </c>
+      <c r="F3" t="s">
+        <v>295</v>
+      </c>
+      <c r="G3" t="s">
+        <v>296</v>
+      </c>
+      <c r="H3" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="4" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B4">
+        <v>105088</v>
+      </c>
+      <c r="C4">
+        <v>10</v>
+      </c>
+      <c r="D4" t="s">
+        <v>264</v>
+      </c>
+      <c r="E4" t="s">
+        <v>265</v>
+      </c>
+      <c r="F4" t="s">
+        <v>266</v>
+      </c>
+      <c r="G4" t="s">
+        <v>61</v>
+      </c>
+      <c r="H4" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="5" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B5">
+        <v>105653</v>
+      </c>
+      <c r="C5">
+        <v>4</v>
+      </c>
+      <c r="D5" t="s">
+        <v>267</v>
+      </c>
+      <c r="E5" t="s">
+        <v>268</v>
+      </c>
+      <c r="F5" t="s">
+        <v>269</v>
+      </c>
+      <c r="G5" t="s">
+        <v>57</v>
+      </c>
+      <c r="H5" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="6" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B6">
+        <v>105089</v>
+      </c>
+      <c r="C6">
+        <v>10</v>
+      </c>
+      <c r="D6" t="s">
+        <v>270</v>
+      </c>
+      <c r="E6" t="s">
+        <v>265</v>
+      </c>
+      <c r="F6" t="s">
+        <v>271</v>
+      </c>
+      <c r="G6" t="s">
+        <v>57</v>
+      </c>
+      <c r="H6" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="7" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B7">
+        <v>105655</v>
+      </c>
+      <c r="C7">
+        <v>5</v>
+      </c>
+      <c r="D7" t="s">
+        <v>272</v>
+      </c>
+      <c r="E7" t="s">
+        <v>273</v>
+      </c>
+      <c r="F7" t="s">
+        <v>274</v>
+      </c>
+      <c r="G7" t="s">
+        <v>57</v>
+      </c>
+      <c r="H7" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="8" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B8">
+        <v>105087</v>
+      </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
+      <c r="D8" t="s">
+        <v>275</v>
+      </c>
+      <c r="E8" t="s">
+        <v>276</v>
+      </c>
+      <c r="F8" t="s">
+        <v>277</v>
+      </c>
+      <c r="G8" t="s">
+        <v>61</v>
+      </c>
+      <c r="H8" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="9" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B9">
+        <v>105709</v>
+      </c>
+      <c r="C9">
+        <v>1</v>
+      </c>
+      <c r="D9" t="s">
+        <v>278</v>
+      </c>
+      <c r="E9" t="s">
+        <v>276</v>
+      </c>
+      <c r="F9" t="s">
+        <v>279</v>
+      </c>
+      <c r="G9" t="s">
+        <v>57</v>
+      </c>
+      <c r="H9" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="10" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B10">
+        <v>105708</v>
+      </c>
+      <c r="C10">
+        <v>1</v>
+      </c>
+      <c r="D10" t="s">
+        <v>280</v>
+      </c>
+      <c r="E10" t="s">
+        <v>276</v>
+      </c>
+      <c r="F10" t="s">
+        <v>281</v>
+      </c>
+      <c r="G10" t="s">
+        <v>57</v>
+      </c>
+      <c r="H10" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="11" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B11">
+        <v>105108</v>
+      </c>
+      <c r="C11">
+        <v>3</v>
+      </c>
+      <c r="D11" t="s">
+        <v>282</v>
+      </c>
+      <c r="E11" t="s">
+        <v>283</v>
+      </c>
+      <c r="F11" t="s">
+        <v>284</v>
+      </c>
+      <c r="G11" t="s">
+        <v>57</v>
+      </c>
+      <c r="H11" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="12" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B12">
+        <v>105654</v>
+      </c>
+      <c r="C12">
+        <v>2</v>
+      </c>
+      <c r="D12" t="s">
+        <v>285</v>
+      </c>
+      <c r="E12" t="s">
+        <v>286</v>
+      </c>
+      <c r="F12" t="s">
+        <v>287</v>
+      </c>
+      <c r="G12" t="s">
+        <v>57</v>
+      </c>
+      <c r="H12" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="13" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B13">
+        <v>105667</v>
+      </c>
+      <c r="C13">
+        <v>9</v>
+      </c>
+      <c r="D13" t="s">
+        <v>288</v>
+      </c>
+      <c r="E13" t="s">
+        <v>289</v>
+      </c>
+      <c r="F13" t="s">
+        <v>290</v>
+      </c>
+      <c r="G13" t="s">
+        <v>61</v>
+      </c>
+      <c r="H13" t="s">
+        <v>61</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{831397A3-B5B5-4502-B050-EC180F79243F}">
   <dimension ref="C2:H12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -3926,21 +4456,21 @@
   <sheetData>
     <row r="2" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C2" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G2" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
     </row>
     <row r="3" spans="3:8" ht="30" x14ac:dyDescent="0.25">
       <c r="C3" s="6" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="D3" s="6">
         <v>1904</v>
       </c>
       <c r="G3" s="6" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="H3" s="6">
         <v>1904</v>
@@ -3948,13 +4478,13 @@
     </row>
     <row r="4" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C4" s="6" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="D4" s="6">
         <v>6291</v>
       </c>
       <c r="G4" s="6" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="H4" s="6">
         <v>6291</v>
@@ -3962,13 +4492,13 @@
     </row>
     <row r="5" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C5" s="6" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="D5" s="6">
         <v>3032</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="H5" s="6">
         <v>3032</v>
@@ -3976,13 +4506,13 @@
     </row>
     <row r="6" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C6" s="6" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="D6" s="6">
         <v>829</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="H6" s="6">
         <v>829</v>
@@ -3990,7 +4520,7 @@
     </row>
     <row r="7" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C7" s="6" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="D7" s="6">
         <v>599</v>
@@ -3998,13 +4528,13 @@
     </row>
     <row r="8" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C8" s="6" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="D8" s="6">
         <v>918</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="H8" s="6">
         <v>1009</v>
@@ -4012,13 +4542,13 @@
     </row>
     <row r="9" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C9" s="6" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="D9" s="6">
         <v>3693</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="H9" s="6">
         <v>3693</v>
@@ -4026,13 +4556,13 @@
     </row>
     <row r="10" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C10" s="6" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="D10" s="6">
         <v>1561</v>
       </c>
       <c r="G10" s="6" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="H10" s="6">
         <v>1561</v>
@@ -4040,13 +4570,13 @@
     </row>
     <row r="11" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C11" s="6" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="D11" s="6">
         <v>890</v>
       </c>
       <c r="G11" s="6" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="H11" s="6">
         <v>890</v>
@@ -4054,1033 +4584,16 @@
     </row>
     <row r="12" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C12" s="6" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="D12" s="6">
         <v>303</v>
       </c>
       <c r="G12" s="6" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="H12" s="6">
         <v>303</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{58AD8689-83A3-4231-B877-3E047206A588}">
-  <dimension ref="C3:E94"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData>
-    <row r="3" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C3">
-        <v>2016</v>
-      </c>
-      <c r="D3">
-        <v>6</v>
-      </c>
-      <c r="E3">
-        <v>82514</v>
-      </c>
-    </row>
-    <row r="4" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C4">
-        <v>2016</v>
-      </c>
-      <c r="D4">
-        <v>8</v>
-      </c>
-      <c r="E4">
-        <v>40401</v>
-      </c>
-    </row>
-    <row r="5" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C5">
-        <v>2016</v>
-      </c>
-      <c r="D5">
-        <v>9</v>
-      </c>
-      <c r="E5">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="6" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C6">
-        <v>2016</v>
-      </c>
-      <c r="D6">
-        <v>10</v>
-      </c>
-      <c r="E6">
-        <v>765</v>
-      </c>
-    </row>
-    <row r="7" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C7">
-        <v>2016</v>
-      </c>
-      <c r="D7">
-        <v>11</v>
-      </c>
-      <c r="E7">
-        <v>12353</v>
-      </c>
-    </row>
-    <row r="8" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C8">
-        <v>2016</v>
-      </c>
-      <c r="D8">
-        <v>12</v>
-      </c>
-      <c r="E8">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="9" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C9">
-        <v>2017</v>
-      </c>
-      <c r="D9">
-        <v>1</v>
-      </c>
-      <c r="E9">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="10" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C10">
-        <v>2017</v>
-      </c>
-      <c r="D10">
-        <v>2</v>
-      </c>
-      <c r="E10">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="11" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C11">
-        <v>2017</v>
-      </c>
-      <c r="D11">
-        <v>3</v>
-      </c>
-      <c r="E11">
-        <v>414</v>
-      </c>
-    </row>
-    <row r="12" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C12">
-        <v>2017</v>
-      </c>
-      <c r="D12">
-        <v>4</v>
-      </c>
-      <c r="E12">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="13" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C13">
-        <v>2017</v>
-      </c>
-      <c r="D13">
-        <v>5</v>
-      </c>
-      <c r="E13">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="14" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C14">
-        <v>2017</v>
-      </c>
-      <c r="D14">
-        <v>6</v>
-      </c>
-      <c r="E14">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="15" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C15">
-        <v>2017</v>
-      </c>
-      <c r="D15">
-        <v>7</v>
-      </c>
-      <c r="E15">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="16" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C16">
-        <v>2017</v>
-      </c>
-      <c r="D16">
-        <v>8</v>
-      </c>
-      <c r="E16">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="17" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C17">
-        <v>2017</v>
-      </c>
-      <c r="D17">
-        <v>9</v>
-      </c>
-      <c r="E17">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="18" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C18">
-        <v>2017</v>
-      </c>
-      <c r="D18">
-        <v>10</v>
-      </c>
-      <c r="E18">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="19" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C19">
-        <v>2017</v>
-      </c>
-      <c r="D19">
-        <v>11</v>
-      </c>
-      <c r="E19">
-        <v>6100</v>
-      </c>
-    </row>
-    <row r="20" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C20">
-        <v>2017</v>
-      </c>
-      <c r="D20">
-        <v>12</v>
-      </c>
-      <c r="E20">
-        <v>8371</v>
-      </c>
-    </row>
-    <row r="21" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C21">
-        <v>2018</v>
-      </c>
-      <c r="D21">
-        <v>1</v>
-      </c>
-      <c r="E21">
-        <v>1816</v>
-      </c>
-    </row>
-    <row r="22" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C22">
-        <v>2018</v>
-      </c>
-      <c r="D22">
-        <v>2</v>
-      </c>
-      <c r="E22">
-        <v>2275</v>
-      </c>
-    </row>
-    <row r="23" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C23">
-        <v>2018</v>
-      </c>
-      <c r="D23">
-        <v>3</v>
-      </c>
-      <c r="E23">
-        <v>1673</v>
-      </c>
-    </row>
-    <row r="24" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C24">
-        <v>2018</v>
-      </c>
-      <c r="D24">
-        <v>4</v>
-      </c>
-      <c r="E24">
-        <v>1445</v>
-      </c>
-    </row>
-    <row r="25" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C25">
-        <v>2018</v>
-      </c>
-      <c r="D25">
-        <v>5</v>
-      </c>
-      <c r="E25">
-        <v>997</v>
-      </c>
-    </row>
-    <row r="26" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C26">
-        <v>2018</v>
-      </c>
-      <c r="D26">
-        <v>6</v>
-      </c>
-      <c r="E26">
-        <v>785</v>
-      </c>
-    </row>
-    <row r="27" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C27">
-        <v>2018</v>
-      </c>
-      <c r="D27">
-        <v>7</v>
-      </c>
-      <c r="E27">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="28" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C28">
-        <v>2018</v>
-      </c>
-      <c r="D28">
-        <v>8</v>
-      </c>
-      <c r="E28">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="29" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C29">
-        <v>2018</v>
-      </c>
-      <c r="D29">
-        <v>9</v>
-      </c>
-      <c r="E29">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="30" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C30">
-        <v>2018</v>
-      </c>
-      <c r="D30">
-        <v>10</v>
-      </c>
-      <c r="E30">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="31" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C31">
-        <v>2018</v>
-      </c>
-      <c r="D31">
-        <v>11</v>
-      </c>
-      <c r="E31">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="32" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C32">
-        <v>2018</v>
-      </c>
-      <c r="D32">
-        <v>12</v>
-      </c>
-      <c r="E32">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="33" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C33">
-        <v>2019</v>
-      </c>
-      <c r="D33">
-        <v>1</v>
-      </c>
-      <c r="E33">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="34" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C34">
-        <v>2019</v>
-      </c>
-      <c r="D34">
-        <v>2</v>
-      </c>
-      <c r="E34">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="35" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C35">
-        <v>2019</v>
-      </c>
-      <c r="D35">
-        <v>3</v>
-      </c>
-      <c r="E35">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="36" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C36">
-        <v>2019</v>
-      </c>
-      <c r="D36">
-        <v>4</v>
-      </c>
-      <c r="E36">
-        <v>996</v>
-      </c>
-    </row>
-    <row r="37" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C37">
-        <v>2019</v>
-      </c>
-      <c r="D37">
-        <v>5</v>
-      </c>
-      <c r="E37">
-        <v>6364</v>
-      </c>
-    </row>
-    <row r="38" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C38">
-        <v>2019</v>
-      </c>
-      <c r="D38">
-        <v>6</v>
-      </c>
-      <c r="E38">
-        <v>4635</v>
-      </c>
-    </row>
-    <row r="39" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C39">
-        <v>2019</v>
-      </c>
-      <c r="D39">
-        <v>7</v>
-      </c>
-      <c r="E39">
-        <v>2975</v>
-      </c>
-    </row>
-    <row r="40" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C40">
-        <v>2019</v>
-      </c>
-      <c r="D40">
-        <v>8</v>
-      </c>
-      <c r="E40">
-        <v>1312</v>
-      </c>
-    </row>
-    <row r="41" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C41">
-        <v>2019</v>
-      </c>
-      <c r="D41">
-        <v>9</v>
-      </c>
-      <c r="E41">
-        <v>3329</v>
-      </c>
-    </row>
-    <row r="42" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C42">
-        <v>2019</v>
-      </c>
-      <c r="D42">
-        <v>10</v>
-      </c>
-      <c r="E42">
-        <v>872</v>
-      </c>
-    </row>
-    <row r="43" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C43">
-        <v>2019</v>
-      </c>
-      <c r="D43">
-        <v>11</v>
-      </c>
-      <c r="E43">
-        <v>495</v>
-      </c>
-    </row>
-    <row r="44" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C44">
-        <v>2019</v>
-      </c>
-      <c r="D44">
-        <v>12</v>
-      </c>
-      <c r="E44">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="45" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C45">
-        <v>2020</v>
-      </c>
-      <c r="D45">
-        <v>1</v>
-      </c>
-      <c r="E45">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="46" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C46">
-        <v>2020</v>
-      </c>
-      <c r="D46">
-        <v>2</v>
-      </c>
-      <c r="E46">
-        <v>476</v>
-      </c>
-    </row>
-    <row r="47" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C47">
-        <v>2020</v>
-      </c>
-      <c r="D47">
-        <v>3</v>
-      </c>
-      <c r="E47">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="48" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C48">
-        <v>2020</v>
-      </c>
-      <c r="D48">
-        <v>4</v>
-      </c>
-      <c r="E48">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="49" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C49">
-        <v>2020</v>
-      </c>
-      <c r="D49">
-        <v>5</v>
-      </c>
-      <c r="E49">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="50" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C50">
-        <v>2020</v>
-      </c>
-      <c r="D50">
-        <v>6</v>
-      </c>
-      <c r="E50">
-        <v>1112</v>
-      </c>
-    </row>
-    <row r="51" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C51">
-        <v>2020</v>
-      </c>
-      <c r="D51">
-        <v>7</v>
-      </c>
-      <c r="E51">
-        <v>10295</v>
-      </c>
-    </row>
-    <row r="52" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C52">
-        <v>2020</v>
-      </c>
-      <c r="D52">
-        <v>8</v>
-      </c>
-      <c r="E52">
-        <v>9110</v>
-      </c>
-    </row>
-    <row r="53" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C53">
-        <v>2020</v>
-      </c>
-      <c r="D53">
-        <v>9</v>
-      </c>
-      <c r="E53">
-        <v>4608</v>
-      </c>
-    </row>
-    <row r="54" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C54">
-        <v>2020</v>
-      </c>
-      <c r="D54">
-        <v>10</v>
-      </c>
-      <c r="E54">
-        <v>3623</v>
-      </c>
-    </row>
-    <row r="55" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C55">
-        <v>2020</v>
-      </c>
-      <c r="D55">
-        <v>11</v>
-      </c>
-      <c r="E55">
-        <v>2103</v>
-      </c>
-    </row>
-    <row r="56" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C56">
-        <v>2020</v>
-      </c>
-      <c r="D56">
-        <v>12</v>
-      </c>
-      <c r="E56">
-        <v>2821</v>
-      </c>
-    </row>
-    <row r="57" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C57">
-        <v>2021</v>
-      </c>
-      <c r="D57">
-        <v>1</v>
-      </c>
-      <c r="E57">
-        <v>2375</v>
-      </c>
-    </row>
-    <row r="58" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C58">
-        <v>2021</v>
-      </c>
-      <c r="D58">
-        <v>2</v>
-      </c>
-      <c r="E58">
-        <v>11926</v>
-      </c>
-    </row>
-    <row r="59" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C59">
-        <v>2021</v>
-      </c>
-      <c r="D59">
-        <v>3</v>
-      </c>
-      <c r="E59">
-        <v>441</v>
-      </c>
-    </row>
-    <row r="60" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C60">
-        <v>2021</v>
-      </c>
-      <c r="D60">
-        <v>4</v>
-      </c>
-      <c r="E60">
-        <v>4456</v>
-      </c>
-    </row>
-    <row r="61" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C61">
-        <v>2021</v>
-      </c>
-      <c r="D61">
-        <v>5</v>
-      </c>
-      <c r="E61">
-        <v>7918</v>
-      </c>
-    </row>
-    <row r="62" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C62">
-        <v>2021</v>
-      </c>
-      <c r="D62">
-        <v>6</v>
-      </c>
-      <c r="E62">
-        <v>2067</v>
-      </c>
-    </row>
-    <row r="63" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C63">
-        <v>2021</v>
-      </c>
-      <c r="D63">
-        <v>7</v>
-      </c>
-      <c r="E63">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="64" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C64">
-        <v>2021</v>
-      </c>
-      <c r="D64">
-        <v>8</v>
-      </c>
-      <c r="E64">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="65" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C65">
-        <v>2021</v>
-      </c>
-      <c r="D65">
-        <v>9</v>
-      </c>
-      <c r="E65">
-        <v>482</v>
-      </c>
-    </row>
-    <row r="66" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C66">
-        <v>2021</v>
-      </c>
-      <c r="D66">
-        <v>10</v>
-      </c>
-      <c r="E66">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="67" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C67">
-        <v>2021</v>
-      </c>
-      <c r="D67">
-        <v>12</v>
-      </c>
-      <c r="E67">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="68" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C68">
-        <v>2022</v>
-      </c>
-      <c r="D68">
-        <v>3</v>
-      </c>
-      <c r="E68">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="69" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C69">
-        <v>2022</v>
-      </c>
-      <c r="D69">
-        <v>4</v>
-      </c>
-      <c r="E69">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="70" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C70">
-        <v>2022</v>
-      </c>
-      <c r="D70">
-        <v>5</v>
-      </c>
-      <c r="E70">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="71" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C71">
-        <v>2022</v>
-      </c>
-      <c r="D71">
-        <v>6</v>
-      </c>
-      <c r="E71">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="72" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C72">
-        <v>2022</v>
-      </c>
-      <c r="D72">
-        <v>9</v>
-      </c>
-      <c r="E72">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="73" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C73">
-        <v>2022</v>
-      </c>
-      <c r="D73">
-        <v>11</v>
-      </c>
-      <c r="E73">
-        <v>800</v>
-      </c>
-    </row>
-    <row r="74" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C74">
-        <v>2022</v>
-      </c>
-      <c r="D74">
-        <v>12</v>
-      </c>
-      <c r="E74">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="75" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C75">
-        <v>2023</v>
-      </c>
-      <c r="D75">
-        <v>3</v>
-      </c>
-      <c r="E75">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="76" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C76">
-        <v>2023</v>
-      </c>
-      <c r="D76">
-        <v>5</v>
-      </c>
-      <c r="E76">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="77" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C77">
-        <v>2023</v>
-      </c>
-      <c r="D77">
-        <v>7</v>
-      </c>
-      <c r="E77">
-        <v>279</v>
-      </c>
-    </row>
-    <row r="78" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C78">
-        <v>2023</v>
-      </c>
-      <c r="D78">
-        <v>8</v>
-      </c>
-      <c r="E78">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="79" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C79">
-        <v>2023</v>
-      </c>
-      <c r="D79">
-        <v>9</v>
-      </c>
-      <c r="E79">
-        <v>952</v>
-      </c>
-    </row>
-    <row r="80" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C80">
-        <v>2023</v>
-      </c>
-      <c r="D80">
-        <v>10</v>
-      </c>
-      <c r="E80">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="81" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C81">
-        <v>2023</v>
-      </c>
-      <c r="D81">
-        <v>11</v>
-      </c>
-      <c r="E81">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="82" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C82">
-        <v>2023</v>
-      </c>
-      <c r="D82">
-        <v>12</v>
-      </c>
-      <c r="E82">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="83" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C83">
-        <v>2024</v>
-      </c>
-      <c r="D83">
-        <v>1</v>
-      </c>
-      <c r="E83">
-        <v>2512</v>
-      </c>
-    </row>
-    <row r="84" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C84">
-        <v>2024</v>
-      </c>
-      <c r="D84">
-        <v>2</v>
-      </c>
-      <c r="E84">
-        <v>2348</v>
-      </c>
-    </row>
-    <row r="85" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C85">
-        <v>2024</v>
-      </c>
-      <c r="D85">
-        <v>3</v>
-      </c>
-      <c r="E85">
-        <v>2190</v>
-      </c>
-    </row>
-    <row r="86" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C86">
-        <v>2024</v>
-      </c>
-      <c r="D86">
-        <v>4</v>
-      </c>
-      <c r="E86">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="87" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C87">
-        <v>2024</v>
-      </c>
-      <c r="D87">
-        <v>5</v>
-      </c>
-      <c r="E87">
-        <v>965</v>
-      </c>
-    </row>
-    <row r="88" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C88">
-        <v>2024</v>
-      </c>
-      <c r="D88">
-        <v>6</v>
-      </c>
-      <c r="E88">
-        <v>1284</v>
-      </c>
-    </row>
-    <row r="89" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C89">
-        <v>2024</v>
-      </c>
-      <c r="D89">
-        <v>7</v>
-      </c>
-      <c r="E89">
-        <v>3295</v>
-      </c>
-    </row>
-    <row r="90" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C90">
-        <v>2024</v>
-      </c>
-      <c r="D90">
-        <v>8</v>
-      </c>
-      <c r="E90">
-        <v>12315</v>
-      </c>
-    </row>
-    <row r="91" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C91">
-        <v>2024</v>
-      </c>
-      <c r="D91">
-        <v>9</v>
-      </c>
-      <c r="E91">
-        <v>6846</v>
-      </c>
-    </row>
-    <row r="92" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C92">
-        <v>2024</v>
-      </c>
-      <c r="D92">
-        <v>10</v>
-      </c>
-      <c r="E92">
-        <v>31667</v>
-      </c>
-    </row>
-    <row r="93" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C93">
-        <v>2024</v>
-      </c>
-      <c r="D93">
-        <v>11</v>
-      </c>
-      <c r="E93">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="94" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="E94">
-        <f>SUM(E3:E93)</f>
-        <v>316461</v>
       </c>
     </row>
   </sheetData>
@@ -5090,534 +4603,232 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C1D50FC-F6C6-4A8B-8B80-3E57F2ED5AA6}">
-  <dimension ref="B2:J23"/>
+  <dimension ref="B3:D22"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="11.7109375" customWidth="1"/>
+    <col min="3" max="3" width="22.28515625" customWidth="1"/>
+    <col min="4" max="4" width="10.85546875" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="2" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="C2" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="3" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="C3">
-        <v>105087</v>
+        <v>1020628</v>
+      </c>
+      <c r="C3" t="s">
+        <v>242</v>
       </c>
       <c r="D3" t="s">
-        <v>80</v>
-      </c>
-      <c r="E3">
-        <v>228</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-      <c r="H3">
-        <v>105087</v>
-      </c>
-      <c r="I3" t="s">
-        <v>80</v>
-      </c>
-      <c r="J3">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="4" spans="2:10" x14ac:dyDescent="0.25">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="4" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B4">
-        <v>1</v>
-      </c>
-      <c r="C4">
-        <v>105087</v>
+        <v>1020656</v>
+      </c>
+      <c r="C4" t="s">
+        <v>244</v>
       </c>
       <c r="D4" t="s">
-        <v>66</v>
-      </c>
-      <c r="E4">
-        <v>854</v>
-      </c>
-      <c r="G4">
-        <v>1</v>
-      </c>
-      <c r="H4">
-        <v>105087</v>
-      </c>
-      <c r="I4" t="s">
-        <v>66</v>
-      </c>
-      <c r="J4">
-        <v>666</v>
-      </c>
-    </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.25">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="5" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B5">
-        <v>1</v>
-      </c>
-      <c r="C5">
-        <v>105087</v>
+        <v>1020657</v>
+      </c>
+      <c r="C5" t="s">
+        <v>246</v>
       </c>
       <c r="D5" t="s">
-        <v>62</v>
-      </c>
-      <c r="E5">
-        <v>2228</v>
-      </c>
-      <c r="G5">
-        <v>1</v>
-      </c>
-      <c r="H5">
-        <v>105087</v>
-      </c>
-      <c r="I5" t="s">
-        <v>62</v>
-      </c>
-      <c r="J5">
-        <v>1108</v>
-      </c>
-    </row>
-    <row r="6" spans="2:10" x14ac:dyDescent="0.25">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="6" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B6">
-        <v>2</v>
-      </c>
-      <c r="C6">
-        <v>105654</v>
+        <v>1020731</v>
+      </c>
+      <c r="C6" t="s">
+        <v>247</v>
       </c>
       <c r="D6" t="s">
-        <v>80</v>
-      </c>
-      <c r="E6">
-        <v>122</v>
-      </c>
-      <c r="G6">
-        <v>2</v>
-      </c>
-      <c r="H6">
-        <v>105654</v>
-      </c>
-      <c r="I6" t="s">
-        <v>80</v>
-      </c>
-      <c r="J6">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.25">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="7" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B7">
-        <v>2</v>
-      </c>
-      <c r="C7">
-        <v>105654</v>
+        <v>1020773</v>
+      </c>
+      <c r="C7" t="s">
+        <v>248</v>
       </c>
       <c r="D7" t="s">
-        <v>66</v>
-      </c>
-      <c r="E7">
-        <v>338</v>
-      </c>
-      <c r="G7">
-        <v>2</v>
-      </c>
-      <c r="H7">
-        <v>105654</v>
-      </c>
-      <c r="I7" t="s">
-        <v>66</v>
-      </c>
-      <c r="J7">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="8" spans="2:10" x14ac:dyDescent="0.25">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="8" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B8">
-        <v>2</v>
-      </c>
-      <c r="C8">
-        <v>105654</v>
+        <v>1020863</v>
+      </c>
+      <c r="C8" t="s">
+        <v>249</v>
       </c>
       <c r="D8" t="s">
-        <v>62</v>
-      </c>
-      <c r="E8">
-        <v>668</v>
-      </c>
-      <c r="G8">
-        <v>2</v>
-      </c>
-      <c r="H8">
-        <v>105654</v>
-      </c>
-      <c r="I8" t="s">
-        <v>62</v>
-      </c>
-      <c r="J8">
-        <v>668</v>
-      </c>
-    </row>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.25">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="9" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B9">
-        <v>3</v>
-      </c>
-      <c r="C9">
-        <v>105108</v>
+        <v>1020905</v>
+      </c>
+      <c r="C9" t="s">
+        <v>250</v>
       </c>
       <c r="D9" t="s">
-        <v>80</v>
-      </c>
-      <c r="E9">
-        <v>250</v>
-      </c>
-      <c r="G9">
-        <v>3</v>
-      </c>
-      <c r="H9">
-        <v>105108</v>
-      </c>
-      <c r="I9" t="s">
-        <v>80</v>
-      </c>
-      <c r="J9">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="10" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="G10">
-        <v>3</v>
-      </c>
-      <c r="H10">
-        <v>105108</v>
-      </c>
-      <c r="I10" t="s">
-        <v>66</v>
-      </c>
-      <c r="J10">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="G11">
-        <v>3</v>
-      </c>
-      <c r="H11">
-        <v>105108</v>
-      </c>
-      <c r="I11" t="s">
-        <v>62</v>
-      </c>
-      <c r="J11">
-        <v>477</v>
-      </c>
-    </row>
-    <row r="12" spans="2:10" x14ac:dyDescent="0.25">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="10" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B10">
+        <v>1020914</v>
+      </c>
+      <c r="C10" t="s">
+        <v>251</v>
+      </c>
+      <c r="D10" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="11" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B11">
+        <v>1020916</v>
+      </c>
+      <c r="C11" t="s">
+        <v>252</v>
+      </c>
+      <c r="D11" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="12" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B12">
-        <v>4</v>
-      </c>
-      <c r="C12">
-        <v>105653</v>
+        <v>1020969</v>
+      </c>
+      <c r="C12" t="s">
+        <v>253</v>
       </c>
       <c r="D12" t="s">
-        <v>80</v>
-      </c>
-      <c r="E12">
-        <v>218</v>
-      </c>
-      <c r="G12">
-        <v>4</v>
-      </c>
-      <c r="H12">
-        <v>105653</v>
-      </c>
-      <c r="I12" t="s">
-        <v>80</v>
-      </c>
-      <c r="J12">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="13" spans="2:10" x14ac:dyDescent="0.25">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="13" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B13">
-        <v>4</v>
-      </c>
-      <c r="C13">
-        <v>105653</v>
+        <v>1021062</v>
+      </c>
+      <c r="C13" t="s">
+        <v>254</v>
       </c>
       <c r="D13" t="s">
-        <v>66</v>
-      </c>
-      <c r="E13">
-        <v>438</v>
-      </c>
-      <c r="G13">
-        <v>4</v>
-      </c>
-      <c r="H13">
-        <v>105653</v>
-      </c>
-      <c r="I13" t="s">
-        <v>66</v>
-      </c>
-      <c r="J13">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="14" spans="2:10" x14ac:dyDescent="0.25">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="14" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B14">
-        <v>4</v>
-      </c>
-      <c r="C14">
-        <v>105653</v>
+        <v>1021162</v>
+      </c>
+      <c r="C14" t="s">
+        <v>255</v>
       </c>
       <c r="D14" t="s">
-        <v>62</v>
-      </c>
-      <c r="E14">
-        <v>768</v>
-      </c>
-      <c r="G14">
-        <v>4</v>
-      </c>
-      <c r="H14">
-        <v>105653</v>
-      </c>
-      <c r="I14" t="s">
-        <v>62</v>
-      </c>
-      <c r="J14">
-        <v>668</v>
-      </c>
-    </row>
-    <row r="15" spans="2:10" x14ac:dyDescent="0.25">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="15" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B15">
-        <v>5</v>
-      </c>
-      <c r="C15">
-        <v>105655</v>
+        <v>1021166</v>
+      </c>
+      <c r="C15" t="s">
+        <v>256</v>
       </c>
       <c r="D15" t="s">
-        <v>80</v>
-      </c>
-      <c r="E15">
-        <v>215</v>
-      </c>
-      <c r="G15">
-        <v>5</v>
-      </c>
-      <c r="H15">
-        <v>105655</v>
-      </c>
-      <c r="I15" t="s">
-        <v>80</v>
-      </c>
-      <c r="J15">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="16" spans="2:10" x14ac:dyDescent="0.25">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="16" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B16">
-        <v>5</v>
-      </c>
-      <c r="C16">
-        <v>105655</v>
+        <v>1021227</v>
+      </c>
+      <c r="C16" t="s">
+        <v>257</v>
       </c>
       <c r="D16" t="s">
-        <v>66</v>
-      </c>
-      <c r="E16">
-        <v>435</v>
-      </c>
-      <c r="G16">
-        <v>5</v>
-      </c>
-      <c r="H16">
-        <v>105655</v>
-      </c>
-      <c r="I16" t="s">
-        <v>66</v>
-      </c>
-      <c r="J16">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="17" spans="2:10" x14ac:dyDescent="0.25">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="17" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B17">
-        <v>5</v>
-      </c>
-      <c r="C17">
-        <v>105655</v>
+        <v>1021247</v>
+      </c>
+      <c r="C17" t="s">
+        <v>258</v>
       </c>
       <c r="D17" t="s">
-        <v>62</v>
-      </c>
-      <c r="E17">
-        <v>765</v>
-      </c>
-      <c r="G17">
-        <v>5</v>
-      </c>
-      <c r="H17">
-        <v>105655</v>
-      </c>
-      <c r="I17" t="s">
-        <v>62</v>
-      </c>
-      <c r="J17">
-        <v>765</v>
-      </c>
-    </row>
-    <row r="18" spans="2:10" x14ac:dyDescent="0.25">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="18" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B18">
-        <v>10</v>
-      </c>
-      <c r="C18">
-        <v>105088</v>
+        <v>1021258</v>
+      </c>
+      <c r="C18" t="s">
+        <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>80</v>
-      </c>
-      <c r="E18">
-        <v>110</v>
-      </c>
-      <c r="G18">
-        <v>10</v>
-      </c>
-      <c r="H18">
-        <v>105088</v>
-      </c>
-      <c r="I18" t="s">
-        <v>80</v>
-      </c>
-      <c r="J18">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="19" spans="2:10" x14ac:dyDescent="0.25">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="19" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B19">
-        <v>10</v>
-      </c>
-      <c r="C19">
-        <v>105088</v>
+        <v>1021352</v>
+      </c>
+      <c r="C19" t="s">
+        <v>260</v>
       </c>
       <c r="D19" t="s">
-        <v>66</v>
-      </c>
-      <c r="E19">
-        <v>438</v>
-      </c>
-      <c r="G19">
-        <v>10</v>
-      </c>
-      <c r="H19">
-        <v>105088</v>
-      </c>
-      <c r="I19" t="s">
-        <v>66</v>
-      </c>
-      <c r="J19">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="20" spans="2:10" x14ac:dyDescent="0.25">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="20" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B20">
-        <v>10</v>
-      </c>
-      <c r="C20">
-        <v>105088</v>
+        <v>1021369</v>
+      </c>
+      <c r="C20" t="s">
+        <v>261</v>
       </c>
       <c r="D20" t="s">
-        <v>62</v>
-      </c>
-      <c r="E20">
-        <v>220</v>
-      </c>
-      <c r="G20">
-        <v>10</v>
-      </c>
-      <c r="H20">
-        <v>105088</v>
-      </c>
-      <c r="I20" t="s">
-        <v>62</v>
-      </c>
-      <c r="J20">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="21" spans="2:10" x14ac:dyDescent="0.25">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="21" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B21">
-        <v>10</v>
-      </c>
-      <c r="C21">
-        <v>105089</v>
+        <v>1021437</v>
+      </c>
+      <c r="C21" t="s">
+        <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>80</v>
-      </c>
-      <c r="E21">
-        <v>441</v>
-      </c>
-      <c r="G21">
-        <v>10</v>
-      </c>
-      <c r="H21">
-        <v>105089</v>
-      </c>
-      <c r="I21" t="s">
-        <v>80</v>
-      </c>
-      <c r="J21">
-        <v>441</v>
-      </c>
-    </row>
-    <row r="22" spans="2:10" x14ac:dyDescent="0.25">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="22" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B22">
-        <v>10</v>
-      </c>
-      <c r="C22">
-        <v>105089</v>
+        <v>1021490</v>
+      </c>
+      <c r="C22" t="s">
+        <v>263</v>
       </c>
       <c r="D22" t="s">
-        <v>66</v>
-      </c>
-      <c r="E22">
-        <v>741</v>
-      </c>
-      <c r="G22">
-        <v>10</v>
-      </c>
-      <c r="H22">
-        <v>105089</v>
-      </c>
-      <c r="I22" t="s">
-        <v>66</v>
-      </c>
-      <c r="J22">
-        <v>741</v>
-      </c>
-    </row>
-    <row r="23" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B23">
-        <v>10</v>
-      </c>
-      <c r="C23">
-        <v>105089</v>
-      </c>
-      <c r="D23" t="s">
-        <v>62</v>
-      </c>
-      <c r="E23">
-        <v>2227</v>
-      </c>
-      <c r="G23">
-        <v>10</v>
-      </c>
-      <c r="H23">
-        <v>105089</v>
-      </c>
-      <c r="I23" t="s">
-        <v>62</v>
-      </c>
-      <c r="J23">
-        <v>1227</v>
+        <v>243</v>
       </c>
     </row>
   </sheetData>
@@ -5626,768 +4837,6 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61765B45-3C92-4BC2-B87F-7B61C3132362}">
-  <dimension ref="B2:O35"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="3" max="3" width="28.7109375" customWidth="1"/>
-    <col min="4" max="4" width="30.5703125" customWidth="1"/>
-    <col min="5" max="5" width="18.5703125" customWidth="1"/>
-    <col min="6" max="6" width="15.7109375" customWidth="1"/>
-    <col min="8" max="8" width="16.42578125" customWidth="1"/>
-    <col min="9" max="9" width="27" customWidth="1"/>
-    <col min="10" max="10" width="23.7109375" customWidth="1"/>
-    <col min="11" max="11" width="19.42578125" customWidth="1"/>
-    <col min="12" max="12" width="12.5703125" customWidth="1"/>
-    <col min="13" max="13" width="23.140625" customWidth="1"/>
-    <col min="14" max="14" width="20" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="C2" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="4" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="C4" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="D4" s="7">
-        <v>45487.799317129633</v>
-      </c>
-      <c r="E4" s="6">
-        <v>3474</v>
-      </c>
-      <c r="F4" s="6">
-        <v>3474</v>
-      </c>
-      <c r="H4" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="I4" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="J4" s="7">
-        <v>45487.7969212963</v>
-      </c>
-      <c r="K4" s="6">
-        <v>3474</v>
-      </c>
-      <c r="M4" s="6" t="s">
-        <v>35</v>
-      </c>
-      <c r="N4" s="7">
-        <v>45487.799317129633</v>
-      </c>
-      <c r="O4" s="6">
-        <v>3474</v>
-      </c>
-    </row>
-    <row r="5" spans="2:15" ht="30" x14ac:dyDescent="0.25">
-      <c r="C5" s="6" t="s">
-        <v>203</v>
-      </c>
-      <c r="D5" s="7">
-        <v>45603.933032407411</v>
-      </c>
-      <c r="E5" s="6">
-        <v>7271</v>
-      </c>
-      <c r="H5" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="I5" s="6" t="s">
-        <v>203</v>
-      </c>
-      <c r="J5" s="7">
-        <v>45603.932650462964</v>
-      </c>
-      <c r="K5" s="6">
-        <v>7271</v>
-      </c>
-      <c r="M5" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="N5" s="7">
-        <v>45488.204421296294</v>
-      </c>
-      <c r="O5" s="6">
-        <v>2104</v>
-      </c>
-    </row>
-    <row r="6" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="C6" s="13" t="s">
-        <v>188</v>
-      </c>
-      <c r="D6" s="14">
-        <v>45592.980578703704</v>
-      </c>
-      <c r="E6" s="13">
-        <v>11282</v>
-      </c>
-      <c r="F6" s="15"/>
-      <c r="G6" s="15"/>
-      <c r="H6" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="I6" s="13" t="s">
-        <v>188</v>
-      </c>
-      <c r="J6" s="10">
-        <v>45603.922986111109</v>
-      </c>
-      <c r="K6" s="9">
-        <v>11380</v>
-      </c>
-      <c r="M6" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="N6" s="7">
-        <v>45580.246689814812</v>
-      </c>
-      <c r="O6" s="6">
-        <v>9550</v>
-      </c>
-    </row>
-    <row r="7" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="C7" s="8"/>
-      <c r="D7" s="8"/>
-      <c r="E7" s="8"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8"/>
-      <c r="H7" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="I7" s="9" t="s">
-        <v>45</v>
-      </c>
-      <c r="J7" s="10">
-        <v>45572.001712962963</v>
-      </c>
-      <c r="K7" s="9">
-        <v>3963</v>
-      </c>
-      <c r="M7" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="N7" s="7">
-        <v>45559.065092592595</v>
-      </c>
-      <c r="O7" s="6">
-        <v>11083</v>
-      </c>
-    </row>
-    <row r="8" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="C8" s="8"/>
-      <c r="D8" s="8"/>
-      <c r="E8" s="8"/>
-      <c r="F8" s="8"/>
-      <c r="G8" s="8"/>
-      <c r="H8" s="9" t="s">
-        <v>34</v>
-      </c>
-      <c r="I8" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="J8" s="10">
-        <v>45555.870868055557</v>
-      </c>
-      <c r="K8" s="9">
-        <v>430</v>
-      </c>
-      <c r="M8" s="6" t="s">
-        <v>187</v>
-      </c>
-      <c r="N8" s="7">
-        <v>45585.078321759262</v>
-      </c>
-      <c r="O8" s="6">
-        <v>7216</v>
-      </c>
-    </row>
-    <row r="9" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="H9" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="I9" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="J9" s="7">
-        <v>45568.769444444442</v>
-      </c>
-      <c r="K9" s="6">
-        <v>1370</v>
-      </c>
-      <c r="M9" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="N9" s="7">
-        <v>45585.078958333332</v>
-      </c>
-      <c r="O9" s="6">
-        <v>6691</v>
-      </c>
-    </row>
-    <row r="10" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B10" t="s">
-        <v>206</v>
-      </c>
-      <c r="C10" s="13" t="s">
-        <v>192</v>
-      </c>
-      <c r="D10" s="14">
-        <v>45607.054201388892</v>
-      </c>
-      <c r="E10" s="13">
-        <v>6918</v>
-      </c>
-      <c r="F10" s="15"/>
-      <c r="G10" s="15"/>
-      <c r="H10" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="I10" s="13" t="s">
-        <v>192</v>
-      </c>
-      <c r="J10" s="10">
-        <v>45608.240393518521</v>
-      </c>
-      <c r="K10" s="9">
-        <v>7098</v>
-      </c>
-      <c r="M10" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="N10" s="7">
-        <v>45559.059641203705</v>
-      </c>
-      <c r="O10" s="6">
-        <v>3838</v>
-      </c>
-    </row>
-    <row r="11" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B11" t="s">
-        <v>206</v>
-      </c>
-      <c r="C11" s="15"/>
-      <c r="D11" s="15"/>
-      <c r="E11" s="15"/>
-      <c r="F11" s="15"/>
-      <c r="G11" s="15"/>
-      <c r="H11" s="15"/>
-      <c r="I11" s="13" t="s">
-        <v>204</v>
-      </c>
-      <c r="J11" s="10">
-        <v>45608.240486111114</v>
-      </c>
-      <c r="K11" s="9">
-        <v>4570</v>
-      </c>
-      <c r="M11" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="N11" s="7">
-        <v>45564.562025462961</v>
-      </c>
-      <c r="O11" s="6">
-        <v>2780</v>
-      </c>
-    </row>
-    <row r="12" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B12" t="s">
-        <v>206</v>
-      </c>
-      <c r="C12" s="15"/>
-      <c r="D12" s="15"/>
-      <c r="E12" s="15"/>
-      <c r="F12" s="13">
-        <v>2104</v>
-      </c>
-      <c r="G12" s="15"/>
-      <c r="H12" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="I12" s="13" t="s">
-        <v>205</v>
-      </c>
-      <c r="J12" s="10">
-        <v>45602.928657407407</v>
-      </c>
-      <c r="K12" s="9">
-        <v>5451</v>
-      </c>
-      <c r="M12" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="N12" s="7">
-        <v>45583.870821759258</v>
-      </c>
-      <c r="O12" s="6">
-        <v>2146</v>
-      </c>
-    </row>
-    <row r="13" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="H13" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="I13" s="9" t="s">
-        <v>48</v>
-      </c>
-      <c r="J13" s="10">
-        <v>45562.205208333333</v>
-      </c>
-      <c r="K13" s="9">
-        <v>938</v>
-      </c>
-      <c r="M13" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="N13" s="7">
-        <v>45564.561944444446</v>
-      </c>
-      <c r="O13" s="6">
-        <v>2756</v>
-      </c>
-    </row>
-    <row r="14" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="H14" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="I14" s="9" t="s">
-        <v>49</v>
-      </c>
-      <c r="J14" s="10">
-        <v>45553.747881944444</v>
-      </c>
-      <c r="K14" s="9">
-        <v>1211</v>
-      </c>
-    </row>
-    <row r="15" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="H15" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="I15" s="6" t="s">
-        <v>50</v>
-      </c>
-      <c r="J15" s="7">
-        <v>45488.006921296299</v>
-      </c>
-      <c r="K15" s="6">
-        <v>2192</v>
-      </c>
-    </row>
-    <row r="16" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="C16" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="D16" s="7">
-        <v>45488.204421296294</v>
-      </c>
-      <c r="E16" s="6">
-        <v>2104</v>
-      </c>
-      <c r="F16" s="6">
-        <v>9550</v>
-      </c>
-      <c r="H16" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="I16" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="J16" s="7">
-        <v>45488.089548611111</v>
-      </c>
-      <c r="K16" s="6">
-        <v>2254</v>
-      </c>
-    </row>
-    <row r="17" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="H17" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="I17" s="6" t="s">
-        <v>189</v>
-      </c>
-      <c r="J17" s="7">
-        <v>45587.166886574072</v>
-      </c>
-      <c r="K17" s="6">
-        <v>1801</v>
-      </c>
-    </row>
-    <row r="18" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C18" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="D18" s="7">
-        <v>45598.704918981479</v>
-      </c>
-      <c r="E18" s="6">
-        <v>1654</v>
-      </c>
-      <c r="H18" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="I18" s="6" t="s">
-        <v>51</v>
-      </c>
-      <c r="J18" s="7">
-        <v>45570.907997685186</v>
-      </c>
-      <c r="K18" s="6">
-        <v>1654</v>
-      </c>
-    </row>
-    <row r="19" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C19" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="D19" s="7">
-        <v>45598.705104166664</v>
-      </c>
-      <c r="E19" s="6">
-        <v>1855</v>
-      </c>
-      <c r="H19" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="I19" s="6" t="s">
-        <v>52</v>
-      </c>
-      <c r="J19" s="7">
-        <v>45570.908067129632</v>
-      </c>
-      <c r="K19" s="6">
-        <v>1855</v>
-      </c>
-    </row>
-    <row r="20" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="I20" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="J20" s="10">
-        <v>45561.140324074076</v>
-      </c>
-      <c r="K20" s="9">
-        <v>686</v>
-      </c>
-    </row>
-    <row r="21" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C21" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="D21" s="7">
-        <v>45580.246689814812</v>
-      </c>
-      <c r="E21" s="6">
-        <v>9550</v>
-      </c>
-      <c r="I21" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="J21" s="7">
-        <v>45580.654513888891</v>
-      </c>
-      <c r="K21" s="6">
-        <v>9550</v>
-      </c>
-    </row>
-    <row r="22" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C22" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="D22" s="7">
-        <v>45601.294317129628</v>
-      </c>
-      <c r="E22" s="6">
-        <v>6075</v>
-      </c>
-      <c r="F22" s="6"/>
-      <c r="H22" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="I22" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="J22" s="7">
-        <v>45601.281597222223</v>
-      </c>
-      <c r="K22" s="6">
-        <v>6075</v>
-      </c>
-    </row>
-    <row r="23" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B23" t="s">
-        <v>206</v>
-      </c>
-      <c r="C23" s="15"/>
-      <c r="D23" s="15"/>
-      <c r="E23" s="15"/>
-      <c r="F23" s="15"/>
-      <c r="G23" s="15"/>
-      <c r="H23" s="15"/>
-      <c r="I23" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="J23" s="10">
-        <v>45562.222928240742</v>
-      </c>
-      <c r="K23" s="9">
-        <v>1633</v>
-      </c>
-    </row>
-    <row r="24" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C24" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="D24" s="7">
-        <v>45592.980821759258</v>
-      </c>
-      <c r="E24" s="6">
-        <v>8304</v>
-      </c>
-      <c r="F24" s="6"/>
-      <c r="H24" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="I24" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="J24" s="7">
-        <v>45583.714583333334</v>
-      </c>
-      <c r="K24" s="6">
-        <v>8304</v>
-      </c>
-    </row>
-    <row r="25" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C25" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="D25" s="7">
-        <v>45602.853263888886</v>
-      </c>
-      <c r="E25" s="6">
-        <v>9421</v>
-      </c>
-      <c r="I25" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="J25" s="7">
-        <v>45602.853148148148</v>
-      </c>
-      <c r="K25" s="6">
-        <v>9422</v>
-      </c>
-    </row>
-    <row r="26" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C26" s="6" t="s">
-        <v>187</v>
-      </c>
-      <c r="D26" s="7">
-        <v>45585.078321759262</v>
-      </c>
-      <c r="E26" s="6">
-        <v>7216</v>
-      </c>
-      <c r="I26" s="6" t="s">
-        <v>187</v>
-      </c>
-      <c r="J26" s="7">
-        <v>45587.921111111114</v>
-      </c>
-      <c r="K26" s="6">
-        <v>9421</v>
-      </c>
-    </row>
-    <row r="27" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C27" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="D27" s="7">
-        <v>45592.98133101852</v>
-      </c>
-      <c r="E27" s="6">
-        <v>6691</v>
-      </c>
-      <c r="F27" s="6"/>
-      <c r="H27" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="I27" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="J27" s="7">
-        <v>45582.831134259257</v>
-      </c>
-      <c r="K27" s="6">
-        <v>6691</v>
-      </c>
-    </row>
-    <row r="28" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C28" s="15"/>
-      <c r="D28" s="15"/>
-      <c r="E28" s="15"/>
-      <c r="F28" s="13"/>
-      <c r="G28" s="15"/>
-      <c r="H28" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="I28" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="J28" s="10">
-        <v>45571.087962962964</v>
-      </c>
-      <c r="K28" s="9">
-        <v>4306</v>
-      </c>
-    </row>
-    <row r="29" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C29" s="6" t="s">
-        <v>190</v>
-      </c>
-      <c r="D29" s="7">
-        <v>45592.981458333335</v>
-      </c>
-      <c r="E29" s="6">
-        <v>5118</v>
-      </c>
-      <c r="F29" s="6"/>
-      <c r="H29" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="I29" s="6" t="s">
-        <v>190</v>
-      </c>
-      <c r="J29" s="7">
-        <v>45587.194444444445</v>
-      </c>
-      <c r="K29" s="6">
-        <v>5118</v>
-      </c>
-    </row>
-    <row r="30" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C30" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="D30" s="7">
-        <v>45559.059641203705</v>
-      </c>
-      <c r="E30" s="6">
-        <v>3838</v>
-      </c>
-      <c r="H30" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="I30" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="J30" s="7">
-        <v>45554.139884259261</v>
-      </c>
-      <c r="K30" s="6">
-        <v>3838</v>
-      </c>
-    </row>
-    <row r="31" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C31" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="D31" s="7">
-        <v>45564.562025462961</v>
-      </c>
-      <c r="E31" s="6">
-        <v>2780</v>
-      </c>
-      <c r="F31" s="6"/>
-      <c r="H31" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="I31" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="J31" s="7">
-        <v>45564.561550925922</v>
-      </c>
-      <c r="K31" s="6">
-        <v>2780</v>
-      </c>
-    </row>
-    <row r="32" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="C32" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="D32" s="7">
-        <v>45592.926134259258</v>
-      </c>
-      <c r="E32" s="6">
-        <v>2667</v>
-      </c>
-      <c r="H32" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="I32" s="6" t="s">
-        <v>42</v>
-      </c>
-      <c r="J32" s="7">
-        <v>45587.760914351849</v>
-      </c>
-      <c r="K32" s="6">
-        <v>2667</v>
-      </c>
-    </row>
-    <row r="33" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="I33" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="J33" s="7">
-        <v>45494.86377314815</v>
-      </c>
-      <c r="K33" s="6">
-        <v>3716</v>
-      </c>
-    </row>
-    <row r="34" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="I34" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="J34" s="7">
-        <v>45564.554328703707</v>
-      </c>
-      <c r="K34" s="6">
-        <v>2756</v>
-      </c>
-    </row>
-    <row r="35" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C35" s="6" t="s">
-        <v>43</v>
-      </c>
-      <c r="D35" s="7">
-        <v>45564.561944444446</v>
-      </c>
-      <c r="E35" s="6">
-        <v>2756</v>
-      </c>
-      <c r="I35" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="J35" s="7">
-        <v>45494.09170138889</v>
-      </c>
-      <c r="K35" s="6">
-        <v>3726</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5729499-E483-4C36-94CD-F33C4A49C2B8}">
   <dimension ref="C3:H87"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -6398,13 +4847,13 @@
   <sheetData>
     <row r="3" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C3" s="6" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="D3" s="6">
         <v>9</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="G3" s="6">
         <v>9</v>
@@ -6416,13 +4865,13 @@
     </row>
     <row r="4" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C4" s="6" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="D4" s="6">
         <v>11</v>
       </c>
       <c r="F4" s="6" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="G4" s="6">
         <v>11</v>
@@ -6434,13 +4883,13 @@
     </row>
     <row r="5" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C5" s="6" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="D5" s="6">
         <v>2</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="G5" s="6">
         <v>2</v>
@@ -6452,13 +4901,13 @@
     </row>
     <row r="6" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C6" s="6" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="D6" s="6">
         <v>5</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="G6" s="6">
         <v>5</v>
@@ -6470,13 +4919,13 @@
     </row>
     <row r="7" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C7" s="6" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="D7" s="6">
         <v>6</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="G7" s="6">
         <v>6</v>
@@ -6488,13 +4937,13 @@
     </row>
     <row r="8" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C8" s="6" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="D8" s="6">
         <v>5</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="G8" s="6">
         <v>5</v>
@@ -6506,13 +4955,13 @@
     </row>
     <row r="9" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C9" s="6" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="D9" s="6">
         <v>8</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="G9" s="6">
         <v>8</v>
@@ -6526,7 +4975,7 @@
       <c r="C10" s="6"/>
       <c r="D10" s="6"/>
       <c r="F10" s="6" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="G10" s="6">
         <v>3</v>
@@ -6538,13 +4987,13 @@
     </row>
     <row r="11" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C11" s="6" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="D11" s="6">
         <v>5</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="G11" s="6">
         <v>5</v>
@@ -6556,13 +5005,13 @@
     </row>
     <row r="12" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C12" s="6" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="D12" s="6">
         <v>13</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="G12" s="6">
         <v>13</v>
@@ -6574,13 +5023,13 @@
     </row>
     <row r="13" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C13" s="6" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="D13" s="6">
         <v>4</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="G13" s="6">
         <v>4</v>
@@ -6592,7 +5041,7 @@
     </row>
     <row r="14" spans="3:8" x14ac:dyDescent="0.25">
       <c r="F14" s="6" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="G14" s="6">
         <v>4</v>
@@ -6604,13 +5053,13 @@
     </row>
     <row r="15" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C15" s="6" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="D15" s="6">
         <v>2</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="G15" s="6">
         <v>2</v>
@@ -6622,13 +5071,13 @@
     </row>
     <row r="16" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C16" s="6" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="D16" s="6">
         <v>38</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="G16" s="6">
         <v>38</v>
@@ -6640,13 +5089,13 @@
     </row>
     <row r="17" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C17" s="6" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="D17" s="6">
         <v>13</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="G17" s="6">
         <v>13</v>
@@ -6658,13 +5107,13 @@
     </row>
     <row r="18" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C18" s="6" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="D18" s="6">
         <v>12</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="G18" s="6">
         <v>12</v>
@@ -6676,13 +5125,13 @@
     </row>
     <row r="19" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C19" s="6" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="D19" s="6">
         <v>17</v>
       </c>
       <c r="F19" s="6" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="G19" s="6">
         <v>17</v>
@@ -6694,13 +5143,13 @@
     </row>
     <row r="20" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C20" s="6" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="D20" s="6">
         <v>22</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="G20" s="6">
         <v>22</v>
@@ -6712,13 +5161,13 @@
     </row>
     <row r="21" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C21" s="6" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="D21" s="6">
         <v>26</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
       <c r="G21" s="6">
         <v>26</v>
@@ -6730,13 +5179,13 @@
     </row>
     <row r="22" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C22" s="6" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="D22" s="6">
         <v>23</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="G22" s="6">
         <v>23</v>
@@ -6748,13 +5197,13 @@
     </row>
     <row r="23" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C23" s="6" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="D23" s="6">
         <v>8</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="G23" s="6">
         <v>8</v>
@@ -6766,13 +5215,13 @@
     </row>
     <row r="24" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C24" s="6" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="D24" s="6">
         <v>10</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="G24" s="6">
         <v>10</v>
@@ -6784,13 +5233,13 @@
     </row>
     <row r="25" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C25" s="6" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="D25" s="6">
         <v>10</v>
       </c>
       <c r="F25" s="6" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
       <c r="G25" s="6">
         <v>10</v>
@@ -6802,13 +5251,13 @@
     </row>
     <row r="26" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C26" s="6" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="D26" s="6">
         <v>36</v>
       </c>
       <c r="F26" s="6" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="G26" s="6">
         <v>36</v>
@@ -6822,7 +5271,7 @@
       <c r="C27" s="6"/>
       <c r="D27" s="6"/>
       <c r="F27" s="6" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="G27" s="6">
         <v>32</v>
@@ -6834,13 +5283,13 @@
     </row>
     <row r="28" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C28" s="6" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="D28" s="6">
         <v>16</v>
       </c>
       <c r="F28" s="6" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
       <c r="G28" s="6">
         <v>16</v>
@@ -6852,13 +5301,13 @@
     </row>
     <row r="29" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C29" s="6" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="D29" s="6">
         <v>32</v>
       </c>
       <c r="F29" s="6" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="G29" s="6">
         <v>32</v>
@@ -6870,13 +5319,13 @@
     </row>
     <row r="30" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C30" s="6" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="D30" s="6">
         <v>8</v>
       </c>
       <c r="F30" s="6" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="G30" s="6">
         <v>8</v>
@@ -6888,13 +5337,13 @@
     </row>
     <row r="31" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C31" s="6" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="D31" s="6">
         <v>28</v>
       </c>
       <c r="F31" s="6" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="G31" s="6">
         <v>28</v>
@@ -6906,13 +5355,13 @@
     </row>
     <row r="32" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C32" s="6" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="D32" s="6">
         <v>23</v>
       </c>
       <c r="F32" s="6" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="G32" s="6">
         <v>23</v>
@@ -6924,13 +5373,13 @@
     </row>
     <row r="33" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C33" s="6" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="D33" s="6">
         <v>5</v>
       </c>
       <c r="F33" s="6" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="G33" s="6">
         <v>5</v>
@@ -6942,13 +5391,13 @@
     </row>
     <row r="34" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C34" s="6" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="D34" s="6">
         <v>12</v>
       </c>
       <c r="F34" s="6" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="G34" s="6">
         <v>12</v>
@@ -6960,13 +5409,13 @@
     </row>
     <row r="35" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C35" s="6" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="D35" s="6">
         <v>5</v>
       </c>
       <c r="F35" s="6" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
       <c r="G35" s="6">
         <v>5</v>
@@ -6978,13 +5427,13 @@
     </row>
     <row r="36" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C36" s="6" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="D36" s="6">
         <v>5</v>
       </c>
       <c r="F36" s="6" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="G36" s="6">
         <v>5</v>
@@ -6996,13 +5445,13 @@
     </row>
     <row r="37" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C37" s="6" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="D37" s="6">
         <v>10</v>
       </c>
       <c r="F37" s="6" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="G37" s="6">
         <v>10</v>
@@ -7014,13 +5463,13 @@
     </row>
     <row r="38" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C38" s="6" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="D38" s="6">
         <v>5</v>
       </c>
       <c r="F38" s="6" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="G38" s="6">
         <v>5</v>
@@ -7032,13 +5481,13 @@
     </row>
     <row r="39" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C39" s="6" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="D39" s="6">
         <v>12</v>
       </c>
       <c r="F39" s="6" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="G39" s="6">
         <v>12</v>
@@ -7050,13 +5499,13 @@
     </row>
     <row r="40" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C40" s="6" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="D40" s="6">
         <v>34</v>
       </c>
       <c r="F40" s="6" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="G40" s="6">
         <v>34</v>
@@ -7068,13 +5517,13 @@
     </row>
     <row r="41" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C41" s="6" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="D41" s="6">
         <v>30</v>
       </c>
       <c r="F41" s="6" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="G41" s="6">
         <v>30</v>
@@ -7086,13 +5535,13 @@
     </row>
     <row r="42" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C42" s="6" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="D42" s="6">
         <v>4</v>
       </c>
       <c r="F42" s="6" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="G42" s="6">
         <v>4</v>
@@ -7104,13 +5553,13 @@
     </row>
     <row r="43" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C43" s="6" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="D43" s="6">
         <v>15</v>
       </c>
       <c r="F43" s="6" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
       <c r="G43" s="6">
         <v>15</v>
@@ -7122,13 +5571,13 @@
     </row>
     <row r="44" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C44" s="6" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="D44" s="6">
         <v>8</v>
       </c>
       <c r="F44" s="6" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="G44" s="6">
         <v>8</v>
@@ -7140,13 +5589,13 @@
     </row>
     <row r="45" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C45" s="6" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="D45" s="6">
         <v>17</v>
       </c>
       <c r="F45" s="6" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="G45" s="6">
         <v>17</v>
@@ -7158,13 +5607,13 @@
     </row>
     <row r="46" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C46" s="6" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="D46" s="6">
         <v>3</v>
       </c>
       <c r="F46" s="6" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
       <c r="G46" s="6">
         <v>3</v>
@@ -7176,13 +5625,13 @@
     </row>
     <row r="47" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C47" s="6" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="D47" s="6">
         <v>10</v>
       </c>
       <c r="F47" s="6" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
       <c r="G47" s="6">
         <v>10</v>
@@ -7194,13 +5643,13 @@
     </row>
     <row r="48" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C48" s="6" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="D48" s="6">
         <v>6</v>
       </c>
       <c r="F48" s="6" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
       <c r="G48" s="6">
         <v>6</v>
@@ -7212,13 +5661,13 @@
     </row>
     <row r="49" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C49" s="6" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="D49" s="6">
         <v>5</v>
       </c>
       <c r="F49" s="6" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
       <c r="G49" s="6">
         <v>5</v>
@@ -7230,13 +5679,13 @@
     </row>
     <row r="50" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C50" s="6" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="D50" s="6">
         <v>7</v>
       </c>
       <c r="F50" s="6" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="G50" s="6">
         <v>7</v>
@@ -7248,13 +5697,13 @@
     </row>
     <row r="51" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C51" s="6" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="D51" s="6">
         <v>12</v>
       </c>
       <c r="F51" s="6" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="G51" s="6">
         <v>12</v>
@@ -7266,13 +5715,13 @@
     </row>
     <row r="52" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C52" s="6" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="D52" s="6">
         <v>10</v>
       </c>
       <c r="F52" s="6" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="G52" s="6">
         <v>10</v>
@@ -7284,13 +5733,13 @@
     </row>
     <row r="53" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C53" s="6" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="D53" s="6">
         <v>1</v>
       </c>
       <c r="F53" s="6" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="G53" s="6">
         <v>1</v>
@@ -7302,13 +5751,13 @@
     </row>
     <row r="54" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C54" s="6" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="D54" s="6">
         <v>4</v>
       </c>
       <c r="F54" s="6" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="G54" s="6">
         <v>4</v>
@@ -7320,13 +5769,13 @@
     </row>
     <row r="55" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C55" s="6" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="D55" s="6">
         <v>3</v>
       </c>
       <c r="F55" s="6" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="G55" s="6">
         <v>3</v>
@@ -7338,13 +5787,13 @@
     </row>
     <row r="56" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C56" s="6" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="D56" s="6">
         <v>10</v>
       </c>
       <c r="F56" s="6" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="G56" s="6">
         <v>10</v>
@@ -7356,13 +5805,13 @@
     </row>
     <row r="57" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C57" s="6" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="D57" s="6">
         <v>10</v>
       </c>
       <c r="F57" s="6" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="G57" s="6">
         <v>10</v>
@@ -7374,13 +5823,13 @@
     </row>
     <row r="58" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C58" s="6" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="D58" s="6">
         <v>42</v>
       </c>
       <c r="F58" s="6" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="G58" s="6">
         <v>42</v>
@@ -7392,13 +5841,13 @@
     </row>
     <row r="59" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C59" s="6" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="D59" s="6">
         <v>7</v>
       </c>
       <c r="F59" s="6" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
       <c r="G59" s="6">
         <v>7</v>
@@ -7410,13 +5859,13 @@
     </row>
     <row r="60" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C60" s="6" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="D60" s="6">
         <v>10</v>
       </c>
       <c r="F60" s="6" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
       <c r="G60" s="6">
         <v>10</v>
@@ -7428,13 +5877,13 @@
     </row>
     <row r="61" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C61" s="6" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="D61" s="6">
         <v>9</v>
       </c>
       <c r="F61" s="6" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="G61" s="6">
         <v>9</v>
@@ -7446,13 +5895,13 @@
     </row>
     <row r="62" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C62" s="6" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="D62" s="6">
         <v>10</v>
       </c>
       <c r="F62" s="6" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
       <c r="G62" s="6">
         <v>10</v>
@@ -7464,13 +5913,13 @@
     </row>
     <row r="63" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C63" s="6" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="D63" s="6">
         <v>9</v>
       </c>
       <c r="F63" s="6" t="s">
-        <v>162</v>
+        <v>157</v>
       </c>
       <c r="G63" s="6">
         <v>9</v>
@@ -7482,13 +5931,13 @@
     </row>
     <row r="64" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C64" s="6" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="D64" s="6">
         <v>11</v>
       </c>
       <c r="F64" s="6" t="s">
-        <v>163</v>
+        <v>158</v>
       </c>
       <c r="G64" s="6">
         <v>11</v>
@@ -7500,13 +5949,13 @@
     </row>
     <row r="65" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C65" s="6" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="D65" s="6">
         <v>13</v>
       </c>
       <c r="F65" s="6" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="G65" s="6">
         <v>13</v>
@@ -7518,13 +5967,13 @@
     </row>
     <row r="66" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C66" s="6" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="D66" s="6">
         <v>20</v>
       </c>
       <c r="F66" s="6" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
       <c r="G66" s="6">
         <v>20</v>
@@ -7536,13 +5985,13 @@
     </row>
     <row r="67" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C67" s="6" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="D67" s="6">
         <v>10</v>
       </c>
       <c r="F67" s="6" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="G67" s="6">
         <v>10</v>
@@ -7554,13 +6003,13 @@
     </row>
     <row r="68" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C68" s="6" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="D68" s="6">
         <v>10</v>
       </c>
       <c r="F68" s="6" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="G68" s="6">
         <v>10</v>
@@ -7572,13 +6021,13 @@
     </row>
     <row r="69" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C69" s="6" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="D69" s="6">
         <v>3</v>
       </c>
       <c r="F69" s="6" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="G69" s="6">
         <v>3</v>
@@ -7590,13 +6039,13 @@
     </row>
     <row r="70" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C70" s="6" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="D70" s="6">
         <v>7</v>
       </c>
       <c r="F70" s="6" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="G70" s="6">
         <v>7</v>
@@ -7608,13 +6057,13 @@
     </row>
     <row r="71" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C71" s="6" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="D71" s="6">
         <v>8</v>
       </c>
       <c r="F71" s="6" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="G71" s="6">
         <v>8</v>
@@ -7626,13 +6075,13 @@
     </row>
     <row r="72" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C72" s="6" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="D72" s="6">
         <v>3</v>
       </c>
       <c r="F72" s="6" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="G72" s="6">
         <v>3</v>
@@ -7644,13 +6093,13 @@
     </row>
     <row r="73" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C73" s="6" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="D73" s="6">
         <v>2</v>
       </c>
       <c r="F73" s="6" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="G73" s="6">
         <v>2</v>
@@ -7662,13 +6111,13 @@
     </row>
     <row r="74" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C74" s="6" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="D74" s="6">
         <v>7</v>
       </c>
       <c r="F74" s="6" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="G74" s="6">
         <v>7</v>
@@ -7680,13 +6129,13 @@
     </row>
     <row r="75" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C75" s="6" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="D75" s="6">
         <v>5</v>
       </c>
       <c r="F75" s="6" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="G75" s="6">
         <v>5</v>
@@ -7698,13 +6147,13 @@
     </row>
     <row r="76" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C76" s="6" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="D76" s="6">
         <v>5</v>
       </c>
       <c r="F76" s="6" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="G76" s="6">
         <v>5</v>
@@ -7716,13 +6165,13 @@
     </row>
     <row r="77" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C77" s="6" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="D77" s="6">
         <v>21</v>
       </c>
       <c r="F77" s="6" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="G77" s="6">
         <v>21</v>
@@ -7734,13 +6183,13 @@
     </row>
     <row r="78" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C78" s="6" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="D78" s="6">
         <v>19</v>
       </c>
       <c r="F78" s="6" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="G78" s="6">
         <v>19</v>
@@ -7752,13 +6201,13 @@
     </row>
     <row r="79" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C79" s="6" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="D79" s="6">
         <v>21</v>
       </c>
       <c r="F79" s="6" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="G79" s="6">
         <v>21</v>
@@ -7770,7 +6219,7 @@
     </row>
     <row r="80" spans="3:8" x14ac:dyDescent="0.25">
       <c r="F80" s="6" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="G80" s="6">
         <v>21</v>
@@ -7782,7 +6231,7 @@
     </row>
     <row r="81" spans="3:8" x14ac:dyDescent="0.25">
       <c r="F81" s="6" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="G81" s="6">
         <v>19</v>
@@ -7794,13 +6243,13 @@
     </row>
     <row r="82" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C82" s="6" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="D82" s="6">
         <v>19</v>
       </c>
       <c r="F82" s="6" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="G82" s="6">
         <v>19</v>
@@ -7812,7 +6261,7 @@
     </row>
     <row r="83" spans="3:8" x14ac:dyDescent="0.25">
       <c r="F83" s="6" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="G83" s="6">
         <v>19</v>
@@ -7824,13 +6273,13 @@
     </row>
     <row r="84" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C84" s="6" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="D84" s="6">
         <v>3</v>
       </c>
       <c r="F84" s="6" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="G84" s="6">
         <v>3</v>
@@ -7842,13 +6291,13 @@
     </row>
     <row r="85" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C85" s="6" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="D85" s="6">
         <v>6</v>
       </c>
       <c r="F85" s="6" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="G85" s="6">
         <v>6</v>
@@ -7860,13 +6309,13 @@
     </row>
     <row r="86" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C86" s="6" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="D86" s="6">
         <v>18</v>
       </c>
       <c r="F86" s="6" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="G86" s="6">
         <v>18</v>
@@ -7878,13 +6327,13 @@
     </row>
     <row r="87" spans="3:8" x14ac:dyDescent="0.25">
       <c r="C87" s="6" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="D87" s="6">
         <v>18</v>
       </c>
       <c r="F87" s="6" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="G87" s="6">
         <v>18</v>

--- a/OPNT Docs/ToDoList.xlsx
+++ b/OPNT Docs/ToDoList.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\AST\GitHub\opnt\OPNT Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D32FB3CD-7885-4819-BE33-D220A9C68C9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96E13791-D036-4CDE-BF56-78249AFB18F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="4" xr2:uid="{C4C29C9D-7A78-44C9-A11D-2D7769206FE1}"/>
+    <workbookView xWindow="1070" yWindow="3190" windowWidth="21490" windowHeight="11130" firstSheet="1" activeTab="6" xr2:uid="{C4C29C9D-7A78-44C9-A11D-2D7769206FE1}"/>
   </bookViews>
   <sheets>
     <sheet name="PROC COMPARE (2)" sheetId="10" r:id="rId1"/>
@@ -23,6 +23,7 @@
     <sheet name="OBJECT COMPARE" sheetId="5" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -43,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="524" uniqueCount="298">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="605" uniqueCount="343">
   <si>
     <t>OPINITO TO DO LIST</t>
   </si>
@@ -943,6 +944,141 @@
   </si>
   <si>
     <t>CCODE</t>
+  </si>
+  <si>
+    <t>indo54</t>
+  </si>
+  <si>
+    <t>PROMODI</t>
+  </si>
+  <si>
+    <t>indo290</t>
+  </si>
+  <si>
+    <t>indo1239</t>
+  </si>
+  <si>
+    <t>indo1418</t>
+  </si>
+  <si>
+    <t>indo1513</t>
+  </si>
+  <si>
+    <t>indo1652</t>
+  </si>
+  <si>
+    <t>indo2290</t>
+  </si>
+  <si>
+    <t>indo2663</t>
+  </si>
+  <si>
+    <t>indo2793</t>
+  </si>
+  <si>
+    <t>indo2856</t>
+  </si>
+  <si>
+    <t>indo3050</t>
+  </si>
+  <si>
+    <t>ANTIMODI</t>
+  </si>
+  <si>
+    <t>indo3174</t>
+  </si>
+  <si>
+    <t>indo3344</t>
+  </si>
+  <si>
+    <t>indo3457</t>
+  </si>
+  <si>
+    <t>indo3572</t>
+  </si>
+  <si>
+    <t>indo3618</t>
+  </si>
+  <si>
+    <t>indo3757</t>
+  </si>
+  <si>
+    <t>indo3818</t>
+  </si>
+  <si>
+    <t>indo3930</t>
+  </si>
+  <si>
+    <t>ast05281i</t>
+  </si>
+  <si>
+    <t>OU1000061</t>
+  </si>
+  <si>
+    <t>DEM</t>
+  </si>
+  <si>
+    <t>OU1000260</t>
+  </si>
+  <si>
+    <t>OU1000284</t>
+  </si>
+  <si>
+    <t>OU1002254</t>
+  </si>
+  <si>
+    <t>OU1002376</t>
+  </si>
+  <si>
+    <t>OU1002618</t>
+  </si>
+  <si>
+    <t>OU1002919</t>
+  </si>
+  <si>
+    <t>OU1003109</t>
+  </si>
+  <si>
+    <t>OU1003144</t>
+  </si>
+  <si>
+    <t>OU1003932</t>
+  </si>
+  <si>
+    <t>OU1004049</t>
+  </si>
+  <si>
+    <t>REPUB</t>
+  </si>
+  <si>
+    <t>OU1004556</t>
+  </si>
+  <si>
+    <t>OU1004618</t>
+  </si>
+  <si>
+    <t>OU1004696</t>
+  </si>
+  <si>
+    <t>OU1005034</t>
+  </si>
+  <si>
+    <t>OU1005357</t>
+  </si>
+  <si>
+    <t>OU1006024</t>
+  </si>
+  <si>
+    <t>OU1006124</t>
+  </si>
+  <si>
+    <t>OU1006482</t>
+  </si>
+  <si>
+    <t>OU1007125</t>
+  </si>
+  <si>
+    <t>TID</t>
   </si>
 </sst>
 </file>
@@ -999,7 +1135,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -1026,13 +1162,6 @@
     <xf numFmtId="22" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1389,7 +1518,7 @@
       </c>
     </row>
     <row r="4" spans="3:15" x14ac:dyDescent="0.25">
-      <c r="C4" s="10" t="s">
+      <c r="C4" s="6" t="s">
         <v>34</v>
       </c>
       <c r="D4" s="7">
@@ -1403,7 +1532,7 @@
         <f>E4-K4</f>
         <v>0</v>
       </c>
-      <c r="H4" s="11"/>
+      <c r="H4" s="6"/>
       <c r="I4" s="6" t="s">
         <v>34</v>
       </c>
@@ -1427,7 +1556,7 @@
         <f t="shared" ref="G5:G39" si="0">E5-K5</f>
         <v>-1267</v>
       </c>
-      <c r="H5" s="11"/>
+      <c r="H5" s="6"/>
       <c r="I5" s="6" t="s">
         <v>240</v>
       </c>
@@ -1446,7 +1575,7 @@
       </c>
     </row>
     <row r="6" spans="3:15" x14ac:dyDescent="0.25">
-      <c r="C6" s="10" t="s">
+      <c r="C6" s="6" t="s">
         <v>197</v>
       </c>
       <c r="D6" s="7">
@@ -1460,7 +1589,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H6" s="11"/>
+      <c r="H6" s="6"/>
       <c r="I6" s="6" t="s">
         <v>197</v>
       </c>
@@ -1479,7 +1608,7 @@
       </c>
     </row>
     <row r="7" spans="3:15" x14ac:dyDescent="0.25">
-      <c r="C7" s="10" t="s">
+      <c r="C7" s="6" t="s">
         <v>183</v>
       </c>
       <c r="D7" s="7">
@@ -1493,7 +1622,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H7" s="11"/>
+      <c r="H7" s="6"/>
       <c r="I7" s="6" t="s">
         <v>183</v>
       </c>
@@ -1512,7 +1641,7 @@
       </c>
     </row>
     <row r="8" spans="3:15" x14ac:dyDescent="0.25">
-      <c r="C8" s="10" t="s">
+      <c r="C8" s="6" t="s">
         <v>233</v>
       </c>
       <c r="D8" s="7">
@@ -1526,7 +1655,7 @@
         <f t="shared" si="0"/>
         <v>305</v>
       </c>
-      <c r="H8" s="11"/>
+      <c r="H8" s="6"/>
       <c r="I8" s="6" t="s">
         <v>233</v>
       </c>
@@ -1545,7 +1674,7 @@
       </c>
     </row>
     <row r="9" spans="3:15" x14ac:dyDescent="0.25">
-      <c r="C9" s="10" t="s">
+      <c r="C9" s="6" t="s">
         <v>234</v>
       </c>
       <c r="D9" s="7">
@@ -1559,7 +1688,7 @@
         <f t="shared" si="0"/>
         <v>126</v>
       </c>
-      <c r="H9" s="11"/>
+      <c r="H9" s="6"/>
       <c r="I9" s="6" t="s">
         <v>234</v>
       </c>
@@ -1578,7 +1707,7 @@
       </c>
     </row>
     <row r="10" spans="3:15" x14ac:dyDescent="0.25">
-      <c r="C10" s="10" t="s">
+      <c r="C10" s="6" t="s">
         <v>44</v>
       </c>
       <c r="D10" s="7">
@@ -1592,7 +1721,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H10" s="11"/>
+      <c r="H10" s="6"/>
       <c r="I10" s="6" t="s">
         <v>44</v>
       </c>
@@ -1611,7 +1740,7 @@
       </c>
     </row>
     <row r="11" spans="3:15" x14ac:dyDescent="0.25">
-      <c r="C11" s="10" t="s">
+      <c r="C11" s="6" t="s">
         <v>235</v>
       </c>
       <c r="D11" s="7">
@@ -1625,7 +1754,6 @@
         <f t="shared" si="0"/>
         <v>-202</v>
       </c>
-      <c r="H11" s="12"/>
       <c r="I11" s="6" t="s">
         <v>235</v>
       </c>
@@ -1644,7 +1772,7 @@
       </c>
     </row>
     <row r="12" spans="3:15" x14ac:dyDescent="0.25">
-      <c r="C12" s="10" t="s">
+      <c r="C12" s="6" t="s">
         <v>45</v>
       </c>
       <c r="D12" s="7">
@@ -1658,7 +1786,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H12" s="11"/>
+      <c r="H12" s="6"/>
       <c r="I12" s="6" t="s">
         <v>45</v>
       </c>
@@ -1677,7 +1805,7 @@
       </c>
     </row>
     <row r="13" spans="3:15" x14ac:dyDescent="0.25">
-      <c r="C13" s="10" t="s">
+      <c r="C13" s="6" t="s">
         <v>186</v>
       </c>
       <c r="D13" s="7">
@@ -1691,7 +1819,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H13" s="11"/>
+      <c r="H13" s="6"/>
       <c r="I13" s="6" t="s">
         <v>186</v>
       </c>
@@ -1710,7 +1838,7 @@
       </c>
     </row>
     <row r="14" spans="3:15" x14ac:dyDescent="0.25">
-      <c r="C14" s="10" t="s">
+      <c r="C14" s="6" t="s">
         <v>198</v>
       </c>
       <c r="D14" s="7">
@@ -1723,7 +1851,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H14" s="11"/>
+      <c r="H14" s="6"/>
       <c r="I14" s="6" t="s">
         <v>198</v>
       </c>
@@ -1735,7 +1863,7 @@
       </c>
     </row>
     <row r="15" spans="3:15" x14ac:dyDescent="0.25">
-      <c r="C15" s="10" t="s">
+      <c r="C15" s="6" t="s">
         <v>199</v>
       </c>
       <c r="D15" s="7">
@@ -1749,7 +1877,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H15" s="11"/>
+      <c r="H15" s="6"/>
       <c r="I15" s="6" t="s">
         <v>199</v>
       </c>
@@ -1761,7 +1889,7 @@
       </c>
     </row>
     <row r="16" spans="3:15" x14ac:dyDescent="0.25">
-      <c r="C16" s="10" t="s">
+      <c r="C16" s="6" t="s">
         <v>46</v>
       </c>
       <c r="D16" s="7">
@@ -1775,7 +1903,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H16" s="11"/>
+      <c r="H16" s="6"/>
       <c r="I16" s="6" t="s">
         <v>46</v>
       </c>
@@ -1787,7 +1915,7 @@
       </c>
     </row>
     <row r="17" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C17" s="10" t="s">
+      <c r="C17" s="6" t="s">
         <v>236</v>
       </c>
       <c r="D17" s="7">
@@ -1801,7 +1929,7 @@
         <f t="shared" si="0"/>
         <v>-114</v>
       </c>
-      <c r="H17" s="11"/>
+      <c r="H17" s="6"/>
       <c r="I17" s="6" t="s">
         <v>236</v>
       </c>
@@ -1813,7 +1941,7 @@
       </c>
     </row>
     <row r="18" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C18" s="10" t="s">
+      <c r="C18" s="6" t="s">
         <v>237</v>
       </c>
       <c r="D18" s="7">
@@ -1827,7 +1955,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H18" s="11"/>
+      <c r="H18" s="6"/>
       <c r="I18" s="6" t="s">
         <v>237</v>
       </c>
@@ -1839,7 +1967,7 @@
       </c>
     </row>
     <row r="19" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C19" s="10" t="s">
+      <c r="C19" s="6" t="s">
         <v>238</v>
       </c>
       <c r="D19" s="7">
@@ -1853,7 +1981,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H19" s="11"/>
+      <c r="H19" s="6"/>
       <c r="I19" s="6" t="s">
         <v>238</v>
       </c>
@@ -1865,7 +1993,7 @@
       </c>
     </row>
     <row r="20" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C20" s="10" t="s">
+      <c r="C20" s="6" t="s">
         <v>47</v>
       </c>
       <c r="D20" s="7">
@@ -1879,7 +2007,6 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H20" s="12"/>
       <c r="I20" s="6" t="s">
         <v>47</v>
       </c>
@@ -1891,7 +2018,7 @@
       </c>
     </row>
     <row r="21" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C21" s="10" t="s">
+      <c r="C21" s="6" t="s">
         <v>239</v>
       </c>
       <c r="D21" s="7">
@@ -1905,7 +2032,6 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H21" s="12"/>
       <c r="I21" s="6" t="s">
         <v>239</v>
       </c>
@@ -1917,7 +2043,7 @@
       </c>
     </row>
     <row r="22" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C22" s="10" t="s">
+      <c r="C22" s="6" t="s">
         <v>35</v>
       </c>
       <c r="D22" s="7">
@@ -1931,7 +2057,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H22" s="11"/>
+      <c r="H22" s="6"/>
       <c r="I22" s="6" t="s">
         <v>35</v>
       </c>
@@ -1943,7 +2069,7 @@
       </c>
     </row>
     <row r="23" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C23" s="10" t="s">
+      <c r="C23" s="6" t="s">
         <v>48</v>
       </c>
       <c r="D23" s="7">
@@ -1957,7 +2083,6 @@
         <f t="shared" si="0"/>
         <v>270</v>
       </c>
-      <c r="H23" s="12"/>
       <c r="I23" s="6" t="s">
         <v>48</v>
       </c>
@@ -1969,7 +2094,7 @@
       </c>
     </row>
     <row r="24" spans="3:11" x14ac:dyDescent="0.25">
-      <c r="C24" s="10" t="s">
+      <c r="C24" s="6" t="s">
         <v>49</v>
       </c>
       <c r="D24" s="7">
@@ -1983,7 +2108,7 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H24" s="11"/>
+      <c r="H24" s="6"/>
       <c r="I24" s="6" t="s">
         <v>49</v>
       </c>
@@ -2009,7 +2134,6 @@
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="H25" s="12"/>
       <c r="I25" s="6" t="s">
         <v>50</v>
       </c>
@@ -4603,7 +4727,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C1D50FC-F6C6-4A8B-8B80-3E57F2ED5AA6}">
-  <dimension ref="B3:D22"/>
+  <dimension ref="B2:E64"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="11.7109375" customWidth="1"/>
@@ -4611,7 +4735,12 @@
     <col min="4" max="4" width="10.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="E2" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="3" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B3">
         <v>1020628</v>
       </c>
@@ -4621,8 +4750,11 @@
       <c r="D3" t="s">
         <v>243</v>
       </c>
-    </row>
-    <row r="4" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="E3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B4">
         <v>1020656</v>
       </c>
@@ -4632,8 +4764,11 @@
       <c r="D4" t="s">
         <v>245</v>
       </c>
-    </row>
-    <row r="5" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="E4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B5">
         <v>1020657</v>
       </c>
@@ -4643,8 +4778,11 @@
       <c r="D5" t="s">
         <v>245</v>
       </c>
-    </row>
-    <row r="6" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="E5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B6">
         <v>1020731</v>
       </c>
@@ -4654,8 +4792,11 @@
       <c r="D6" t="s">
         <v>243</v>
       </c>
-    </row>
-    <row r="7" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="E6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B7">
         <v>1020773</v>
       </c>
@@ -4665,8 +4806,11 @@
       <c r="D7" t="s">
         <v>245</v>
       </c>
-    </row>
-    <row r="8" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="E7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B8">
         <v>1020863</v>
       </c>
@@ -4676,8 +4820,11 @@
       <c r="D8" t="s">
         <v>245</v>
       </c>
-    </row>
-    <row r="9" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="E8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B9">
         <v>1020905</v>
       </c>
@@ -4687,8 +4834,11 @@
       <c r="D9" t="s">
         <v>243</v>
       </c>
-    </row>
-    <row r="10" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="E9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B10">
         <v>1020914</v>
       </c>
@@ -4698,8 +4848,11 @@
       <c r="D10" t="s">
         <v>243</v>
       </c>
-    </row>
-    <row r="11" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="E10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B11">
         <v>1020916</v>
       </c>
@@ -4709,8 +4862,11 @@
       <c r="D11" t="s">
         <v>245</v>
       </c>
-    </row>
-    <row r="12" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="E11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B12">
         <v>1020969</v>
       </c>
@@ -4720,8 +4876,11 @@
       <c r="D12" t="s">
         <v>245</v>
       </c>
-    </row>
-    <row r="13" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="E12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B13">
         <v>1021062</v>
       </c>
@@ -4731,8 +4890,11 @@
       <c r="D13" t="s">
         <v>243</v>
       </c>
-    </row>
-    <row r="14" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="E13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B14">
         <v>1021162</v>
       </c>
@@ -4742,8 +4904,11 @@
       <c r="D14" t="s">
         <v>245</v>
       </c>
-    </row>
-    <row r="15" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="E14">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B15">
         <v>1021166</v>
       </c>
@@ -4753,8 +4918,11 @@
       <c r="D15" t="s">
         <v>243</v>
       </c>
-    </row>
-    <row r="16" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="E15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B16">
         <v>1021227</v>
       </c>
@@ -4764,8 +4932,11 @@
       <c r="D16" t="s">
         <v>245</v>
       </c>
-    </row>
-    <row r="17" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="E16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B17">
         <v>1021247</v>
       </c>
@@ -4775,8 +4946,11 @@
       <c r="D17" t="s">
         <v>243</v>
       </c>
-    </row>
-    <row r="18" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="E17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B18">
         <v>1021258</v>
       </c>
@@ -4786,8 +4960,11 @@
       <c r="D18" t="s">
         <v>245</v>
       </c>
-    </row>
-    <row r="19" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="E18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B19">
         <v>1021352</v>
       </c>
@@ -4797,8 +4974,11 @@
       <c r="D19" t="s">
         <v>243</v>
       </c>
-    </row>
-    <row r="20" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="E19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B20">
         <v>1021369</v>
       </c>
@@ -4808,8 +4988,11 @@
       <c r="D20" t="s">
         <v>245</v>
       </c>
-    </row>
-    <row r="21" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="E20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B21">
         <v>1021437</v>
       </c>
@@ -4819,8 +5002,11 @@
       <c r="D21" t="s">
         <v>243</v>
       </c>
-    </row>
-    <row r="22" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="E21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B22">
         <v>1021490</v>
       </c>
@@ -4829,6 +5015,569 @@
       </c>
       <c r="D22" t="s">
         <v>243</v>
+      </c>
+      <c r="E22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B24">
+        <v>1016054</v>
+      </c>
+      <c r="C24" t="s">
+        <v>298</v>
+      </c>
+      <c r="D24" t="s">
+        <v>299</v>
+      </c>
+      <c r="E24">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B25">
+        <v>1016290</v>
+      </c>
+      <c r="C25" t="s">
+        <v>300</v>
+      </c>
+      <c r="D25" t="s">
+        <v>299</v>
+      </c>
+      <c r="E25">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B26">
+        <v>1017239</v>
+      </c>
+      <c r="C26" t="s">
+        <v>301</v>
+      </c>
+      <c r="D26" t="s">
+        <v>299</v>
+      </c>
+      <c r="E26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B27">
+        <v>1017418</v>
+      </c>
+      <c r="C27" t="s">
+        <v>302</v>
+      </c>
+      <c r="D27" t="s">
+        <v>299</v>
+      </c>
+      <c r="E27">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B28">
+        <v>1017513</v>
+      </c>
+      <c r="C28" t="s">
+        <v>303</v>
+      </c>
+      <c r="D28" t="s">
+        <v>299</v>
+      </c>
+      <c r="E28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B29">
+        <v>1017652</v>
+      </c>
+      <c r="C29" t="s">
+        <v>304</v>
+      </c>
+      <c r="D29" t="s">
+        <v>299</v>
+      </c>
+      <c r="E29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B30">
+        <v>1018290</v>
+      </c>
+      <c r="C30" t="s">
+        <v>305</v>
+      </c>
+      <c r="D30" t="s">
+        <v>299</v>
+      </c>
+      <c r="E30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B31">
+        <v>1018663</v>
+      </c>
+      <c r="C31" t="s">
+        <v>306</v>
+      </c>
+      <c r="D31" t="s">
+        <v>299</v>
+      </c>
+      <c r="E31">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B32">
+        <v>1018793</v>
+      </c>
+      <c r="C32" t="s">
+        <v>307</v>
+      </c>
+      <c r="D32" t="s">
+        <v>299</v>
+      </c>
+      <c r="E32">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B33">
+        <v>1018856</v>
+      </c>
+      <c r="C33" t="s">
+        <v>308</v>
+      </c>
+      <c r="D33" t="s">
+        <v>299</v>
+      </c>
+      <c r="E33">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B34">
+        <v>1019050</v>
+      </c>
+      <c r="C34" t="s">
+        <v>309</v>
+      </c>
+      <c r="D34" t="s">
+        <v>310</v>
+      </c>
+      <c r="E34">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B35">
+        <v>1019174</v>
+      </c>
+      <c r="C35" t="s">
+        <v>311</v>
+      </c>
+      <c r="D35" t="s">
+        <v>310</v>
+      </c>
+      <c r="E35">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B36">
+        <v>1019344</v>
+      </c>
+      <c r="C36" t="s">
+        <v>312</v>
+      </c>
+      <c r="D36" t="s">
+        <v>310</v>
+      </c>
+      <c r="E36">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B37">
+        <v>1019457</v>
+      </c>
+      <c r="C37" t="s">
+        <v>313</v>
+      </c>
+      <c r="D37" t="s">
+        <v>310</v>
+      </c>
+      <c r="E37">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B38">
+        <v>1019572</v>
+      </c>
+      <c r="C38" t="s">
+        <v>314</v>
+      </c>
+      <c r="D38" t="s">
+        <v>310</v>
+      </c>
+      <c r="E38">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B39">
+        <v>1019618</v>
+      </c>
+      <c r="C39" t="s">
+        <v>315</v>
+      </c>
+      <c r="D39" t="s">
+        <v>310</v>
+      </c>
+      <c r="E39">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B40">
+        <v>1019757</v>
+      </c>
+      <c r="C40" t="s">
+        <v>316</v>
+      </c>
+      <c r="D40" t="s">
+        <v>310</v>
+      </c>
+      <c r="E40">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B41">
+        <v>1019818</v>
+      </c>
+      <c r="C41" t="s">
+        <v>317</v>
+      </c>
+      <c r="D41" t="s">
+        <v>310</v>
+      </c>
+      <c r="E41">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B42">
+        <v>1019930</v>
+      </c>
+      <c r="C42" t="s">
+        <v>318</v>
+      </c>
+      <c r="D42" t="s">
+        <v>310</v>
+      </c>
+      <c r="E42">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B43">
+        <v>1020333</v>
+      </c>
+      <c r="C43" t="s">
+        <v>319</v>
+      </c>
+      <c r="D43" t="s">
+        <v>310</v>
+      </c>
+      <c r="E43">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B45">
+        <v>1000061</v>
+      </c>
+      <c r="C45" t="s">
+        <v>320</v>
+      </c>
+      <c r="D45" t="s">
+        <v>321</v>
+      </c>
+      <c r="E45">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B46">
+        <v>1000260</v>
+      </c>
+      <c r="C46" t="s">
+        <v>322</v>
+      </c>
+      <c r="D46" t="s">
+        <v>321</v>
+      </c>
+      <c r="E46">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B47">
+        <v>1000284</v>
+      </c>
+      <c r="C47" t="s">
+        <v>323</v>
+      </c>
+      <c r="D47" t="s">
+        <v>321</v>
+      </c>
+      <c r="E47">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B48">
+        <v>1002254</v>
+      </c>
+      <c r="C48" t="s">
+        <v>324</v>
+      </c>
+      <c r="D48" t="s">
+        <v>321</v>
+      </c>
+      <c r="E48">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B49">
+        <v>1002376</v>
+      </c>
+      <c r="C49" t="s">
+        <v>325</v>
+      </c>
+      <c r="D49" t="s">
+        <v>321</v>
+      </c>
+      <c r="E49">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B50">
+        <v>1002618</v>
+      </c>
+      <c r="C50" t="s">
+        <v>326</v>
+      </c>
+      <c r="D50" t="s">
+        <v>321</v>
+      </c>
+      <c r="E50">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B51">
+        <v>1002919</v>
+      </c>
+      <c r="C51" t="s">
+        <v>327</v>
+      </c>
+      <c r="D51" t="s">
+        <v>321</v>
+      </c>
+      <c r="E51">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B52">
+        <v>1003109</v>
+      </c>
+      <c r="C52" t="s">
+        <v>328</v>
+      </c>
+      <c r="D52" t="s">
+        <v>321</v>
+      </c>
+      <c r="E52">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B53">
+        <v>1003144</v>
+      </c>
+      <c r="C53" t="s">
+        <v>329</v>
+      </c>
+      <c r="D53" t="s">
+        <v>321</v>
+      </c>
+      <c r="E53">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B54">
+        <v>1003932</v>
+      </c>
+      <c r="C54" t="s">
+        <v>330</v>
+      </c>
+      <c r="D54" t="s">
+        <v>321</v>
+      </c>
+      <c r="E54">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B55">
+        <v>1004049</v>
+      </c>
+      <c r="C55" t="s">
+        <v>331</v>
+      </c>
+      <c r="D55" t="s">
+        <v>332</v>
+      </c>
+      <c r="E55">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B56">
+        <v>1004556</v>
+      </c>
+      <c r="C56" t="s">
+        <v>333</v>
+      </c>
+      <c r="D56" t="s">
+        <v>332</v>
+      </c>
+      <c r="E56">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B57">
+        <v>1004618</v>
+      </c>
+      <c r="C57" t="s">
+        <v>334</v>
+      </c>
+      <c r="D57" t="s">
+        <v>332</v>
+      </c>
+      <c r="E57">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B58">
+        <v>1004696</v>
+      </c>
+      <c r="C58" t="s">
+        <v>335</v>
+      </c>
+      <c r="D58" t="s">
+        <v>332</v>
+      </c>
+      <c r="E58">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B59">
+        <v>1005034</v>
+      </c>
+      <c r="C59" t="s">
+        <v>336</v>
+      </c>
+      <c r="D59" t="s">
+        <v>332</v>
+      </c>
+      <c r="E59">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B60">
+        <v>1005357</v>
+      </c>
+      <c r="C60" t="s">
+        <v>337</v>
+      </c>
+      <c r="D60" t="s">
+        <v>332</v>
+      </c>
+      <c r="E60">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B61">
+        <v>1006024</v>
+      </c>
+      <c r="C61" t="s">
+        <v>338</v>
+      </c>
+      <c r="D61" t="s">
+        <v>332</v>
+      </c>
+      <c r="E61">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B62">
+        <v>1006124</v>
+      </c>
+      <c r="C62" t="s">
+        <v>339</v>
+      </c>
+      <c r="D62" t="s">
+        <v>332</v>
+      </c>
+      <c r="E62">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B63">
+        <v>1006482</v>
+      </c>
+      <c r="C63" t="s">
+        <v>340</v>
+      </c>
+      <c r="D63" t="s">
+        <v>332</v>
+      </c>
+      <c r="E63">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B64">
+        <v>1007125</v>
+      </c>
+      <c r="C64" t="s">
+        <v>341</v>
+      </c>
+      <c r="D64" t="s">
+        <v>332</v>
+      </c>
+      <c r="E64">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
